--- a/LLMCASE/标准数据/多轮带改写_标准化_20260421_111851.xlsx
+++ b/LLMCASE/标准数据/多轮带改写_标准化_20260421_111851.xlsx
@@ -7984,14 +7984,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8447,28 +8440,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -8477,118 +8473,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -8939,7 +8932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:E125"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <sheetData>
@@ -9130,7 +9123,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" hidden="1" spans="1:5">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -9147,7 +9140,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:5">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -9164,7 +9157,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" hidden="1" spans="1:5">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -9181,7 +9174,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" hidden="1" spans="1:5">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>51</v>
       </c>
@@ -9317,7 +9310,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" hidden="1" spans="1:5">
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>77</v>
       </c>
@@ -9487,7 +9480,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="33" hidden="1" spans="1:5">
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
         <v>107</v>
       </c>
@@ -9742,7 +9735,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:5">
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>150</v>
       </c>
@@ -9759,7 +9752,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="1:5">
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
         <v>152</v>
       </c>
@@ -9810,7 +9803,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="52" hidden="1" spans="1:5">
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
         <v>162</v>
       </c>
@@ -9929,7 +9922,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="1:5">
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
         <v>179</v>
       </c>
@@ -10116,7 +10109,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="70" hidden="1" spans="1:5">
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>209</v>
       </c>
@@ -10167,7 +10160,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="73" hidden="1" spans="1:5">
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
         <v>218</v>
       </c>
@@ -10184,7 +10177,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" hidden="1" spans="1:5">
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
         <v>219</v>
       </c>
@@ -10201,7 +10194,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="75" hidden="1" spans="1:5">
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>220</v>
       </c>
@@ -10218,7 +10211,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="76" hidden="1" spans="1:5">
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
         <v>221</v>
       </c>
@@ -10235,7 +10228,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="77" hidden="1" spans="1:5">
+    <row r="77" spans="1:5">
       <c r="A77" t="s">
         <v>223</v>
       </c>
@@ -10252,7 +10245,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="78" hidden="1" spans="1:5">
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
         <v>225</v>
       </c>
@@ -10269,7 +10262,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="79" hidden="1" spans="1:5">
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
         <v>226</v>
       </c>
@@ -10286,7 +10279,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="80" hidden="1" spans="1:5">
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
         <v>228</v>
       </c>
@@ -10303,7 +10296,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="81" hidden="1" spans="1:5">
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
         <v>230</v>
       </c>
@@ -10320,7 +10313,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="82" hidden="1" spans="1:5">
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
         <v>231</v>
       </c>
@@ -10337,7 +10330,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="83" hidden="1" spans="1:5">
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
         <v>233</v>
       </c>
@@ -10354,7 +10347,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="84" hidden="1" spans="1:5">
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
         <v>234</v>
       </c>
@@ -10371,7 +10364,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="85" hidden="1" spans="1:5">
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
         <v>219</v>
       </c>
@@ -10388,7 +10381,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="86" hidden="1" spans="1:5">
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
         <v>218</v>
       </c>
@@ -10405,7 +10398,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="87" hidden="1" spans="1:5">
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
         <v>218</v>
       </c>
@@ -10422,7 +10415,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="88" hidden="1" spans="1:5">
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
         <v>236</v>
       </c>
@@ -10439,7 +10432,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="89" hidden="1" spans="1:5">
+    <row r="89" spans="1:5">
       <c r="A89" t="s">
         <v>238</v>
       </c>
@@ -10456,7 +10449,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="90" hidden="1" spans="1:5">
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
         <v>223</v>
       </c>
@@ -10626,7 +10619,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="100" hidden="1" spans="1:5">
+    <row r="100" spans="1:5">
       <c r="A100" t="s">
         <v>266</v>
       </c>
@@ -11070,159 +11063,6 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E125" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="安全助手(零信任）客户端FAQ&#10;参考下图：&#10;&#10;1.5、问题：打开零信任时提示连接控制器失败，如下图：&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;选择控制器切换124.71.208.207地址；&#10;&#10;b.如a步骤切换控制器地址依然不解决的情况下，可选择重置控制器再输入124.71.208.207参考下图：&#10;&#10;1.6、问题：启动零信任时提示JavaScript错误，无法正常启动，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.打开终端—sudo vi /etc/hosts文件下添加127.0.0.1 localhost&#10;&#10;1.7、问题：nslookup正常解析域名情况下，使用safari、火狐浏览器访问应用报403，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.更换Google浏览器，即可正常访问应用&#10;&#10;1.8、问题：启动零信任时无快捷登录方式，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;随机输入一个用户名，再返回上一级，选择快捷登录方式，参考下图：&#10;&#10;1.9、问题：退出零信任后发现外网基本上不了例如：www.baidu.com&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;（2）双击点卸载&#10;&#10;（3）输入安全助手卸载码（e2vPsv8$）后，运行卸载&#10;&#10;4、零信任安装指引&#10;（1）双击点击安装包打开------&gt;点“是” ，如下图&#10;&#10;（2）点—&gt;我同意，如下图&#10;&#10;（3）选择安装位置（可自定义选择安装位置）默认即可，点击—&gt;安装，如下图&#10;&#10;（4）等待安装完成即可，如下图&#10;&#10;（5）安装完成默认勾选运行零信任，桌面可看到零信任图标，如下图&#10;&#10;(6)打开零信任扫码登录，即可通过浏览器访问内部系统，如下图&#10;&#10;(7)如果第一次安装提示需要输入控制器地址，请输入sec.zy.com或124.71.208.207，点击确认后扫码登录使用&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;最佳设置&#10;1.2控制器地址：124.71.208.207&#10;&#10;1.3零信任软件推荐设置【重要：减少零信任被误关闭】&#10;&#10;2、零信任软件常见问题：&#10;1、提示不合法的用户名【返回上一级，选择快捷方式登录】&#10;提示会话已经过期，请重新登陆【返回上一级，选择快捷方式登录】&#10;扫码登录提示认证失败【返回上一级，选择快捷方式登录】&#10;&#10;2、登陆零信任后提示无无法访问此网页【关闭浏览器，重新登陆零信任并刷新策略】&#10;&#10;3、打开零信任扫码登录后提示开启私网DNS失败，请稍后重试【联系IT帮助台获取最新版本安装包并覆盖安装】&#10;&#10;4、网络及系统问题&#10;4.1退出零信任后无法访问外网【清除本地dns 127.0.0.1设置或修改为自动获取】&#10;macbook：&#10;Windwos：&#10;&#10;4.2退出零信任后可以登陆企微和微信，无法打开网页【修改Internet代理】&#10;&#10;4.3软件冲突--IOA【网络异常，卸载IOA（已不再使用）并重启电脑】&#10;&#10;4.3开机进入桌面很慢，自动弹窗警告【卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项】&#10;&#10;5、用户权限相关&#10;5.1打开零信任无OA访问窗口，空白&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;零信任配置指引&#10;下载安装包&#10;Windows系统版本&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe&#10;&#10;Macbook版本&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250715/TrustCyberLink_PC_Setup_2.207.122.dmg&#10;&#10;2、安装完成后：&#10;控制器地址:124.71.208.207&#10;&#10;3、企业微信扫码登录后即可访问应用&#10;&#10;4、进来界面后单击设置按钮-勾选开机自动运行-勾选最小化到托盘或勾选退出TrustCyberLink&#10;&#10;5、退出登陆&#10;企业微信扫码登录后，在不使用零信任时可选择退出登录&#10;&#10;扫码登陆时认证失败&#10;重新进入扫码登陆界面即可&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;&#10;问题：mac端登录零信任后提示以下报错&#10;&#10;答案：&gt;1：打开终端检查&#10;输入sudo vi /etc/hosts&#10;查看下面是否有存在127.0.0.1 localhost，如果没有需要手动添加上去&#10;2：先点退出零信任，再查看网络上的dns是不是有127.0.0.1， 如果存在需要手动去掉重新登录即可&#10;插图：（如有）&#10;&#10;问题：安全助手卸载办法&#10;答案：&gt;&#10;Windows版客户端&#10;https://doc.weixin.qq.com/doc/w3_AScA5wbEAIkCNuZkWktsqQDuXa04c?scode=AO4AZgeBAAsXMgnZwMAScA5wbEAIk&#10;Mac版客户端&#10;https://doc.weixin.qq.com/doc/w3_AcQAcwauALkCNx9aHWdGuQ861ZCTg?scode=AO4AZgeBAAshjQyPqvAScA5wbEAIk&#10;插图：（如有）&#10;&#10;问题：：如何修改host文件（mac）&#10;答案：&gt;1：打开终端检查&#10;输入sudo vi /etc/hosts&#10;查看下面是否有存在127.0.0.1 localhost，如果没有需要手动添加上去&#10;2：先点退出零信任，再查看网络上的dns是不是有127.0.0.1， 如果存在需要手动去掉重新登录即可&#10;插图：（如有）&#10;&#10;问题：：如何修改host文件（Windows）&#10;答案：&gt;进入C:\Windows\System32\drivers\etc\hosts，打开host文件，输入127.0.0.1 localhost，编辑完成保存关闭文件"/>
-        <filter val="安全助手(零信任）客户端FAQ&#10;参考下图：&#10;&#10;1.5、问题：打开零信任时提示连接控制器失败，如下图：&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;选择控制器切换124.71.208.207地址；&#10;&#10;b.如a步骤切换控制器地址依然不解决的情况下，可选择重置控制器再输入124.71.208.207参考下图：&#10;&#10;1.6、问题：启动零信任时提示JavaScript错误，无法正常启动，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.打开终端—sudo vi /etc/hosts文件下添加127.0.0.1 localhost&#10;&#10;1.7、问题：nslookup正常解析域名情况下，使用safari、火狐浏览器访问应用报403，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.更换Google浏览器，即可正常访问应用&#10;&#10;1.8、问题：启动零信任时无快捷登录方式，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;随机输入一个用户名，再返回上一级，选择快捷登录方式，参考下图：&#10;&#10;1.9、问题：退出零信任后发现外网基本上不了例如：www.baidu.com&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;最佳设置&#10;1.2控制器地址：124.71.208.207&#10;&#10;1.3零信任软件推荐设置【重要：减少零信任被误关闭】&#10;&#10;2、零信任软件常见问题：&#10;1、提示不合法的用户名【返回上一级，选择快捷方式登录】&#10;提示会话已经过期，请重新登陆【返回上一级，选择快捷方式登录】&#10;扫码登录提示认证失败【返回上一级，选择快捷方式登录】&#10;&#10;2、登陆零信任后提示无无法访问此网页【关闭浏览器，重新登陆零信任并刷新策略】&#10;&#10;3、打开零信任扫码登录后提示开启私网DNS失败，请稍后重试【联系IT帮助台获取最新版本安装包并覆盖安装】&#10;&#10;4、网络及系统问题&#10;4.1退出零信任后无法访问外网【清除本地dns 127.0.0.1设置或修改为自动获取】&#10;macbook：&#10;Windwos：&#10;&#10;4.2退出零信任后可以登陆企微和微信，无法打开网页【修改Internet代理】&#10;&#10;4.3软件冲突--IOA【网络异常，卸载IOA（已不再使用）并重启电脑】&#10;&#10;4.3开机进入桌面很慢，自动弹窗警告【卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项】&#10;&#10;5、用户权限相关&#10;5.1打开零信任无OA访问窗口，空白&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;（2）双击点卸载&#10;&#10;（3）输入安全助手卸载码（e2vPsv8$）后，运行卸载&#10;&#10;4、零信任安装指引&#10;（1）双击点击安装包打开------&gt;点“是” ，如下图&#10;&#10;（2）点—&gt;我同意，如下图&#10;&#10;（3）选择安装位置（可自定义选择安装位置）默认即可，点击—&gt;安装，如下图&#10;&#10;（4）等待安装完成即可，如下图&#10;&#10;（5）安装完成默认勾选运行零信任，桌面可看到零信任图标，如下图&#10;&#10;(6)打开零信任扫码登录，即可通过浏览器访问内部系统，如下图&#10;&#10;(7)如果第一次安装提示需要输入控制器地址，请输入sec.zy.com或124.71.208.207，点击确认后扫码登录使用&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;零信任配置指引&#10;下载安装包&#10;Windows系统版本&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe&#10;&#10;Macbook版本&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250715/TrustCyberLink_PC_Setup_2.207.122.dmg&#10;&#10;2、安装完成后：&#10;控制器地址:124.71.208.207&#10;&#10;3、企业微信扫码登录后即可访问应用&#10;&#10;4、进来界面后单击设置按钮-勾选开机自动运行-勾选最小化到托盘或勾选退出TrustCyberLink&#10;&#10;5、退出登陆&#10;企业微信扫码登录后，在不使用零信任时可选择退出登录&#10;&#10;扫码登陆时认证失败&#10;重新进入扫码登陆界面即可&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;安全助手（零信任）客户端FAQ&#10;操作问题&#10;问题：登录零信任后访问应用时浏览器页面提示403forbidden，如下图：&#10;&#10;设备类型：&#10;Windows/macbook&#10;解决方案：&#10;使用其他浏览器访问&#10;设置浏览器后重新打开进行访问应用&#10;（1）Google浏览器&#10;&#10;（2）火狐浏览器&#10;&#10;问题：登录零信任后当访问应用时提示无法访问此网站，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10; 先关闭浏览器，点击刷新 重新获取策略（刷新一次未解决可以继续点击刷新）参考下图：&#10;&#10; 当a步骤重新获取策略后还是一样提示无法访问此网站时可退出登录零信任，再退出零信任客户端，重新打开扫码登录可参考下图：&#10;&#10;问题：打开零信任扫码登陆时，提示不合法的状态，如下图&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;a.返回上一级，去掉用户名，选择快捷方式登陆参考下图：&#10;&#10;1.4、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;返回上一级，重新选择快捷方式登陆"/>
-        <filter val="安全助手(零信任）客户端FAQ&#10;参考下图：&#10;&#10;1.5、问题：打开零信任时提示连接控制器失败，如下图：&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;选择控制器切换124.71.208.207地址；&#10;&#10;b.如a步骤切换控制器地址依然不解决的情况下，可选择重置控制器再输入124.71.208.207参考下图：&#10;&#10;1.6、问题：启动零信任时提示JavaScript错误，无法正常启动，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.打开终端—sudo vi /etc/hosts文件下添加127.0.0.1 localhost&#10;&#10;1.7、问题：nslookup正常解析域名情况下，使用safari、火狐浏览器访问应用报403，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.更换Google浏览器，即可正常访问应用&#10;&#10;1.8、问题：启动零信任时无快捷登录方式，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;随机输入一个用户名，再返回上一级，选择快捷登录方式，参考下图：&#10;&#10;1.9、问题：退出零信任后发现外网基本上不了例如：www.baidu.com&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;最佳设置&#10;1.2控制器地址：124.71.208.207&#10;&#10;1.3零信任软件推荐设置【重要：减少零信任被误关闭】&#10;&#10;2、零信任软件常见问题：&#10;1、提示不合法的用户名【返回上一级，选择快捷方式登录】&#10;提示会话已经过期，请重新登陆【返回上一级，选择快捷方式登录】&#10;扫码登录提示认证失败【返回上一级，选择快捷方式登录】&#10;&#10;2、登陆零信任后提示无无法访问此网页【关闭浏览器，重新登陆零信任并刷新策略】&#10;&#10;3、打开零信任扫码登录后提示开启私网DNS失败，请稍后重试【联系IT帮助台获取最新版本安装包并覆盖安装】&#10;&#10;4、网络及系统问题&#10;4.1退出零信任后无法访问外网【清除本地dns 127.0.0.1设置或修改为自动获取】&#10;macbook：&#10;Windwos：&#10;&#10;4.2退出零信任后可以登陆企微和微信，无法打开网页【修改Internet代理】&#10;&#10;4.3软件冲突--IOA【网络异常，卸载IOA（已不再使用）并重启电脑】&#10;&#10;4.3开机进入桌面很慢，自动弹窗警告【卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项】&#10;&#10;5、用户权限相关&#10;5.1打开零信任无OA访问窗口，空白&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.需要把本机网络的DNS127.0.0.1去掉即可，参考下图：&#10;&#10;1.10、问题：为什么我登录不了TMS、EVIP……，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;请先安装零信任，并扫码登录—登录后不能退出零信任&#10;参考下图：&#10;&#10;1.11、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;去到安装目录C:\Program Files (x86)\TrustCyberLink目录下打开TrustCyberLink.exe&#10;1.12、问题：打开零信任没有企业微信按钮 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新打开或者点击控制切换器—点击124.71.208.207或者sec.zy.com-点击确认即可&#10;1.13、问题：安装助手完成时零信任未安装成功 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新安装即可&#10;1.14、问题：提示 “由于找不到 UAADataCenter.dl，无法继续执行代码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;安全助手（零信任）客户端FAQ&#10;操作问题&#10;问题：登录零信任后访问应用时浏览器页面提示403forbidden，如下图：&#10;&#10;设备类型：&#10;Windows/macbook&#10;解决方案：&#10;使用其他浏览器访问&#10;设置浏览器后重新打开进行访问应用&#10;（1）Google浏览器&#10;&#10;（2）火狐浏览器&#10;&#10;问题：登录零信任后当访问应用时提示无法访问此网站，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10; 先关闭浏览器，点击刷新 重新获取策略（刷新一次未解决可以继续点击刷新）参考下图：&#10;&#10; 当a步骤重新获取策略后还是一样提示无法访问此网站时可退出登录零信任，再退出零信任客户端，重新打开扫码登录可参考下图：&#10;&#10;问题：打开零信任扫码登陆时，提示不合法的状态，如下图&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;a.返回上一级，去掉用户名，选择快捷方式登陆参考下图：&#10;&#10;1.4、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;返回上一级，重新选择快捷方式登陆&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;（2）双击点卸载&#10;&#10;（3）输入安全助手卸载码（e2vPsv8$）后，运行卸载&#10;&#10;4、零信任安装指引&#10;（1）双击点击安装包打开------&gt;点“是” ，如下图&#10;&#10;（2）点—&gt;我同意，如下图&#10;&#10;（3）选择安装位置（可自定义选择安装位置）默认即可，点击—&gt;安装，如下图&#10;&#10;（4）等待安装完成即可，如下图&#10;&#10;（5）安装完成默认勾选运行零信任，桌面可看到零信任图标，如下图&#10;&#10;(6)打开零信任扫码登录，即可通过浏览器访问内部系统，如下图&#10;&#10;(7)如果第一次安装提示需要输入控制器地址，请输入sec.zy.com或124.71.208.207，点击确认后扫码登录使用"/>
-        <filter val="安全助手(零信任）客户端FAQ&#10;参考下图：&#10;&#10;1.5、问题：打开零信任时提示连接控制器失败，如下图：&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;选择控制器切换124.71.208.207地址；&#10;&#10;b.如a步骤切换控制器地址依然不解决的情况下，可选择重置控制器再输入124.71.208.207参考下图：&#10;&#10;1.6、问题：启动零信任时提示JavaScript错误，无法正常启动，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.打开终端—sudo vi /etc/hosts文件下添加127.0.0.1 localhost&#10;&#10;1.7、问题：nslookup正常解析域名情况下，使用safari、火狐浏览器访问应用报403，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.更换Google浏览器，即可正常访问应用&#10;&#10;1.8、问题：启动零信任时无快捷登录方式，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;随机输入一个用户名，再返回上一级，选择快捷登录方式，参考下图：&#10;&#10;1.9、问题：退出零信任后发现外网基本上不了例如：www.baidu.com&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;（2）双击点卸载&#10;&#10;（3）输入安全助手卸载码（e2vPsv8$）后，运行卸载&#10;&#10;4、零信任安装指引&#10;（1）双击点击安装包打开------&gt;点“是” ，如下图&#10;&#10;（2）点—&gt;我同意，如下图&#10;&#10;（3）选择安装位置（可自定义选择安装位置）默认即可，点击—&gt;安装，如下图&#10;&#10;（4）等待安装完成即可，如下图&#10;&#10;（5）安装完成默认勾选运行零信任，桌面可看到零信任图标，如下图&#10;&#10;(6)打开零信任扫码登录，即可通过浏览器访问内部系统，如下图&#10;&#10;(7)如果第一次安装提示需要输入控制器地址，请输入sec.zy.com或124.71.208.207，点击确认后扫码登录使用&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;最佳设置&#10;1.2控制器地址：124.71.208.207&#10;&#10;1.3零信任软件推荐设置【重要：减少零信任被误关闭】&#10;&#10;2、零信任软件常见问题：&#10;1、提示不合法的用户名【返回上一级，选择快捷方式登录】&#10;提示会话已经过期，请重新登陆【返回上一级，选择快捷方式登录】&#10;扫码登录提示认证失败【返回上一级，选择快捷方式登录】&#10;&#10;2、登陆零信任后提示无无法访问此网页【关闭浏览器，重新登陆零信任并刷新策略】&#10;&#10;3、打开零信任扫码登录后提示开启私网DNS失败，请稍后重试【联系IT帮助台获取最新版本安装包并覆盖安装】&#10;&#10;4、网络及系统问题&#10;4.1退出零信任后无法访问外网【清除本地dns 127.0.0.1设置或修改为自动获取】&#10;macbook：&#10;Windwos：&#10;&#10;4.2退出零信任后可以登陆企微和微信，无法打开网页【修改Internet代理】&#10;&#10;4.3软件冲突--IOA【网络异常，卸载IOA（已不再使用）并重启电脑】&#10;&#10;4.3开机进入桌面很慢，自动弹窗警告【卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项】&#10;&#10;5、用户权限相关&#10;5.1打开零信任无OA访问窗口，空白&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;零信任配置指引&#10;下载安装包&#10;Windows系统版本&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe&#10;&#10;Macbook版本&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250715/TrustCyberLink_PC_Setup_2.207.122.dmg&#10;&#10;2、安装完成后：&#10;控制器地址:124.71.208.207&#10;&#10;3、企业微信扫码登录后即可访问应用&#10;&#10;4、进来界面后单击设置按钮-勾选开机自动运行-勾选最小化到托盘或勾选退出TrustCyberLink&#10;&#10;5、退出登陆&#10;企业微信扫码登录后，在不使用零信任时可选择退出登录&#10;&#10;扫码登陆时认证失败&#10;重新进入扫码登陆界面即可&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【零信任-5】零信任-Windows清除DNS指引&#10;故障现象：网络正常连接，浏览器没网，但是企微和微信等能正常登录和对话&#10;一、同时按“win+R”输入“control”&#10;&#10;弹出“控制面板”界面选择类别&#10;&#10;点击“查看网络状态和任务”&#10;&#10;点击如图位置&#10;&#10;点击“属性”&#10;&#10;点击“Internet 协议版本 4(TCP/IPv4)”&#10;&#10;点击“自动获得 DNS 服务器地址(B)”&#10;&#10;最终完成效果&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）"/>
-        <filter val="window系统共享文件夹连接指引&#10;&#10;2.2、共享文件夹创建快捷方式放置桌面&#10;2.2.1、需要创建快捷方式的文件夹上，点击【右键】，选择【创建快捷方式】，该文件夹的快捷访问路径就在桌面可查&#10;&#10;无法正常连接共享盘&#10;背景：情况1：老师去其它校区教研或者教学，回到自己常驻校区发现共享盘连接不上&#10;      情况2：老师需要使用其它校区共享盘工作，连接不上共享盘&#10;3.1、删除Windows凭证，再进行重新连接&#10;按键盘 WIN( 田 ) + R , 运行框中输入‘control’-点击‘凭证管理器’&#10;&#10;点击‘window凭据’-点击‘192.168.0.26’-点击‘删除’&#10;&#10;删除后记得重启电脑，更新改动，重新连接共享文件夹&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【共享-2】校区MAC系统共享文件夹连接指引&#10;指引文档介绍&#10;校区老师电脑&#10;访问共享文件夹的用户名和密码规则：&#10;业务对应的用户名:  成长-班辅（fdb ）  亲子-个辅（gf ）   志业（sgz）&#10;用户名：业务字母代表&#10;密码：zy+校区+业务缩写&#10;比如说鸟巢成长校区：用户名是fdb ，密码是zyncfdb&#10;（注意：成长（fdb ）  亲子（gf ）   志业（gz）的文件夹是有读写权限）&#10;校区的课室一体机&#10;课室共享文件夹ks（在一体机上使用）：&#10;用户名：ks&#10;密码：ks&#10;（注意：ks文件夹此时只有读的权限）&#10;&#10;映射共享网络磁盘&#10;2.1、访问共享文件夹&#10;(1) 在电脑的左上角，点击 【GO/前往】-【connect to server/连接服务器】，或者使用键盘快捷键【command+k】，&#10;&#10;输入校区共享盘地址 smb://192.168.0.26&#10;&#10;注：图中第2步 “+” 必需要操作&#10;输入账号密码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【共享-1】window系统共享文件夹连接指引&#10;指引文档介绍&#10;校区老师电脑&#10;访问共享文件夹的用户名和密码规则：&#10;业务对应的用户名:  成长-班辅（fdb ）  亲子-个辅（gf ）   志业（sgz）&#10;用户名：业务字母代表&#10;密码：zy+校区+业务缩写&#10;比如说鸟巢成长校区：用户名是fdb ，密码是zyncfdb&#10;（注意：成长（fdb ）  亲子（gf ）   志业（gz）的文件夹是有读写权限）&#10;校区的课室一体机&#10;课室共享文件夹ks（在一体机上使用）：&#10;用户名：ks&#10;密码：ks&#10;（注意：ks文件夹此时只有读的权限）&#10;&#10;映射共享网络磁盘&#10;2.1、访问共享文件夹&#10;（1）点击【我的电脑】或【此电脑】，点击左上角，输入校区共享IP地址 \\192.168.0.26，然后点击回车&#10;&#10;（2）见到共享文件夹，例如“ks”(课室共享) 、“班辅共享”或“个辅共享”，双击需要访问的共享文件夹，例如“班辅共享”，在弹出的安全验证窗口输入验证信息用户“fdb”、密码“zyqxlfdb”，并且勾选“记住我的凭据”（需按校区修改密码）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;校区MAC系统共享文件夹连接指引&#10;输入完点连接就会自动弹出共享盘&#10;&#10;设置开机自动挂载共享盘：打开系统偏好设置，点选“用户和群组”&#10;&#10;在左侧列表中选择你的用户名，点选“登录项”标签&#10;将已经挂载的网络驱动器图标拖放到登录项列表中&#10;可选：点选“隐藏”框，这样系统启动和登录时挂载网络驱动器后，不会自动打开 Finder 窗口&#10;&#10;2.2共享文件夹创建快捷方式放置桌面&#10;需要创建快捷方式的文件夹上，点击【右键】，选择【创建快捷方式】，该文件夹的快捷访问路径就在桌面可查&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;共享盘的处理方式&#10;、操作指南&#10;&#10;一、电脑标准：&#10;1、不可有共享快捷访问方式&#10;2、清除共享已存登录密码&#10;二、操作指南&#10;1、删除快捷访问方式&#10;2、删除共享密码&#10;&#10;3、删除共享快捷方式后，&#10;如何访问共享&#10;&#10;打开后，输入共享访问密码即可（再次访问后，不要钩先记住密码）"/>
-        <filter val="安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;（2）双击点卸载&#10;&#10;（3）输入安全助手卸载码（e2vPsv8$）后，运行卸载&#10;&#10;4、零信任安装指引&#10;（1）双击点击安装包打开------&gt;点“是” ，如下图&#10;&#10;（2）点—&gt;我同意，如下图&#10;&#10;（3）选择安装位置（可自定义选择安装位置）默认即可，点击—&gt;安装，如下图&#10;&#10;（4）等待安装完成即可，如下图&#10;&#10;（5）安装完成默认勾选运行零信任，桌面可看到零信任图标，如下图&#10;&#10;(6)打开零信任扫码登录，即可通过浏览器访问内部系统，如下图&#10;&#10;(7)如果第一次安装提示需要输入控制器地址，请输入sec.zy.com或124.71.208.207，点击确认后扫码登录使用&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;安全助手卸载和零信任工具安装指引&#10;&#10;注明：先卸载安全助手，后安装零信任工具，如果没有安全助手，可覆盖安装零信任工具&#10;&#10;1、零信任工具下载链接：&#10;Windows版本：&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe  （新版本下载链接）  &#10;&#10;2、管理员口令和安全助手卸载码都是e2vPsv8$&#10;&#10;3、安全助手卸载指引&#10;3.1、第一种卸载方式&#10;（1） 右键安全助手图标，点击进入特权模式，输入管理员口令（e2vPsv8$)即可进入特权模式&#10;&#10;（2）进入特权模式后，在本地电脑C:\Windows\LVUAAgentInstBaseRoot找到此文件运行卸载 &#10;&#10;输入安全助手卸载码（卸载密码默认 e2vPsv8$）&#10;&#10;3.2、第二种卸载方式&#10;（1）若是Win10 系统点击左下角，找到并打开文件夹“UniAccess安全助手”，右键点击“启动或显示托盘图标 ”，点击更多，点击打开文件位置&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.需要把本机网络的DNS127.0.0.1去掉即可，参考下图：&#10;&#10;1.10、问题：为什么我登录不了TMS、EVIP……，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;请先安装零信任，并扫码登录—登录后不能退出零信任&#10;参考下图：&#10;&#10;1.11、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;去到安装目录C:\Program Files (x86)\TrustCyberLink目录下打开TrustCyberLink.exe&#10;1.12、问题：打开零信任没有企业微信按钮 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新打开或者点击控制切换器—点击124.71.208.207或者sec.zy.com-点击确认即可&#10;1.13、问题：安装助手完成时零信任未安装成功 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新安装即可&#10;1.14、问题：提示 “由于找不到 UAADataCenter.dl，无法继续执行代码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【零信任-6】windows安全助手（零信任）卸载&#10;&#10;1   找到软件所在位置&#10;&#10;1.1 找到安装的软件的位置进行卸载&#10;&#10;a.通过桌面 win 键查找进入&#10;&#10;Win 键安全助手右键点击“ 启动或显示托盘图标”更多打开文件位置&#10;&#10;b.直接输入到安装目录进入&#10;&#10;C:\ProgramData\Microsoft\Windows\Start Menu\Programs\安全助手&#10;&#10;1.2 双击运行卸载&#10;&#10;1.3 管理员口令是e2vPsv8$&#10;&#10;1.4 完成卸载&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;零信任配置指引&#10;下载安装包&#10;Windows系统版本&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe&#10;&#10;Macbook版本&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250715/TrustCyberLink_PC_Setup_2.207.122.dmg&#10;&#10;2、安装完成后：&#10;控制器地址:124.71.208.207&#10;&#10;3、企业微信扫码登录后即可访问应用&#10;&#10;4、进来界面后单击设置按钮-勾选开机自动运行-勾选最小化到托盘或勾选退出TrustCyberLink&#10;&#10;5、退出登陆&#10;企业微信扫码登录后，在不使用零信任时可选择退出登录&#10;&#10;扫码登陆时认证失败&#10;重新进入扫码登陆界面即可&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）"/>
-        <filter val="【打印机-8】Windows系统安装京瓷打印机指引&#10;一、下载打印机驱动包存到电脑硬盘上&#10;驱动包下载地址：京瓷打印机驱动下载&#10;二、安装打印机&#10;注：安装前需要先收集打印机IP地址和型号（部分共用的打印机需要准备部门密码）&#10;打印机IP地址，图示&#10;&#10;查询打印机型号，图示&#10;&#10;1、解压驱动包&#10;&#10;2、打开安装程序, 按步骤安装&#10;进入文件夹，双击Setup.exe&#10;&#10;接受，选择自定义安装&#10;&#10;以下内容请根据打印机实际型号和IP填写&#10;&#10;添加打印机驱动和安装升级的组件&#10;&#10;打印机安装完成&#10;&#10;三、设置打印机&#10;1、修改名称、设置双面打印&#10;打开计算机，跳至控制面板，进入硬件设备&#10;&#10;右击，打印机属性&#10;&#10;修改打印机名称&#10;&#10;设置双面打印&#10;&#10;2、打印机显示脱机时，需要设置取消SNMP&#10;&#10;3、添加部门id&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-6】Windows系统添加一体打印机部门ID&#10;1、打开控制面板&#10;&#10;2、右击对应型号打印机 - 点打印机属性（型号可以在打印机面前看到）&#10;&#10;3、点最后一项设备设置 - 点管理员&#10;&#10;注：每机每部门的ID都不一样&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址： http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;悦智学打印指引手册-打印机插件安装-0604&#10;打印机安装插件指引&#10;1. 打开火狐浏览器&#10;在地址栏输入：about:config 2. &#10;3. 在搜索框搜索：security.tls.version.min &#10;5. TMS点击执行安装&#10;&#10;警告：面临潜在的安全风险&#10;Firefox检测到潜在的安全威胁，因此没有继续访问localhost若您访问此网站，攻击者可能会尝试&#10;详细了解&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-3】MAC 连接打印机操作指引&#10;一、下载驱动包&#10;京瓷打印机mac系统驱动下载&#10;&#10;注：安装前需要先知道打印机IP地址，如下图所示：&#10;&#10;安装驱动&#10;双击驱动包&#10;&#10;若在桌面没有找到驱动，则使用“command+空格键”弹出的搜索框里输入“Kyocera OS X 10.9+ Web build 2024.05.16”，找到并双击驱动包&#10;&#10;双击安装程序&#10;&#10;一路安装&#10;&#10;安装完成后，需要重启电脑!!!&#10;&#10;二、添加打印机&#10;进入系统偏好设置&#10;&#10;进入打印机与扫描仪&#10;&#10;添加设置&#10;&#10;选择IP连接，输入对应打印机IP地址，选择连接协议&#10;&#10;（若电脑无法自动识别打印机型号，请检查打印机是否出现网络问题，例如网线松动等）&#10;&#10;完成添加，可以进行打印&#10;三、各协议解释&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-7】Windows修改打印机IP指引&#10;一、同时按“win+R”输入“control”&#10;&#10;弹出“控制面板”界面选择类别&#10;&#10;点击“查看设备和打印机”&#10;&#10;选择需要修改IP地址的打印机&#10;当前以“Kyocera TASKalfa 300i KX”打印机为例&#10;&#10;选择打印机，右键“打印机属性”&#10;&#10;选择”端口“，选中当前打印机端口&#10;&#10;选择”配置端口“&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址： http://oa.zy.com ）"/>
-        <filter val="【打铃-3】打铃系统(雨花石版)设置指引&#10;双击打开程序&#10;&#10;2、设置打铃计划先暂停任务，再点管理（操作界面如下图）&#10;&#10;3、添加与修改打铃计划，最后记得点启用，计划才生效&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打铃-2】打铃系统(自动版)设置指引&#10;打开桌面快捷方式&#10;&#10;2.设定单日任务计划，如下图所示&#10;&#10;3.复制到其他星期，如下图&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;雨花石打铃系统安装前必看和SN&#10;雨花石打铃系统安装及注册注意事项：1、建议装D盘2、安装的第一步是不要运行程序，要先把快捷方式改成“在管理员模式下运行”才能运行和注册，否则注册不生效遇到注册不生效情况，需要重装系统之后重复以上步骤注册用以下信息：用户名：紫色缘序列号：TXkb-VNwr-pLpo-UKfe-hzsf&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;TMK操作说明文档&#10;&#10;普通电话跟进&#10;03 &#10;来电跟进&#10;&#10;来电接听&#10;需要点击“接起”&#10;有来电的时候，linphone会弹屏并响铃，&#10;02759565129&#10;sip:02759565129@172.16.1.118&#10;&#10;来电接听&#10;“接起”之后&#10;（支持“转接”和&#10;可完善客户信息并填写跟进信息&#10;，系统会自动弹屏，&#10;&#10;普通电话跟进&#10;04 &#10;来电回访&#10;&#10;来电回访&#10;报表对资源进行回访&#10;（可通过“预约回访时间”筛选）&#10;1、客服可在“座席呼入管理”&#10;“座席回访记录&#10;2、回访记录可在&#10;报表查看"/>
-        <filter val="校区切换壁纸指引&#10;【一体机-6】手动切换壁纸指引&#10;背景说明：&#10; IT桌面支持组已在校区教学一体机部署好桌面壁纸自动更换程序，校区老师只需要在指定的《壁纸》文件夹按以下要求进行图片更换即可&#10;进去D盘目录的“壁纸”文件夹&#10;注意：准备要设置的壁纸一定要为”jpg“格式的图片，所以设置前需将不是“jpg”格式的壁纸改为jpg格式，同时将壁纸命名为“1.jpg”&#10;1.1修改格式-指南，例如：将png修改为jpg&#10;查看--&gt;勾选文件扩展名&#10;&#10;壁纸重命名修改前：修改后：回车确认即可&#10;2、备份当前“壁纸”文件夹中的“1.jpg”改为“3.jpg”&#10;&#10;修改后&#10;&#10;这一步为了以后优惠过期了，如有需要切换回来这张壁纸做备份&#10;3、设置壁纸&#10;将修改好的“1.jpg”复制到“壁纸”文件夹里&#10;&#10;等待一分钟即可设置成功&#10;返回教学一体机桌面等待1分钟，出现新更换的桌面壁纸表示已更换成功&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【一体机-5】希沃一体机修改信息&#10;1、确认信息&#10;&#10;每台一体机确认以下信息是否正确&#10;&#10;2、修改信息&#10;如果不对，请按照以下步骤修改&#10;&#10;密码验证：密码为252385&#10;&#10;3、希沃管家下载&#10;&#10;https://cstore-pub-cos-seewo-report-tx.seewo.com/seewo-report_uwixmpvuhhulnhlwhmwxqylhvwhhihhh?sign=q-sign-algorithm%3Dsha1%26q-ak%3DAKIDJUXMxJRLzPaeMp20jDSTFl23pLcdPwDF%26q-sign-time%3D1715822949%3B2031182949%26q-key-time%3D1715822949%3B2031182949%26q-header-list%3Dhost%26q-url-param-list%3Dresponse-content-disposition%26q-signature%3D301def99ef4d42e76603f7e8bae9f2713a143f73&amp;response-content-disposition=attachment%3Bfilename%3D%22SeewoServiceSetup_1.4.6.3588.exe%22%3Bfilename%2A%3Dutf-8%27%27SeewoServiceSetup_1.4.6.3588.exe&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;希沃一体机修改信息&#10;（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【一体机-1】希象传屏下载指引&#10;打开浏览器，输入www.baidu.com&#10;在搜索框，输入希沃官网，进去希沃官网（不要进错了，如图：）&#10;&#10;点击【服务支持】-【希沃软件】，往下拉，找到【希象传屏】-点击【立即下载】，调转页面，往下拉&#10;&#10;找到【希象传屏】-根据需求选择版本&#10;&#10;接收端：希沃一体机选择Windows版本下载&#10;&#10;发送端：根据电脑系统版本进行选择&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;说明书-希沃白板[简称：EasiNote]2024&#10;&#10;图片&#10;排版&#10;名称&#10;file0008.png&#10;&#10;调整&#10;裁剪&#10;&#10;样式首个样式为“无样式”，图片默认为无样式点击需要的样&#10;&#10;替换点击替换按钮打开本地文件夹，选中图片文件后，点击打开&#10;&#10;去背景点击去背景按键可对图片进行背景处理，选中要处理的背&#10;景色进行拖动即可将所选区域同背景色进行去除，如图3-2-2-6-4 所&#10;&#10;2）音视频"/>
-        <filter val="兼职老师企微账号管理指引&#10;2、授权后需要在企微手机端接收【企微微信团队】应用推送消息扫脸实名认证后权限才能生&#10;效&#10;&#10;企业微信团队&#10;企业安装的应用“商加咖微客助手”将于2天后试用到期，到期后企业将无法继续使用，请尽快升级到付费版本前往升级&#10;&#10;1、浏览器打开企微后台登入网址：work.weixin.qq.com/login，企微扫码登入，如未完成第&#10;二部授权，登入后台会提示“当前微信号未注册企业”&#10;&#10;企业微信扫码登录&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;说明书-希沃白板[简称：EasiNote]2024&#10;&#10;8）最小化：点击&#10;最小化按钮可将软件最小化到任务栏&#10;3.3.2 昵称&#10;点击左下角昵称上的&#10;头像按钮，可进入该账号的云空间页面如图&#10;&#10;3-3-2-1老师可在最近课件列表中找到近期打开过的课件，也可以在云空间列表&#10;中切换其他课件、教案进行授课；还可以退出当前账号，使用其他账号登录获取&#10;&#10;课件进行授课&#10;1)切换课件点击云空间列表的课件即可快速加载选中课件进行授课；&#10;&#10;2)退出登录&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;07卓越在线运营后台操作手册V2&#10;登录运营后台一. &#10;打开以下地址，输入通行证账号密码进行登录；&#10;&#10;教师管理二.&#10;1. 新增教师&#10;备注：新增老师的同时系统会自动为新增的老师创建1 个学员账号，账号为企微手机号，密码为手机密码&#10;后六位&#10;选择左侧导航【老师管理-老师列表】，点击【新建老师】；&#10;&#10;点击【确认新增】，完成教师添加&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;08卓越在线常见问题QA&#10;&#10;②我是听课的老师，如何登录学生端&#10;答：听课的老师需要打开学生端，然后选择【其他登录】，账号为您的企业微信手机&#10;&#10;注意，集团员工登录学生端时，都是选择【其他登录】&#10;&#10;③我是辅导老师，如何登录监课页面&#10;&#10;答：辅导老师需要打开网页版：https://zxx.zy.com/mt/live/schedule，然后选择&#10;【通行证登录】，输入你登录企业微信时的账号密码，或者直接用企业微信扫码，即&#10;可登录&#10;&#10;④我是学生/家长，如何登录学生端&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;鲸准教（原AIPT）系统操作文档&#10;&#10;8.4删除老师&#10;可以将老师从老师列表中删除，后续可以重新【添加】&#10;&#10;8.5老师数据&#10;在老师数据Tab，可以按学届查看老师的教学信息，包括老师的带班数量和发布任务的情况&#10;&#10;五、E教学&#10;我的班级&#10;1.1 班级列表&#10;我的班级中的班级列表，呈现了老师所带的班级这里的数据来自于E学校中的班级管理&#10;&#10;1.1 花名册：可在班级列表中查看班级学员名单，且可查看每个学员的详细信息&#10;&#10;1.2 积分榜单：在班级列表的操作栏中新增了【积分榜单】入口，点击后可查看选中班级所有学生的积分获取/排名情况，积分统计方式分为：一周新增积分数量及排名、一月新增积分数量及排名、总积分数量及排名；&#10;&#10;老师们也可以通过选择周次/月份/积分获取方式，来查询目标周次/月份/获取方式的积分获取及排名情况；例如：月份选择了2023年12月，则【一月新增积分】及【一月新增积分排名】则只统计2023年12月的情况;&#10;&#10;老师们也可以点击【导出】按钮，将班级中所有学生的积分情况导出至本地&#10;&#10;积分明细：在积分榜单中，点击学生姓名后，可查看选中学生的积分获取情况页面会展示每个积分获取方式各获得了多少积分"/>
-        <filter val="安全助手(零信任）客户端FAQ&#10;&quot;&#10;1.19、问题：扫码登陆时认证失败 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;重新进入扫码登陆界面即可&#10;1.20、问题：登录了零信任，但是访问不了内网 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;1、确认电脑上没有IOA，或者有没登录IOA（建议卸载了，后续不会用了，原来限制的域名换到了新的零信任）&#10;2、处理掉IOA后，再次扫码登录零信任（退IOA前扫码了的话，也需要退出再扫一次码）&#10;3、登录超时了，退出零信任，重新登录&#10;参考下图：&#10;1.21、问题：开机进入系统很慢，运行慢，杀毒软件不断弹窗 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项&#10;1.22、问题：登录了零信任，点击应用提示“请求失败”  如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;退出零信任，重新登录&#10;1.23、问题：兼职老师登录零信任，应用列表是空白 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;因为零信任同步企微账号，分配组有问题，没有分配到与企微一致的组织架构下，而且分到默认组（需要绿盟排查原因），需要零信任管理员人工更改分组&#10;1.24、问题：部分应用无法访问，如ssoin.zy.com &#10;设备类型：&#10;mac&#10;解决方案：&#10;ping ssoin.zy.com的ip是10.12.81.44，但是在浏览器访问页面，发现请求ip是外网IP，暂未有解决根源的办法，临时办法：本地host绑定为10.12.81.44&#10;设备兼容性问题&#10;2.1、 问题：打开零信任扫码登录后提示开启私网DNS失败，请稍后重试&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.需要把本机网络的DNS127.0.0.1去掉即可，参考下图：&#10;&#10;1.10、问题：为什么我登录不了TMS、EVIP……，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;请先安装零信任，并扫码登录—登录后不能退出零信任&#10;参考下图：&#10;&#10;1.11、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;去到安装目录C:\Program Files (x86)\TrustCyberLink目录下打开TrustCyberLink.exe&#10;1.12、问题：打开零信任没有企业微信按钮 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新打开或者点击控制切换器—点击124.71.208.207或者sec.zy.com-点击确认即可&#10;1.13、问题：安装助手完成时零信任未安装成功 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新安装即可&#10;1.14、问题：提示 “由于找不到 UAADataCenter.dl，无法继续执行代码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;安全助手（零信任）客户端FAQ&#10;操作问题&#10;问题：登录零信任后访问应用时浏览器页面提示403forbidden，如下图：&#10;&#10;设备类型：&#10;Windows/macbook&#10;解决方案：&#10;使用其他浏览器访问&#10;设置浏览器后重新打开进行访问应用&#10;（1）Google浏览器&#10;&#10;（2）火狐浏览器&#10;&#10;问题：登录零信任后当访问应用时提示无法访问此网站，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10; 先关闭浏览器，点击刷新 重新获取策略（刷新一次未解决可以继续点击刷新）参考下图：&#10;&#10; 当a步骤重新获取策略后还是一样提示无法访问此网站时可退出登录零信任，再退出零信任客户端，重新打开扫码登录可参考下图：&#10;&#10;问题：打开零信任扫码登陆时，提示不合法的状态，如下图&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;a.返回上一级，去掉用户名，选择快捷方式登陆参考下图：&#10;&#10;1.4、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;返回上一级，重新选择快捷方式登陆&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;最佳设置&#10;1.2控制器地址：124.71.208.207&#10;&#10;1.3零信任软件推荐设置【重要：减少零信任被误关闭】&#10;&#10;2、零信任软件常见问题：&#10;1、提示不合法的用户名【返回上一级，选择快捷方式登录】&#10;提示会话已经过期，请重新登陆【返回上一级，选择快捷方式登录】&#10;扫码登录提示认证失败【返回上一级，选择快捷方式登录】&#10;&#10;2、登陆零信任后提示无无法访问此网页【关闭浏览器，重新登陆零信任并刷新策略】&#10;&#10;3、打开零信任扫码登录后提示开启私网DNS失败，请稍后重试【联系IT帮助台获取最新版本安装包并覆盖安装】&#10;&#10;4、网络及系统问题&#10;4.1退出零信任后无法访问外网【清除本地dns 127.0.0.1设置或修改为自动获取】&#10;macbook：&#10;Windwos：&#10;&#10;4.2退出零信任后可以登陆企微和微信，无法打开网页【修改Internet代理】&#10;&#10;4.3软件冲突--IOA【网络异常，卸载IOA（已不再使用）并重启电脑】&#10;&#10;4.3开机进入桌面很慢，自动弹窗警告【卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项】&#10;&#10;5、用户权限相关&#10;5.1打开零信任无OA访问窗口，空白&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;（2）双击点卸载&#10;&#10;（3）输入安全助手卸载码（e2vPsv8$）后，运行卸载&#10;&#10;4、零信任安装指引&#10;（1）双击点击安装包打开------&gt;点“是” ，如下图&#10;&#10;（2）点—&gt;我同意，如下图&#10;&#10;（3）选择安装位置（可自定义选择安装位置）默认即可，点击—&gt;安装，如下图&#10;&#10;（4）等待安装完成即可，如下图&#10;&#10;（5）安装完成默认勾选运行零信任，桌面可看到零信任图标，如下图&#10;&#10;(6)打开零信任扫码登录，即可通过浏览器访问内部系统，如下图&#10;&#10;(7)如果第一次安装提示需要输入控制器地址，请输入sec.zy.com或124.71.208.207，点击确认后扫码登录使用"/>
-        <filter val="【监控-5】监控客户端切换账号指引&#10;注意：这个登录软件的账号，并非监控回放的账号，一般为了方便才设置成用户名：user密码：345110jk/it&#10;&#10;打开监控客户端“iVMS-4200 3.13.0.5 客户端”，主菜单界面的右边设备管理&#10;&#10;选择需要更改的监控，点击“笔形状图标”&#10;&#10;修改账号和密码，切换到有回放功能的账号，才可以看回放&#10;&#10;(有回放功能)普通用户1:  userxq  密码: 345110xq&#10;(无回放功能)普通用户2:  user  密码:  345110jk&#10;最后显示“在线”表示连接成功&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【监控-1】Edge浏览器查看监控&#10;指引文档介绍&#10;使用浏览器查看校区监控，需要满足以下要求：&#10;1.1、电脑系统：Win10以上版本；&#10;1.2、浏览器：Edge浏览器的Internet Explorer 模式&#10;Edge浏览器的设置步骤&#10;打开Edge浏览器，点击右上角的三个点，打开设置&#10;&#10;2、在搜索框输入：Explorer&#10;&#10;3、往下滑动找到‘允许在Internet Explorer模式下重新加载网站(IE模式)’选择允许&#10;&#10;4、右上角的三个点里面就会添加一个‘在Intermet Explorer模式下重新加载’&#10;&#10;5、在网页搜索框里面输入监控IP地址192.168.0.X（X范围一般为5~10）&#10;&#10;进入到登录界面后，先点击右上角三个点 选择在‘Intermet Explorer模式下重新加载’，再输入账号密码登录即可&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【监控-6】ivms-4200 Lite监控客户端设置&#10;添加校区监控&#10;&#10;设置 &#10;改成ntp.aliyun.com，防止IP变更（新装监控默认没设置）&#10;&#10;(有回放功能)普通用户1:  userxq  密码: 345110xq&#10;(无回放功能)普通用户2:  user  密码:  345110jk&#10;&#10;存储设置（默认）&#10;&#10;所有通道开启移动侦测，灵敏度4，布放打开（每个通道都要手动点一次）&#10;&#10;启动视频信号丢失功能，邮件联动（每个通道都要手动设置）&#10;&#10;异常报警，邮件联动&#10;设置移动侦测录像计划&#10;摄像头画面清晰度设置（不同型号的摄像头，可设置参数不一样，如出现有摄像头不能同时生效，需要再另外分批再设置一次）&#10;通过客户端给摄像头改名字&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【监控-2】监控系统客户端安装指引&#10;（一）客户端下载地址&#10;iVMS-4200客户端下载地址（复制到浏览器打开并下载）：https://partners.hikvision.com/tools/tooldetail?id=599912121330368512&#10;&#10;（二）客户端安装步骤&#10;右击ivms-4200海康软件，选择【以管理员身份运行】选项，选择【是】&#10;&#10;勾选【我接受许可证协议条款】，然后单击【下一步】按钮&#10;&#10;如下图：“请选择要安装的功能”只需要勾选【视频】，“目标文件夹”选择切换到非C盘安装，然后单击【安装】按钮&#10;&#10;（三）设置账号和密码&#10;设置监控用户名：user ，密码：345110jk密保问题可以统一档案是1&#10;&#10;添加录像机&#10;设备管理—设备&#10;&#10;(有回放功能)普通用户1:userxq密码:345110xq&#10;(无回放功能)普通用户2:user密码:345110jk &#10;&#10;（五）主预览和远程回放&#10;打开程序默认进入主预览界面，如下图所示&#10;&#10;远程回放操作&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【监控-7】监控客户端增删录像机操作指引&#10;添加录像机&#10;&#10;(有回放功能)普通用户1:userxq密码:345110xq&#10;(无回放功能)普通用户2:user密码:345110jk &#10;&#10;删除录像机&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）"/>
-        <filter val="【日常使用-12】C盘空间满了该如何清理&#10;方法一：&#10;win—&gt;磁盘清理&#10;&#10;方法二：&#10; 转移微信的个人数据文件&#10;  微信—&gt;设置—&gt;文件管理—&gt;文件管理（微信个人数据文件就在这个文件夹里）—&gt;更改 更改至 C盘 以外的盘符）&#10;   更改完成后C盘就会释放出很多的空间&#10;&#10;方法三：&#10;转移企微的个人数据文件&#10;企微—设置—存储管理&#10;&#10;方法四：&#10; win+r—%temp%  全选删除&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【一体机-7】教学一体机一键清理D盘文件指引&#10;在打开一体机的“此电脑”&#10;打开D盘&#10;在D盘下找到“清理D盘.bat”，双击运行清理工具&#10;&#10;清理工具运行中，请勿点击黑框，会停止运行&#10;&#10;清理结束标志“垃圾文件清理成功”，按任意键退出&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;启动提示错误：程序文件缺失 CefSharp&#10;&#10;一些需要注意的地方：&#10;如果第三步中有安全软件误报，请点击“允许”（正常情况下安全软件更新到最新是不会误报的）&#10;如果发现 C 盘空间已满，应该在第三步之前提前清理出一部分空间出来&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）"/>
-        <filter val="共享盘的处理方式&#10;、操作指南&#10;&#10;一、电脑标准：&#10;1、不可有共享快捷访问方式&#10;2、清除共享已存登录密码&#10;二、操作指南&#10;1、删除快捷访问方式&#10;2、删除共享密码&#10;&#10;3、删除共享快捷方式后，&#10;如何访问共享&#10;&#10;打开后，输入共享访问密码即可（再次访问后，不要钩先记住密码）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【共享-2】校区MAC系统共享文件夹连接指引&#10;指引文档介绍&#10;校区老师电脑&#10;访问共享文件夹的用户名和密码规则：&#10;业务对应的用户名:  成长-班辅（fdb ）  亲子-个辅（gf ）   志业（sgz）&#10;用户名：业务字母代表&#10;密码：zy+校区+业务缩写&#10;比如说鸟巢成长校区：用户名是fdb ，密码是zyncfdb&#10;（注意：成长（fdb ）  亲子（gf ）   志业（gz）的文件夹是有读写权限）&#10;校区的课室一体机&#10;课室共享文件夹ks（在一体机上使用）：&#10;用户名：ks&#10;密码：ks&#10;（注意：ks文件夹此时只有读的权限）&#10;&#10;映射共享网络磁盘&#10;2.1、访问共享文件夹&#10;(1) 在电脑的左上角，点击 【GO/前往】-【connect to server/连接服务器】，或者使用键盘快捷键【command+k】，&#10;&#10;输入校区共享盘地址 smb://192.168.0.26&#10;&#10;注：图中第2步 “+” 必需要操作&#10;输入账号密码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【共享-1】window系统共享文件夹连接指引&#10;指引文档介绍&#10;校区老师电脑&#10;访问共享文件夹的用户名和密码规则：&#10;业务对应的用户名:  成长-班辅（fdb ）  亲子-个辅（gf ）   志业（sgz）&#10;用户名：业务字母代表&#10;密码：zy+校区+业务缩写&#10;比如说鸟巢成长校区：用户名是fdb ，密码是zyncfdb&#10;（注意：成长（fdb ）  亲子（gf ）   志业（gz）的文件夹是有读写权限）&#10;校区的课室一体机&#10;课室共享文件夹ks（在一体机上使用）：&#10;用户名：ks&#10;密码：ks&#10;（注意：ks文件夹此时只有读的权限）&#10;&#10;映射共享网络磁盘&#10;2.1、访问共享文件夹&#10;（1）点击【我的电脑】或【此电脑】，点击左上角，输入校区共享IP地址 \\192.168.0.26，然后点击回车&#10;&#10;（2）见到共享文件夹，例如“ks”(课室共享) 、“班辅共享”或“个辅共享”，双击需要访问的共享文件夹，例如“班辅共享”，在弹出的安全验证窗口输入验证信息用户“fdb”、密码“zyqxlfdb”，并且勾选“记住我的凭据”（需按校区修改密码）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;window系统共享文件夹连接指引&#10;&#10;2.2、共享文件夹创建快捷方式放置桌面&#10;2.2.1、需要创建快捷方式的文件夹上，点击【右键】，选择【创建快捷方式】，该文件夹的快捷访问路径就在桌面可查&#10;&#10;无法正常连接共享盘&#10;背景：情况1：老师去其它校区教研或者教学，回到自己常驻校区发现共享盘连接不上&#10;      情况2：老师需要使用其它校区共享盘工作，连接不上共享盘&#10;3.1、删除Windows凭证，再进行重新连接&#10;按键盘 WIN( 田 ) + R , 运行框中输入‘control’-点击‘凭证管理器’&#10;&#10;点击‘window凭据’-点击‘192.168.0.26’-点击‘删除’&#10;&#10;删除后记得重启电脑，更新改动，重新连接共享文件夹&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;校区MAC系统共享文件夹连接指引&#10;输入完点连接就会自动弹出共享盘&#10;&#10;设置开机自动挂载共享盘：打开系统偏好设置，点选“用户和群组”&#10;&#10;在左侧列表中选择你的用户名，点选“登录项”标签&#10;将已经挂载的网络驱动器图标拖放到登录项列表中&#10;可选：点选“隐藏”框，这样系统启动和登录时挂载网络驱动器后，不会自动打开 Finder 窗口&#10;&#10;2.2共享文件夹创建快捷方式放置桌面&#10;需要创建快捷方式的文件夹上，点击【右键】，选择【创建快捷方式】，该文件夹的快捷访问路径就在桌面可查&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）"/>
-        <filter val="08卓越在线常见问题QA&#10;&#10;班主任可以在TMS 找到学员二维码发给家长，让家长用微信扫码绑定，再用此微信&#10;&#10;3、下载了Windows的exe安装包导致无法安装&#10;https://zxx.zy.com/download 指引家长下载安卓的apk 安装包或直接下载好发给&#10;家长&#10;&#10;4、华为设备安装失败&#10;（1）、打开设备的“设置”，找到并点击“安全和隐私”选项&#10;&#10;（2）、在安全和隐私界面找到并点击“更多安全设置”&#10;（3）、在选项中关闭“外部来源应用检查”&#10;（4）、再重新点击下载好的安装包安装即可&#10;5、其他情况无法安装&#10;（1）、https://zxx.zy.com/download 指引家长下载安卓的安装包或直接下载好安卓&#10;安装包然后发给家长&#10;（2）、安装应用宝，在应用宝上下搜索“卓越在线”下载载安装&#10;iOS 学生端&#10;1.下载AppStore 中的“卓越在线”提示需要支付&#10;使用该视频引导用户：&#10;https://jingyan.baidu.com/article/fdffd1f8f492f4b3e88ca154.html&#10;&#10;2.iOS端学生登录进入应用反复闪退&#10;1.记录学生的账号反馈给研发&#10;2.提示学生使用紧急备用链接上课&#10;&#10;3.学生登录后提示“学生信息异常，请联系客服进行处理”&#10;指引学生用登录的手机号微信关注“微服务”并绑定学员，在用同一微信登录“卓越&#10;在线&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;说明书-希沃白板[简称：EasiNote]2024&#10;单击下拉框，选择需要的分辨率，默认选择2592*1944&#10;3.4.1.9 返回白板&#10;点击返回白板按钮，返回希沃白板授课端&#10;&#10;3.4.2 反馈器&#10;3.4.2.1 安装&#10;选择应用软件安装程序，双击程序图标解压安装包在安装包解压完成后，&#10;&#10;将弹出如图3-4-2-1-1所示的软件准备安装界面&#10;&#10;点击“下一步”进入安装路径选择页面如图3-4-2-1-2&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;05卓越在线小班模式-教师端操作手册V2&#10;&#10;2 . &#10;下载地址：https://zxx.zy.com/mt/download &#10;下载时选择【Windows桌面端（小班）】&#10;&#10; 安装系统&#10;下载完成后，点击安装包进行安装，若系统弹出安全提示，点击【仍要运行】即可：&#10;&#10;Windows已保护你的电脑&#10;Windows Defender SmartScreen 已阻止启动一个未识别的应用&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;悦智学AI录入导学案操作文档&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【悦智学-2】悦智学备课操作指引&#10;1、在【日程】找到【待准备】的课程，点击【去准备】&#10;&#10;2、跳转到新界面后，点击右上角【去准备】&#10;&#10;3、跳转到【项目产品】界面，选择需要引用的导学案，点击【引用】&#10;&#10;4、跳转到导学案编辑页面，可以按需编辑导学案后或直接点击【推送】&#10;&#10;5、完成备课后，可选择对应的【课堂资料】-【预览】，进入详情页面，点击右上角【打印】即可；"/>
-        <filter val="新伙伴入职指引3&#10;&#10;方式: 企业邮箱/企业微信跳转;具体流程: 企业邮箱/企业微信“绩效与学习平台”自动发送学习通知，可直接跳转链接学习&#10;方式: 企业门户;具体流程: 网址及登录详看【一、办公设备指引】&#10;学习路径：企业门户→绩效人才系统→我的学习&#10;方式: 登录Italent系统;具体流程: 网址：https://www.italent.cn/Login&#10;账号：企业邮箱账号&#10;密码：通过忘记密码重新设置&#10;&#10;微信号【卓越教育企业文化】&#10;—卓越er都看卓越文化: 微博号【卓越教育】&#10;—来互动，关注卓越微博;微信号【卓越会员微服务】&#10;—卓越会员都在这里: 微信【卓二代小助手】&#10;—有娃的卓越人赶紧加入吧&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;绩效系统操作手册（员工）-2025目标管理篇&#10;绩效系统员工自助操作指南&#10;（员工版）&#10;—2025目标管理篇&#10;&#10;绩效计划制定&#10;登录系统&#10;绩效计划制定与审批&#10;&#10;目标修订&#10;目标管理与追踪&#10;&#10;登录系统&#10;登录企业门户&#10;推荐使用谷歌Chrome浏览器&#10;https://ssoin.zy.com/ogin&#10;登录企业门户：&#10;&#10;绩效计划制定&#10;登录系统&#10;绩效计划制定与审批&#10;&#10;目标修订&#10;目标管理与追踪&#10;&#10;绩效计划制定&#10;开始绩效计划制定&#10;首页中「我的待办」或者右上角的待办图标，&#10;&#10;绩效计划制定&#10;点击“去处理”后，即进入目标制定的界面，以下为界面示例&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;绩效系统操作手册（员工）-2025目标管理篇&#10;&#10;6分钟前&#10;&#10;绩效计划制定&#10;登录系统&#10;绩效计划制定与审批&#10;&#10;目标修订&#10;目标管理与追踪&#10;&#10;目标管理与追踪&#10;点击任务行的编辑按钮，可以修改任务具体信息，同时任务超期后，&#10;系统会每天在线提醒&#10;&#10;也可以进行任务分解，添加进展等&#10;&#10;目标管理与追踪&#10;点击对应目标的“沟通”，可在线协同，在沟通协作中填写沟通信息，上传附件等&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;绩效系统操作手册（经理）-绩效评估篇V3&#10;&#10;点击【我的待办】或者右上角的“小信封”图标，进入绩效待办事项&#10;&#10;直接上级评估&#10;进入待办列表页面，点击对应员工的姓名，可进入绩效详情页进行打分&#10;&#10;评估卓越教育2025年中非教绩效评估&#10;&#10;直接上级评估&#10;系统设置是与原绩效套表一致，评分对应绩效等级&#10;&#10;直接上级评估—工作成果评估&#10;进入评估页面后，对该员工的工作成果及关键绩效行为进行等级评定及填写评语（选填）&#10;&#10;在员工本人列可以看到员工自评的等级以及自我评语&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;新伙伴入职指引3&#10;&#10;卓越教育人力发展中心&#10;办公设施指引: 办公工具;办公设施指引: 账号;办公设施指引: 初始密码;办公设施指引: Tips&#10;办公设施指引: WiFi;办公设施指引: ZYJX;办公设施指引: AP4008809880..!!JX;办公设施指引: 全集团办公点、校区通用&#10;办公设施指引: 企业微信;办公设施指引: 手机号登录即可;办公设施指引: 无;办公设施指引: 登陆：https://qy.weixin.qq.com先下载PC端和手机客户端，首次可使用员工手机号验证码登录，登陆后可绑定个人微信，并进行实名认证，只有实名认证后，员工才能使用对外客户联系功能"/>
-        <filter val="安全助手(零信任）客户端FAQ&#10;参考下图：&#10;&#10;1.5、问题：打开零信任时提示连接控制器失败，如下图：&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;选择控制器切换124.71.208.207地址；&#10;&#10;b.如a步骤切换控制器地址依然不解决的情况下，可选择重置控制器再输入124.71.208.207参考下图：&#10;&#10;1.6、问题：启动零信任时提示JavaScript错误，无法正常启动，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.打开终端—sudo vi /etc/hosts文件下添加127.0.0.1 localhost&#10;&#10;1.7、问题：nslookup正常解析域名情况下，使用safari、火狐浏览器访问应用报403，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.更换Google浏览器，即可正常访问应用&#10;&#10;1.8、问题：启动零信任时无快捷登录方式，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;随机输入一个用户名，再返回上一级，选择快捷登录方式，参考下图：&#10;&#10;1.9、问题：退出零信任后发现外网基本上不了例如：www.baidu.com&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.需要把本机网络的DNS127.0.0.1去掉即可，参考下图：&#10;&#10;1.10、问题：为什么我登录不了TMS、EVIP……，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;请先安装零信任，并扫码登录—登录后不能退出零信任&#10;参考下图：&#10;&#10;1.11、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;去到安装目录C:\Program Files (x86)\TrustCyberLink目录下打开TrustCyberLink.exe&#10;1.12、问题：打开零信任没有企业微信按钮 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新打开或者点击控制切换器—点击124.71.208.207或者sec.zy.com-点击确认即可&#10;1.13、问题：安装助手完成时零信任未安装成功 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新安装即可&#10;1.14、问题：提示 “由于找不到 UAADataCenter.dl，无法继续执行代码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;安全助手（零信任）客户端FAQ&#10;操作问题&#10;问题：登录零信任后访问应用时浏览器页面提示403forbidden，如下图：&#10;&#10;设备类型：&#10;Windows/macbook&#10;解决方案：&#10;使用其他浏览器访问&#10;设置浏览器后重新打开进行访问应用&#10;（1）Google浏览器&#10;&#10;（2）火狐浏览器&#10;&#10;问题：登录零信任后当访问应用时提示无法访问此网站，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10; 先关闭浏览器，点击刷新 重新获取策略（刷新一次未解决可以继续点击刷新）参考下图：&#10;&#10; 当a步骤重新获取策略后还是一样提示无法访问此网站时可退出登录零信任，再退出零信任客户端，重新打开扫码登录可参考下图：&#10;&#10;问题：打开零信任扫码登陆时，提示不合法的状态，如下图&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;a.返回上一级，去掉用户名，选择快捷方式登陆参考下图：&#10;&#10;1.4、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;返回上一级，重新选择快捷方式登陆&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&quot;&#10;1.19、问题：扫码登陆时认证失败 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;重新进入扫码登陆界面即可&#10;1.20、问题：登录了零信任，但是访问不了内网 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;1、确认电脑上没有IOA，或者有没登录IOA（建议卸载了，后续不会用了，原来限制的域名换到了新的零信任）&#10;2、处理掉IOA后，再次扫码登录零信任（退IOA前扫码了的话，也需要退出再扫一次码）&#10;3、登录超时了，退出零信任，重新登录&#10;参考下图：&#10;1.21、问题：开机进入系统很慢，运行慢，杀毒软件不断弹窗 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项&#10;1.22、问题：登录了零信任，点击应用提示“请求失败”  如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;退出零信任，重新登录&#10;1.23、问题：兼职老师登录零信任，应用列表是空白 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;因为零信任同步企微账号，分配组有问题，没有分配到与企微一致的组织架构下，而且分到默认组（需要绿盟排查原因），需要零信任管理员人工更改分组&#10;1.24、问题：部分应用无法访问，如ssoin.zy.com &#10;设备类型：&#10;mac&#10;解决方案：&#10;ping ssoin.zy.com的ip是10.12.81.44，但是在浏览器访问页面，发现请求ip是外网IP，暂未有解决根源的办法，临时办法：本地host绑定为10.12.81.44&#10;设备兼容性问题&#10;2.1、 问题：打开零信任扫码登录后提示开启私网DNS失败，请稍后重试&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;最佳设置&#10;1.2控制器地址：124.71.208.207&#10;&#10;1.3零信任软件推荐设置【重要：减少零信任被误关闭】&#10;&#10;2、零信任软件常见问题：&#10;1、提示不合法的用户名【返回上一级，选择快捷方式登录】&#10;提示会话已经过期，请重新登陆【返回上一级，选择快捷方式登录】&#10;扫码登录提示认证失败【返回上一级，选择快捷方式登录】&#10;&#10;2、登陆零信任后提示无无法访问此网页【关闭浏览器，重新登陆零信任并刷新策略】&#10;&#10;3、打开零信任扫码登录后提示开启私网DNS失败，请稍后重试【联系IT帮助台获取最新版本安装包并覆盖安装】&#10;&#10;4、网络及系统问题&#10;4.1退出零信任后无法访问外网【清除本地dns 127.0.0.1设置或修改为自动获取】&#10;macbook：&#10;Windwos：&#10;&#10;4.2退出零信任后可以登陆企微和微信，无法打开网页【修改Internet代理】&#10;&#10;4.3软件冲突--IOA【网络异常，卸载IOA（已不再使用）并重启电脑】&#10;&#10;4.3开机进入桌面很慢，自动弹窗警告【卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项】&#10;&#10;5、用户权限相关&#10;5.1打开零信任无OA访问窗口，空白"/>
-        <filter val="【监控-5】监控客户端切换账号指引&#10;注意：这个登录软件的账号，并非监控回放的账号，一般为了方便才设置成用户名：user密码：345110jk/it&#10;&#10;打开监控客户端“iVMS-4200 3.13.0.5 客户端”，主菜单界面的右边设备管理&#10;&#10;选择需要更改的监控，点击“笔形状图标”&#10;&#10;修改账号和密码，切换到有回放功能的账号，才可以看回放&#10;&#10;(有回放功能)普通用户1:  userxq  密码: 345110xq&#10;(无回放功能)普通用户2:  user  密码:  345110jk&#10;最后显示“在线”表示连接成功&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【监控-1】Edge浏览器查看监控&#10;指引文档介绍&#10;使用浏览器查看校区监控，需要满足以下要求：&#10;1.1、电脑系统：Win10以上版本；&#10;1.2、浏览器：Edge浏览器的Internet Explorer 模式&#10;Edge浏览器的设置步骤&#10;打开Edge浏览器，点击右上角的三个点，打开设置&#10;&#10;2、在搜索框输入：Explorer&#10;&#10;3、往下滑动找到‘允许在Internet Explorer模式下重新加载网站(IE模式)’选择允许&#10;&#10;4、右上角的三个点里面就会添加一个‘在Intermet Explorer模式下重新加载’&#10;&#10;5、在网页搜索框里面输入监控IP地址192.168.0.X（X范围一般为5~10）&#10;&#10;进入到登录界面后，先点击右上角三个点 选择在‘Intermet Explorer模式下重新加载’，再输入账号密码登录即可&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;&#10;插图：（如有）&#10;&#10;问题：希沃管理后台账号注册&#10;答案：&#10;注册希沃魔方账号：https://campus.seewo.com/login?redirect_url=https://campus.seewo.com/#/&#10;修改姓名及昵称信息为：校区+名字&#10;登陆提交OA权限申请，登陆OA系统 &gt;搜索账户/权限申请 &gt;希沃集控系统，按图例填写信息&#10;插图：（如有）&#10;&#10;问题：Seafile客户端下载&#10;答案：&#10;Windows挂载盘客户端：https://seafile-downloads.oss-cn-shanghai.aliyuncs.com/seadrive-3.0.9.msi&#10;Mac挂载盘客户端：&#10;https://seafile-downloads.oss-cn-shanghai.aliyuncs.com/seadrive-3.0.9.pkg&#10;插图：（如有）&#10;&#10;问题：Wps Office下载&#10;答案：下载链接：https://package.mac.wpscdn.cn/mac_wps_pkg/wps_installer/1.0.4.004/WPS_Office_Installer.zip&#10;&#10;插图：（如有）&#10;&#10;问题：用Edge打开监控网页&#10;答案：&#10;1、到Edge设置功能开启IE模式（如果已开启略过此步骤）；&#10;&#10;2、操作步骤：&#10;输入监控的网址--切换IE模式（直接关闭弹出的询问框即可）--输入监控网站的登录信息即可&#10;&#10;插图：（如有）&#10;&#10;问题：如何解除办公电脑的冰点还原软件&#10;答案：&#10;1、可以通过按住Shift键同时鼠标左键双击右下角的小白熊头像，&#10;2、或者按快捷键Ctrl+Alt+Shift+F6将冰点还原解锁界面调出来了 &#10;&#10;解锁密码：ballsir或public&#10;&#10;4、红框位置是选择设置冻结或解冻功能；&#10;插图：（如有）&#10;&#10;问题：企业微信扫码登录零信任成功后，零信任不能正常使用&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【监控-6】ivms-4200 Lite监控客户端设置&#10;添加校区监控&#10;&#10;设置 &#10;改成ntp.aliyun.com，防止IP变更（新装监控默认没设置）&#10;&#10;(有回放功能)普通用户1:  userxq  密码: 345110xq&#10;(无回放功能)普通用户2:  user  密码:  345110jk&#10;&#10;存储设置（默认）&#10;&#10;所有通道开启移动侦测，灵敏度4，布放打开（每个通道都要手动点一次）&#10;&#10;启动视频信号丢失功能，邮件联动（每个通道都要手动设置）&#10;&#10;异常报警，邮件联动&#10;设置移动侦测录像计划&#10;摄像头画面清晰度设置（不同型号的摄像头，可设置参数不一样，如出现有摄像头不能同时生效，需要再另外分批再设置一次）&#10;通过客户端给摄像头改名字&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;部分系统网址帐号密码&#10;系统类型：教学线; 系统名：E研发; 网址：pm.zy.com; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：E学校; 网址：sc.zy.com; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：E教学; 网址：zxx.zy.com/jx/; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：E教研; 网址：https://zxx.zy.com/jyy/resourceCenter; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：E测评; 网址：https://zxx.zy.com/assess-test/#/accountmanagement/index; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：在线测; 网址：https://zxx.zy.com/unitest-admin/; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：卓越在线; 网址：zxx.zy.com/op; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：华途加密; 网址：https://121.37.10.216:9444/dsm/admin/common/main —工作表1&#10;系统类型：教学线; 系统名：物流管理; 网址：http://www.opees.cn/ZX/ZX-login.aspx —工作表1&#10;系统类型：教学线; 系统名：教师库管理系统; 网址：https://teacher.beststudy.com/b/login; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：营运线; 系统名：TMS; 网址：tms.zy.com; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：营运线; 系统名：SCRM; 网址：https://yy.zy.com/scrm/#/dashboard; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：其他; 系统名：classin; 网址：https://console.eeo.cn/saas/school/index.html#/fullPage/Index —工作表1"/>
-        <filter val="window系统共享文件夹连接指引&#10;&#10;2.2、共享文件夹创建快捷方式放置桌面&#10;2.2.1、需要创建快捷方式的文件夹上，点击【右键】，选择【创建快捷方式】，该文件夹的快捷访问路径就在桌面可查&#10;&#10;无法正常连接共享盘&#10;背景：情况1：老师去其它校区教研或者教学，回到自己常驻校区发现共享盘连接不上&#10;      情况2：老师需要使用其它校区共享盘工作，连接不上共享盘&#10;3.1、删除Windows凭证，再进行重新连接&#10;按键盘 WIN( 田 ) + R , 运行框中输入‘control’-点击‘凭证管理器’&#10;&#10;点击‘window凭据’-点击‘192.168.0.26’-点击‘删除’&#10;&#10;删除后记得重启电脑，更新改动，重新连接共享文件夹&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;（该群定期清理）&#10;插图：（如有）&#10;&#10;问题：新电脑故障，需要联系售后处理（维保内）&#10;答案：企微扫码进群，进群后@广州立诚捷安电子专注智能弱电工程 协助你处理保内故障（该群定期清理）&#10;插图：（如有）&#10;&#10;问题：Windows电脑校区电脑连接共享&#10;答案：打开任意文件夹，在地址栏输入\\192.168.0.26，在弹出对话框输入账户密码，勾选记住密码点击确认选择你要的文件夹右键发送快捷方式到桌面&#10;插图：（如有）&#10;&#10;问题：Mac电脑校区电脑连接共享&#10;答案：在Finder（访达）状态中 &gt;顶部菜单 &gt;前往 &gt;连接服务器，在弹出对话框选择注册用户后输入账户密码，勾选记住密码点击确认&#10;插图：（如有）&#10;&#10;问题：校区电脑连接共享提示多连接&#10;答案：注销或重启电脑&#10;插图：（如有）&#10;&#10;问题：打开企微的邮箱，提示“账号已被禁用，请联系企业管理员了解详情”&#10;答案：企微自带邮箱功能已禁用，请在企业微信搜索263企业邮箱，输入账户密码绑定&#10;插图：&#10;&#10;问题：各类系统账户及权限申请&#10;答案：登陆提交OA权限申请，登陆OA系统 &gt;搜索账户/权限申请 &gt;按需要选择系统及权限，如未能列明，请描述详细需求&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;校区MAC系统共享文件夹连接指引&#10;输入完点连接就会自动弹出共享盘&#10;&#10;设置开机自动挂载共享盘：打开系统偏好设置，点选“用户和群组”&#10;&#10;在左侧列表中选择你的用户名，点选“登录项”标签&#10;将已经挂载的网络驱动器图标拖放到登录项列表中&#10;可选：点选“隐藏”框，这样系统启动和登录时挂载网络驱动器后，不会自动打开 Finder 窗口&#10;&#10;2.2共享文件夹创建快捷方式放置桌面&#10;需要创建快捷方式的文件夹上，点击【右键】，选择【创建快捷方式】，该文件夹的快捷访问路径就在桌面可查&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;共享盘的处理方式&#10;、操作指南&#10;&#10;一、电脑标准：&#10;1、不可有共享快捷访问方式&#10;2、清除共享已存登录密码&#10;二、操作指南&#10;1、删除快捷访问方式&#10;2、删除共享密码&#10;&#10;3、删除共享快捷方式后，&#10;如何访问共享&#10;&#10;打开后，输入共享访问密码即可（再次访问后，不要钩先记住密码）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【共享-2】校区MAC系统共享文件夹连接指引&#10;指引文档介绍&#10;校区老师电脑&#10;访问共享文件夹的用户名和密码规则：&#10;业务对应的用户名:  成长-班辅（fdb ）  亲子-个辅（gf ）   志业（sgz）&#10;用户名：业务字母代表&#10;密码：zy+校区+业务缩写&#10;比如说鸟巢成长校区：用户名是fdb ，密码是zyncfdb&#10;（注意：成长（fdb ）  亲子（gf ）   志业（gz）的文件夹是有读写权限）&#10;校区的课室一体机&#10;课室共享文件夹ks（在一体机上使用）：&#10;用户名：ks&#10;密码：ks&#10;（注意：ks文件夹此时只有读的权限）&#10;&#10;映射共享网络磁盘&#10;2.1、访问共享文件夹&#10;(1) 在电脑的左上角，点击 【GO/前往】-【connect to server/连接服务器】，或者使用键盘快捷键【command+k】，&#10;&#10;输入校区共享盘地址 smb://192.168.0.26&#10;&#10;注：图中第2步 “+” 必需要操作&#10;输入账号密码"/>
-        <filter val="【共享-1】window系统共享文件夹连接指引&#10;指引文档介绍&#10;校区老师电脑&#10;访问共享文件夹的用户名和密码规则：&#10;业务对应的用户名:  成长-班辅（fdb ）  亲子-个辅（gf ）   志业（sgz）&#10;用户名：业务字母代表&#10;密码：zy+校区+业务缩写&#10;比如说鸟巢成长校区：用户名是fdb ，密码是zyncfdb&#10;（注意：成长（fdb ）  亲子（gf ）   志业（gz）的文件夹是有读写权限）&#10;校区的课室一体机&#10;课室共享文件夹ks（在一体机上使用）：&#10;用户名：ks&#10;密码：ks&#10;（注意：ks文件夹此时只有读的权限）&#10;&#10;映射共享网络磁盘&#10;2.1、访问共享文件夹&#10;（1）点击【我的电脑】或【此电脑】，点击左上角，输入校区共享IP地址 \\192.168.0.26，然后点击回车&#10;&#10;（2）见到共享文件夹，例如“ks”(课室共享) 、“班辅共享”或“个辅共享”，双击需要访问的共享文件夹，例如“班辅共享”，在弹出的安全验证窗口输入验证信息用户“fdb”、密码“zyqxlfdb”，并且勾选“记住我的凭据”（需按校区修改密码）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【共享-2】校区MAC系统共享文件夹连接指引&#10;指引文档介绍&#10;校区老师电脑&#10;访问共享文件夹的用户名和密码规则：&#10;业务对应的用户名:  成长-班辅（fdb ）  亲子-个辅（gf ）   志业（sgz）&#10;用户名：业务字母代表&#10;密码：zy+校区+业务缩写&#10;比如说鸟巢成长校区：用户名是fdb ，密码是zyncfdb&#10;（注意：成长（fdb ）  亲子（gf ）   志业（gz）的文件夹是有读写权限）&#10;校区的课室一体机&#10;课室共享文件夹ks（在一体机上使用）：&#10;用户名：ks&#10;密码：ks&#10;（注意：ks文件夹此时只有读的权限）&#10;&#10;映射共享网络磁盘&#10;2.1、访问共享文件夹&#10;(1) 在电脑的左上角，点击 【GO/前往】-【connect to server/连接服务器】，或者使用键盘快捷键【command+k】，&#10;&#10;输入校区共享盘地址 smb://192.168.0.26&#10;&#10;注：图中第2步 “+” 必需要操作&#10;输入账号密码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;window系统共享文件夹连接指引&#10;&#10;2.2、共享文件夹创建快捷方式放置桌面&#10;2.2.1、需要创建快捷方式的文件夹上，点击【右键】，选择【创建快捷方式】，该文件夹的快捷访问路径就在桌面可查&#10;&#10;无法正常连接共享盘&#10;背景：情况1：老师去其它校区教研或者教学，回到自己常驻校区发现共享盘连接不上&#10;      情况2：老师需要使用其它校区共享盘工作，连接不上共享盘&#10;3.1、删除Windows凭证，再进行重新连接&#10;按键盘 WIN( 田 ) + R , 运行框中输入‘control’-点击‘凭证管理器’&#10;&#10;点击‘window凭据’-点击‘192.168.0.26’-点击‘删除’&#10;&#10;删除后记得重启电脑，更新改动，重新连接共享文件夹&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;校区MAC系统共享文件夹连接指引&#10;输入完点连接就会自动弹出共享盘&#10;&#10;设置开机自动挂载共享盘：打开系统偏好设置，点选“用户和群组”&#10;&#10;在左侧列表中选择你的用户名，点选“登录项”标签&#10;将已经挂载的网络驱动器图标拖放到登录项列表中&#10;可选：点选“隐藏”框，这样系统启动和登录时挂载网络驱动器后，不会自动打开 Finder 窗口&#10;&#10;2.2共享文件夹创建快捷方式放置桌面&#10;需要创建快捷方式的文件夹上，点击【右键】，选择【创建快捷方式】，该文件夹的快捷访问路径就在桌面可查&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【日常使用-19】seafile使用指引&#10;seaflie安装&#10;seafile下载地址：https://www.seafile.com/download/&#10;seafile 桌面客户端下载&#10;&#10;默认安装即可&#10;&#10;选择资料下载路径，不要选择C盘，尽量选择大内存的盘&#10;注意：共享盘下载的东西都会存在此文件夹&#10;&#10;点击选择添加资料保存路径，方便查找&#10;&#10;新建一个文件夹存放资料&#10;&#10;起一个容易记的名字，存放资料&#10;&#10;选定文件夹后，点击“选择文件夹”&#10;&#10;点击下一步&#10;&#10;登录seafile&#10;注意：填写部门云盘网站、输入邮箱，密码是OA密码&#10;&#10;云盘成功登录后的界面 &#10;&#10;假如此为资料库，在此文件夹内新建文件会同步到云盘&#10;&#10;选择当前“同步文件夹”资源库&#10;&#10;右键将文件同步选择到磁盘容量大的磁盘&#10;&#10;默认即可&#10;&#10;在“资料库”添加一个“测试.docx”文件&#10;&#10;文件有绿色的”✔“就是代表已上传的资料库&#10;&#10;如果不想同步，在屏幕右下角任务栏找到seafile图标右键“关闭自动同步”同步则开启&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单"/>
-        <filter val="安全助手(零信任）客户端FAQ&#10;参考下图：&#10;&#10;1.5、问题：打开零信任时提示连接控制器失败，如下图：&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;选择控制器切换124.71.208.207地址；&#10;&#10;b.如a步骤切换控制器地址依然不解决的情况下，可选择重置控制器再输入124.71.208.207参考下图：&#10;&#10;1.6、问题：启动零信任时提示JavaScript错误，无法正常启动，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.打开终端—sudo vi /etc/hosts文件下添加127.0.0.1 localhost&#10;&#10;1.7、问题：nslookup正常解析域名情况下，使用safari、火狐浏览器访问应用报403，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.更换Google浏览器，即可正常访问应用&#10;&#10;1.8、问题：启动零信任时无快捷登录方式，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;随机输入一个用户名，再返回上一级，选择快捷登录方式，参考下图：&#10;&#10;1.9、问题：退出零信任后发现外网基本上不了例如：www.baidu.com&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;（2）双击点卸载&#10;&#10;（3）输入安全助手卸载码（e2vPsv8$）后，运行卸载&#10;&#10;4、零信任安装指引&#10;（1）双击点击安装包打开------&gt;点“是” ，如下图&#10;&#10;（2）点—&gt;我同意，如下图&#10;&#10;（3）选择安装位置（可自定义选择安装位置）默认即可，点击—&gt;安装，如下图&#10;&#10;（4）等待安装完成即可，如下图&#10;&#10;（5）安装完成默认勾选运行零信任，桌面可看到零信任图标，如下图&#10;&#10;(6)打开零信任扫码登录，即可通过浏览器访问内部系统，如下图&#10;&#10;(7)如果第一次安装提示需要输入控制器地址，请输入sec.zy.com或124.71.208.207，点击确认后扫码登录使用&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;最佳设置&#10;1.2控制器地址：124.71.208.207&#10;&#10;1.3零信任软件推荐设置【重要：减少零信任被误关闭】&#10;&#10;2、零信任软件常见问题：&#10;1、提示不合法的用户名【返回上一级，选择快捷方式登录】&#10;提示会话已经过期，请重新登陆【返回上一级，选择快捷方式登录】&#10;扫码登录提示认证失败【返回上一级，选择快捷方式登录】&#10;&#10;2、登陆零信任后提示无无法访问此网页【关闭浏览器，重新登陆零信任并刷新策略】&#10;&#10;3、打开零信任扫码登录后提示开启私网DNS失败，请稍后重试【联系IT帮助台获取最新版本安装包并覆盖安装】&#10;&#10;4、网络及系统问题&#10;4.1退出零信任后无法访问外网【清除本地dns 127.0.0.1设置或修改为自动获取】&#10;macbook：&#10;Windwos：&#10;&#10;4.2退出零信任后可以登陆企微和微信，无法打开网页【修改Internet代理】&#10;&#10;4.3软件冲突--IOA【网络异常，卸载IOA（已不再使用）并重启电脑】&#10;&#10;4.3开机进入桌面很慢，自动弹窗警告【卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项】&#10;&#10;5、用户权限相关&#10;5.1打开零信任无OA访问窗口，空白&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;零信任配置指引&#10;下载安装包&#10;Windows系统版本&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe&#10;&#10;Macbook版本&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250715/TrustCyberLink_PC_Setup_2.207.122.dmg&#10;&#10;2、安装完成后：&#10;控制器地址:124.71.208.207&#10;&#10;3、企业微信扫码登录后即可访问应用&#10;&#10;4、进来界面后单击设置按钮-勾选开机自动运行-勾选最小化到托盘或勾选退出TrustCyberLink&#10;&#10;5、退出登陆&#10;企业微信扫码登录后，在不使用零信任时可选择退出登录&#10;&#10;扫码登陆时认证失败&#10;重新进入扫码登陆界面即可&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【零信任-4】mac零信任卸载手册&#10;卸载前确保零信任没有打开，否则无法卸载；&#10;&#10;退出零信任&#10;&#10;2.在电脑上面的菜单栏，找到前往，进入用用程序&#10;&#10;3.找到零信任，右键，移到废纸&#10;4.卸载完后，找到网络设置，找到DNS，如果有127.0.0.1，则删除保存，如果没有这一步可不管&#10;&#10;5.回到桌面，扎到菜单栏的实用工具&#10;&#10;找到终端&#10;&#10;6.在终端界面分别输入下面的命令&#10;过程将提示输入密码密码不会显示，直接输入后回车即可若密码不对，会提示错误重新输入"/>
-        <filter val="263邮箱Q&amp;A&#10;问题：263企业邮箱修改密码&#10;答案：自助修改密码路径：企业微信 &gt; 工作台 &gt; IT服务台 &gt; 更多功能 &gt;邮箱密码重置&#10;插图：&#10;&#10;问题：263企业邮箱修改密码（已绑定手机）&#10;答案：打开网址https://mm.263.com/wm2e/website/jsp/resetPassword.jsp&#10;插图：&#10;&#10;问题：263企业邮箱网页登陆地址&#10;答案：登陆网址https://www.263.net&#10;插图：&#10;&#10;问题：263企业邮箱修改密码规则&#10;答案：密码需要包含大小写、数字、符号，长度不小于8位，不能使用连续的字符，不能使用简单密码&#10;插图：&#10;&#10;问题：263企业邮箱客户端服务器地址&#10;答案：建议使用IMAP+SMTP组合，详情见附图&#10;插图：&#10;&#10;问题：如何在苹果mail邮件客户端中设置IMAP收发邮件&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱使用指引&#10;如下图：&#10;&#10;2.2 捆绑263邮箱的旧手机号码已注销或不能收取短信验证码，需要在OA系统上发起账户/权限申请】流程进行捆绑手机号码的变更，按以下步骤操作：&#10;2.2.1登录OA系统，点击【发起流程】-【IT类】-【IT服务】-【账户/权限申请】，“系统”选择“263企业邮箱 ”，“描述”写清楚你的需求&#10;&#10;忘记263邮箱密码/修改263邮箱密码&#10;登录企业微信-【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】，如下图：&#10;&#10;企业微信绑定263邮箱进行使用&#10;登录企业微信-【工作台】-【263企业邮箱】，输入邮箱和密码就可以完成绑定&#10;重置邮箱密码之后也需要重新捆绑企业微信才可以正常使用&#10;&#10;登录263邮箱时候提示：用户邮箱状态异常&#10;需要先登录企业微信-【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】进行密码重置，然后再进行微信绑定&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【邮箱-4】重置邮箱密码&#10;重置密码：企业微信，点击【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【邮箱-12】263邮箱设置--Macbook 邮件篇&#10;【修改263邮箱登陆密码】&#10;&#10;【忘记邮箱密码重置办法】&#10;重置密码：企业微信，点击【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】&#10;&#10;【Macbook 邮件更新密码步骤】&#10;&#10;【Macbook 邮件客户端配置263邮箱步骤】&#10;&#10;按图补充1~3点信息&#10;&#10;设置完成，测试邮件收发&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【邮箱-10】263邮箱设置--Outlook篇&#10;【修改263邮箱登陆密码】&#10;&#10;【忘记邮箱密码重置办法】&#10;打开企业微信搜索【IT服务台】，更多功能→重置邮箱密码，按页面步骤进行密码修改&#10;&#10;【Outlook更新密码】&#10;&#10;【Outlook 邮件客户端配置263邮箱步骤】&#10;&#10;设置完成，测试邮件收发&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）"/>
-        <filter val="【日常使用-12】C盘空间满了该如何清理&#10;方法一：&#10;win—&gt;磁盘清理&#10;&#10;方法二：&#10; 转移微信的个人数据文件&#10;  微信—&gt;设置—&gt;文件管理—&gt;文件管理（微信个人数据文件就在这个文件夹里）—&gt;更改 更改至 C盘 以外的盘符）&#10;   更改完成后C盘就会释放出很多的空间&#10;&#10;方法三：&#10;转移企微的个人数据文件&#10;企微—设置—存储管理&#10;&#10;方法四：&#10; win+r—%temp%  全选删除&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;启动提示错误：程序文件缺失 CefSharp&#10;&#10;一些需要注意的地方：&#10;如果第三步中有安全软件误报，请点击“允许”（正常情况下安全软件更新到最新是不会误报的）&#10;如果发现 C 盘空间已满，应该在第三步之前提前清理出一部分空间出来&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【一体机-7】教学一体机一键清理D盘文件指引&#10;在打开一体机的“此电脑”&#10;打开D盘&#10;在D盘下找到“清理D盘.bat”，双击运行清理工具&#10;&#10;清理工具运行中，请勿点击黑框，会停止运行&#10;&#10;清理结束标志“垃圾文件清理成功”，按任意键退出&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;迎检前台（班辅或者班辅个辅混合的前台）及里程范围内办公室电脑处理方式&#10;迎检前台（班辅或者班辅个辅混合的前台）&#10;及里程范围内办公室电脑处理方式&#10;一、电脑标准：&#10;1. 校区电脑必须&quot;干净&quot;，所有工作相关软件及档案资料必须最大程度清理或转移—&#10;可放共享盘&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;非里程范围内的电脑迎检方式&#10;&#10;校区电脑数量及要求：&#10;1. 前台最好只有1 台，超过2 台的电脑必须从前台收走回避；&#10;2. 办公室里的办公电脑也需要按要求配置，不能出现&quot;卓越&quot;&quot;zy&quot;；&#10;二、操作指南&#10;电脑数据处理&#10;1、清理数据&#10;在应检账号下删除清理桌面企业微信等其它工作图标，以及工作资料（转移到移动硬盘&#10;或共享盘）：检查清理磁盘无工作相关内容（例如：花名册、报名记录、共享文件夹链&#10;接（直接删除链接）、课件、数据分析文件、Excel 统计表格等；主要位置：浏览器下载&#10;保留企微或微信微信记录（可以使用企微，但必须隐蔽使用，不要自动运行/自动登录；&#10;&#10;目录、文档目录，各硬盘分区下的工作目录等）"/>
-        <filter val="【日常使用-12】C盘空间满了该如何清理&#10;方法一：&#10;win—&gt;磁盘清理&#10;&#10;方法二：&#10; 转移微信的个人数据文件&#10;  微信—&gt;设置—&gt;文件管理—&gt;文件管理（微信个人数据文件就在这个文件夹里）—&gt;更改 更改至 C盘 以外的盘符）&#10;   更改完成后C盘就会释放出很多的空间&#10;&#10;方法三：&#10;转移企微的个人数据文件&#10;企微—设置—存储管理&#10;&#10;方法四：&#10; win+r—%temp%  全选删除&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【一体机-7】教学一体机一键清理D盘文件指引&#10;在打开一体机的“此电脑”&#10;打开D盘&#10;在D盘下找到“清理D盘.bat”，双击运行清理工具&#10;&#10;清理工具运行中，请勿点击黑框，会停止运行&#10;&#10;清理结束标志“垃圾文件清理成功”，按任意键退出&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;启动提示错误：程序文件缺失 CefSharp&#10;&#10;一些需要注意的地方：&#10;如果第三步中有安全软件误报，请点击“允许”（正常情况下安全软件更新到最新是不会误报的）&#10;如果发现 C 盘空间已满，应该在第三步之前提前清理出一部分空间出来&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【日常使用—1】微信文件空间释放&#10;1.登录微信后点击左下角按钮，如下图所示，再点击设置&#10;&#10;2.打开后点击文件管理，打开文件夹&#10;&#10;3.再打开FileStorage&#10;&#10;4.打开图中相应的文件夹进行按月份删除处理，具体说明如下：&#10;&#10;Cache：文件夹是存储的缓存文件，里面自动按月份建的文件夹，虽然占用空间也不大，可以按月份选择性删除，也可以全部删除；&#10;Files：文件夹里是微信存储的文件，word、excel、pdf、压缩文件等等里面也是自动按照月份建的文件夹，你可以按照月份来选择性删除，为安全也可以打开文件来确认后删除；&#10;Image：里面自动保存了微信聊天记录中的表情图片、微信下载的表情包、收藏的表情图片等，这些图片不能直接打开是因为经过了加密处理，以防泄露个人信息&#10;Video：文件夹里是你存储的视频文件，包括视频和封面文件这个占用空间是比较大的，为安全也可以打开文件来确认后删除&#10;注：删除文件需谨慎考虑，删除后就无法恢复&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）"/>
-        <filter val="安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;（2）双击点卸载&#10;&#10;（3）输入安全助手卸载码（e2vPsv8$）后，运行卸载&#10;&#10;4、零信任安装指引&#10;（1）双击点击安装包打开------&gt;点“是” ，如下图&#10;&#10;（2）点—&gt;我同意，如下图&#10;&#10;（3）选择安装位置（可自定义选择安装位置）默认即可，点击—&gt;安装，如下图&#10;&#10;（4）等待安装完成即可，如下图&#10;&#10;（5）安装完成默认勾选运行零信任，桌面可看到零信任图标，如下图&#10;&#10;(6)打开零信任扫码登录，即可通过浏览器访问内部系统，如下图&#10;&#10;(7)如果第一次安装提示需要输入控制器地址，请输入sec.zy.com或124.71.208.207，点击确认后扫码登录使用&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;安全助手卸载和零信任工具安装指引&#10;&#10;注明：先卸载安全助手，后安装零信任工具，如果没有安全助手，可覆盖安装零信任工具&#10;&#10;1、零信任工具下载链接：&#10;Windows版本：&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe  （新版本下载链接）  &#10;&#10;2、管理员口令和安全助手卸载码都是e2vPsv8$&#10;&#10;3、安全助手卸载指引&#10;3.1、第一种卸载方式&#10;（1） 右键安全助手图标，点击进入特权模式，输入管理员口令（e2vPsv8$)即可进入特权模式&#10;&#10;（2）进入特权模式后，在本地电脑C:\Windows\LVUAAgentInstBaseRoot找到此文件运行卸载 &#10;&#10;输入安全助手卸载码（卸载密码默认 e2vPsv8$）&#10;&#10;3.2、第二种卸载方式&#10;（1）若是Win10 系统点击左下角，找到并打开文件夹“UniAccess安全助手”，右键点击“启动或显示托盘图标 ”，点击更多，点击打开文件位置&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;&#10;答案：&gt;零信任sdp_engine进程损坏，下载sdp_engine.exe文件，并替换sdp_engine.exe文件，重新打开零信任扫码登录&#10;下载地址：https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/sdp_engine.exe&#10;插图：（如有）&#10;找到下载文件sdp_engine.exe，复制这个文件拷贝到零信任安装目录替换文件sdp_engine.exe，比如C:\Program Files (x86)\TrustCyberLink\resources\app\engine&#10;&#10;问题：MacBook电脑安装完零信任打开需要输入密码进行提权，密码提示不对问题&#10;答案：&gt;由于mac未设置足够权限给SDP客户端导致，需要添加零信任权限&#10;路径：设置-隐私与安全性-添加零信任程序开启SDP相关的权限即可&#10;插图：（如有）&#10;&#10;如解决方法一仍然提示密码错误，检查密码是否有字符串，有的话把字符串修改后再重新打开，输入密码进行提取&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;最佳设置&#10;1.2控制器地址：124.71.208.207&#10;&#10;1.3零信任软件推荐设置【重要：减少零信任被误关闭】&#10;&#10;2、零信任软件常见问题：&#10;1、提示不合法的用户名【返回上一级，选择快捷方式登录】&#10;提示会话已经过期，请重新登陆【返回上一级，选择快捷方式登录】&#10;扫码登录提示认证失败【返回上一级，选择快捷方式登录】&#10;&#10;2、登陆零信任后提示无无法访问此网页【关闭浏览器，重新登陆零信任并刷新策略】&#10;&#10;3、打开零信任扫码登录后提示开启私网DNS失败，请稍后重试【联系IT帮助台获取最新版本安装包并覆盖安装】&#10;&#10;4、网络及系统问题&#10;4.1退出零信任后无法访问外网【清除本地dns 127.0.0.1设置或修改为自动获取】&#10;macbook：&#10;Windwos：&#10;&#10;4.2退出零信任后可以登陆企微和微信，无法打开网页【修改Internet代理】&#10;&#10;4.3软件冲突--IOA【网络异常，卸载IOA（已不再使用）并重启电脑】&#10;&#10;4.3开机进入桌面很慢，自动弹窗警告【卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项】&#10;&#10;5、用户权限相关&#10;5.1打开零信任无OA访问窗口，空白&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.需要把本机网络的DNS127.0.0.1去掉即可，参考下图：&#10;&#10;1.10、问题：为什么我登录不了TMS、EVIP……，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;请先安装零信任，并扫码登录—登录后不能退出零信任&#10;参考下图：&#10;&#10;1.11、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;去到安装目录C:\Program Files (x86)\TrustCyberLink目录下打开TrustCyberLink.exe&#10;1.12、问题：打开零信任没有企业微信按钮 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新打开或者点击控制切换器—点击124.71.208.207或者sec.zy.com-点击确认即可&#10;1.13、问题：安装助手完成时零信任未安装成功 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新安装即可&#10;1.14、问题：提示 “由于找不到 UAADataCenter.dl，无法继续执行代码"/>
-        <filter val="安全助手(零信任）客户端FAQ&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.需要把本机网络的DNS127.0.0.1去掉即可，参考下图：&#10;&#10;1.10、问题：为什么我登录不了TMS、EVIP……，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;请先安装零信任，并扫码登录—登录后不能退出零信任&#10;参考下图：&#10;&#10;1.11、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;去到安装目录C:\Program Files (x86)\TrustCyberLink目录下打开TrustCyberLink.exe&#10;1.12、问题：打开零信任没有企业微信按钮 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新打开或者点击控制切换器—点击124.71.208.207或者sec.zy.com-点击确认即可&#10;1.13、问题：安装助手完成时零信任未安装成功 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新安装即可&#10;1.14、问题：提示 “由于找不到 UAADataCenter.dl，无法继续执行代码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【零信任-4】mac零信任卸载手册&#10;卸载前确保零信任没有打开，否则无法卸载；&#10;&#10;退出零信任&#10;&#10;2.在电脑上面的菜单栏，找到前往，进入用用程序&#10;&#10;3.找到零信任，右键，移到废纸&#10;4.卸载完后，找到网络设置，找到DNS，如果有127.0.0.1，则删除保存，如果没有这一步可不管&#10;&#10;5.回到桌面，扎到菜单栏的实用工具&#10;&#10;找到终端&#10;&#10;6.在终端界面分别输入下面的命令&#10;过程将提示输入密码密码不会显示，直接输入后回车即可若密码不对，会提示错误重新输入&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;（2）双击点卸载&#10;&#10;（3）输入安全助手卸载码（e2vPsv8$）后，运行卸载&#10;&#10;4、零信任安装指引&#10;（1）双击点击安装包打开------&gt;点“是” ，如下图&#10;&#10;（2）点—&gt;我同意，如下图&#10;&#10;（3）选择安装位置（可自定义选择安装位置）默认即可，点击—&gt;安装，如下图&#10;&#10;（4）等待安装完成即可，如下图&#10;&#10;（5）安装完成默认勾选运行零信任，桌面可看到零信任图标，如下图&#10;&#10;(6)打开零信任扫码登录，即可通过浏览器访问内部系统，如下图&#10;&#10;(7)如果第一次安装提示需要输入控制器地址，请输入sec.zy.com或124.71.208.207，点击确认后扫码登录使用&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;1、下载和安装：&#10;Windows版本：下载链接https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe&#10;MAC版本：下载链接&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.120.dmg&#10;如需更最新版本，请企业微信联系IT帮助台获取&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;&#10;答案：&gt;零信任sdp_engine进程损坏，下载sdp_engine.exe文件，并替换sdp_engine.exe文件，重新打开零信任扫码登录&#10;下载地址：https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/sdp_engine.exe&#10;插图：（如有）&#10;找到下载文件sdp_engine.exe，复制这个文件拷贝到零信任安装目录替换文件sdp_engine.exe，比如C:\Program Files (x86)\TrustCyberLink\resources\app\engine&#10;&#10;问题：MacBook电脑安装完零信任打开需要输入密码进行提权，密码提示不对问题&#10;答案：&gt;由于mac未设置足够权限给SDP客户端导致，需要添加零信任权限&#10;路径：设置-隐私与安全性-添加零信任程序开启SDP相关的权限即可&#10;插图：（如有）&#10;&#10;如解决方法一仍然提示密码错误，检查密码是否有字符串，有的话把字符串修改后再重新打开，输入密码进行提取"/>
-        <filter val="【日常使用-19】seafile使用指引&#10;seaflie安装&#10;seafile下载地址：https://www.seafile.com/download/&#10;seafile 桌面客户端下载&#10;&#10;默认安装即可&#10;&#10;选择资料下载路径，不要选择C盘，尽量选择大内存的盘&#10;注意：共享盘下载的东西都会存在此文件夹&#10;&#10;点击选择添加资料保存路径，方便查找&#10;&#10;新建一个文件夹存放资料&#10;&#10;起一个容易记的名字，存放资料&#10;&#10;选定文件夹后，点击“选择文件夹”&#10;&#10;点击下一步&#10;&#10;登录seafile&#10;注意：填写部门云盘网站、输入邮箱，密码是OA密码&#10;&#10;云盘成功登录后的界面 &#10;&#10;假如此为资料库，在此文件夹内新建文件会同步到云盘&#10;&#10;选择当前“同步文件夹”资源库&#10;&#10;右键将文件同步选择到磁盘容量大的磁盘&#10;&#10;默认即可&#10;&#10;在“资料库”添加一个“测试.docx”文件&#10;&#10;文件有绿色的”✔“就是代表已上传的资料库&#10;&#10;如果不想同步，在屏幕右下角任务栏找到seafile图标右键“关闭自动同步”同步则开启&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;seafile使用指引&#10;（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;&#10;插图：（如有）&#10;&#10;问题：希沃管理后台账号注册&#10;答案：&#10;注册希沃魔方账号：https://campus.seewo.com/login?redirect_url=https://campus.seewo.com/#/&#10;修改姓名及昵称信息为：校区+名字&#10;登陆提交OA权限申请，登陆OA系统 &gt;搜索账户/权限申请 &gt;希沃集控系统，按图例填写信息&#10;插图：（如有）&#10;&#10;问题：Seafile客户端下载&#10;答案：&#10;Windows挂载盘客户端：https://seafile-downloads.oss-cn-shanghai.aliyuncs.com/seadrive-3.0.9.msi&#10;Mac挂载盘客户端：&#10;https://seafile-downloads.oss-cn-shanghai.aliyuncs.com/seadrive-3.0.9.pkg&#10;插图：（如有）&#10;&#10;问题：Wps Office下载&#10;答案：下载链接：https://package.mac.wpscdn.cn/mac_wps_pkg/wps_installer/1.0.4.004/WPS_Office_Installer.zip&#10;&#10;插图：（如有）&#10;&#10;问题：用Edge打开监控网页&#10;答案：&#10;1、到Edge设置功能开启IE模式（如果已开启略过此步骤）；&#10;&#10;2、操作步骤：&#10;输入监控的网址--切换IE模式（直接关闭弹出的询问框即可）--输入监控网站的登录信息即可&#10;&#10;插图：（如有）&#10;&#10;问题：如何解除办公电脑的冰点还原软件&#10;答案：&#10;1、可以通过按住Shift键同时鼠标左键双击右下角的小白熊头像，&#10;2、或者按快捷键Ctrl+Alt+Shift+F6将冰点还原解锁界面调出来了 &#10;&#10;解锁密码：ballsir或public&#10;&#10;4、红框位置是选择设置冻结或解冻功能；&#10;插图：（如有）&#10;&#10;问题：企业微信扫码登录零信任成功后，零信任不能正常使用"/>
-        <filter val="windows零信任卸载手册&#10;【零信任-3】windows零信任卸载&#10;打开控制面板&#10;win+R&gt;输入control&#10;&#10;点击卸载程序&#10;&#10;双击卸载&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【零信任-4】mac零信任卸载手册&#10;卸载前确保零信任没有打开，否则无法卸载；&#10;&#10;退出零信任&#10;&#10;2.在电脑上面的菜单栏，找到前往，进入用用程序&#10;&#10;3.找到零信任，右键，移到废纸&#10;4.卸载完后，找到网络设置，找到DNS，如果有127.0.0.1，则删除保存，如果没有这一步可不管&#10;&#10;5.回到桌面，扎到菜单栏的实用工具&#10;&#10;找到终端&#10;&#10;6.在终端界面分别输入下面的命令&#10;过程将提示输入密码密码不会显示，直接输入后回车即可若密码不对，会提示错误重新输入&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;安全助手卸载和零信任工具安装指引&#10;&#10;注明：先卸载安全助手，后安装零信任工具，如果没有安全助手，可覆盖安装零信任工具&#10;&#10;1、零信任工具下载链接：&#10;Windows版本：&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe  （新版本下载链接）  &#10;&#10;2、管理员口令和安全助手卸载码都是e2vPsv8$&#10;&#10;3、安全助手卸载指引&#10;3.1、第一种卸载方式&#10;（1） 右键安全助手图标，点击进入特权模式，输入管理员口令（e2vPsv8$)即可进入特权模式&#10;&#10;（2）进入特权模式后，在本地电脑C:\Windows\LVUAAgentInstBaseRoot找到此文件运行卸载 &#10;&#10;输入安全助手卸载码（卸载密码默认 e2vPsv8$）&#10;&#10;3.2、第二种卸载方式&#10;（1）若是Win10 系统点击左下角，找到并打开文件夹“UniAccess安全助手”，右键点击“启动或显示托盘图标 ”，点击更多，点击打开文件位置&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;（2）双击点卸载&#10;&#10;（3）输入安全助手卸载码（e2vPsv8$）后，运行卸载&#10;&#10;4、零信任安装指引&#10;（1）双击点击安装包打开------&gt;点“是” ，如下图&#10;&#10;（2）点—&gt;我同意，如下图&#10;&#10;（3）选择安装位置（可自定义选择安装位置）默认即可，点击—&gt;安装，如下图&#10;&#10;（4）等待安装完成即可，如下图&#10;&#10;（5）安装完成默认勾选运行零信任，桌面可看到零信任图标，如下图&#10;&#10;(6)打开零信任扫码登录，即可通过浏览器访问内部系统，如下图&#10;&#10;(7)如果第一次安装提示需要输入控制器地址，请输入sec.zy.com或124.71.208.207，点击确认后扫码登录使用&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【零信任-6】windows安全助手（零信任）卸载&#10;&#10;1   找到软件所在位置&#10;&#10;1.1 找到安装的软件的位置进行卸载&#10;&#10;a.通过桌面 win 键查找进入&#10;&#10;Win 键安全助手右键点击“ 启动或显示托盘图标”更多打开文件位置&#10;&#10;b.直接输入到安装目录进入&#10;&#10;C:\ProgramData\Microsoft\Windows\Start Menu\Programs\安全助手&#10;&#10;1.2 双击运行卸载&#10;&#10;1.3 管理员口令是e2vPsv8$&#10;&#10;1.4 完成卸载&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）"/>
-        <filter val="【零信任-4】mac零信任卸载手册&#10;卸载前确保零信任没有打开，否则无法卸载；&#10;&#10;退出零信任&#10;&#10;2.在电脑上面的菜单栏，找到前往，进入用用程序&#10;&#10;3.找到零信任，右键，移到废纸&#10;4.卸载完后，找到网络设置，找到DNS，如果有127.0.0.1，则删除保存，如果没有这一步可不管&#10;&#10;5.回到桌面，扎到菜单栏的实用工具&#10;&#10;找到终端&#10;&#10;6.在终端界面分别输入下面的命令&#10;过程将提示输入密码密码不会显示，直接输入后回车即可若密码不对，会提示错误重新输入&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;mac零信任卸载手册&#10;（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;&#10;问题：mac端登录零信任后提示以下报错&#10;&#10;答案：&gt;1：打开终端检查&#10;输入sudo vi /etc/hosts&#10;查看下面是否有存在127.0.0.1 localhost，如果没有需要手动添加上去&#10;2：先点退出零信任，再查看网络上的dns是不是有127.0.0.1， 如果存在需要手动去掉重新登录即可&#10;插图：（如有）&#10;&#10;问题：安全助手卸载办法&#10;答案：&gt;&#10;Windows版客户端&#10;https://doc.weixin.qq.com/doc/w3_AScA5wbEAIkCNuZkWktsqQDuXa04c?scode=AO4AZgeBAAsXMgnZwMAScA5wbEAIk&#10;Mac版客户端&#10;https://doc.weixin.qq.com/doc/w3_AcQAcwauALkCNx9aHWdGuQ861ZCTg?scode=AO4AZgeBAAshjQyPqvAScA5wbEAIk&#10;插图：（如有）&#10;&#10;问题：：如何修改host文件（mac）&#10;答案：&gt;1：打开终端检查&#10;输入sudo vi /etc/hosts&#10;查看下面是否有存在127.0.0.1 localhost，如果没有需要手动添加上去&#10;2：先点退出零信任，再查看网络上的dns是不是有127.0.0.1， 如果存在需要手动去掉重新登录即可&#10;插图：（如有）&#10;&#10;问题：：如何修改host文件（Windows）&#10;答案：&gt;进入C:\Windows\System32\drivers\etc\hosts，打开host文件，输入127.0.0.1 localhost，编辑完成保存关闭文件&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;&#10;答案：&gt;零信任sdp_engine进程损坏，下载sdp_engine.exe文件，并替换sdp_engine.exe文件，重新打开零信任扫码登录&#10;下载地址：https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/sdp_engine.exe&#10;插图：（如有）&#10;找到下载文件sdp_engine.exe，复制这个文件拷贝到零信任安装目录替换文件sdp_engine.exe，比如C:\Program Files (x86)\TrustCyberLink\resources\app\engine&#10;&#10;问题：MacBook电脑安装完零信任打开需要输入密码进行提权，密码提示不对问题&#10;答案：&gt;由于mac未设置足够权限给SDP客户端导致，需要添加零信任权限&#10;路径：设置-隐私与安全性-添加零信任程序开启SDP相关的权限即可&#10;插图：（如有）&#10;&#10;如解决方法一仍然提示密码错误，检查密码是否有字符串，有的话把字符串修改后再重新打开，输入密码进行提取&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;参考下图：&#10;&#10;1.5、问题：打开零信任时提示连接控制器失败，如下图：&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;选择控制器切换124.71.208.207地址；&#10;&#10;b.如a步骤切换控制器地址依然不解决的情况下，可选择重置控制器再输入124.71.208.207参考下图：&#10;&#10;1.6、问题：启动零信任时提示JavaScript错误，无法正常启动，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.打开终端—sudo vi /etc/hosts文件下添加127.0.0.1 localhost&#10;&#10;1.7、问题：nslookup正常解析域名情况下，使用safari、火狐浏览器访问应用报403，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.更换Google浏览器，即可正常访问应用&#10;&#10;1.8、问题：启动零信任时无快捷登录方式，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;随机输入一个用户名，再返回上一级，选择快捷登录方式，参考下图：&#10;&#10;1.9、问题：退出零信任后发现外网基本上不了例如：www.baidu.com"/>
-        <filter val="【一体机-2】希象传屏接收端使用指引&#10;一、功能介绍&#10;投屏&#10;安装完成，桌面图标为“无线传屏”&#10;希象传屏接收端&#10;&#10;打开即可获得传屏码&#10;&#10;发送端，输入“投屏码”即可进行投屏&#10;&#10;文件共享&#10;&#10;“传屏码常显”功能&#10;&#10;注意：默认“安全模式”不开启，否则开启后需要输入“4位数字码”&#10;提示：”安全模式“如果有需要再开启，正常情况下这个东西不需要&#10;&#10;最小化功能，点击即可返回桌面&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【一体机-3】希象传屏发送端使用指引&#10;一、希象传屏安装&#10;点击下载windows 、mac&#10;C盘内存少可选择其他盘进行安装&#10;&#10;打开希象传屏，输入接收端得投屏码进行投屏&#10;&#10;如何进行投屏&#10;注意：投屏需要连接同一个wifi&#10;&#10;打开一体机桌面的“无线传屏”程序&#10;&#10;获取投屏码，希象传屏（发送端）输入投屏即可投屏&#10;&#10;发送端可选择投屏方式为“桌面”或者“窗口”&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;AI智能体开发知识库&#10;&#10;### 优质开场白示例参考&#10;- 以AI智能体“家校沟通助手”为例，它的开场白如下：&#10;你好，我是家校沟通助手bubble🥰我能提供以下功能：👉家校沟通模拟：助手扮演家长/老师进行对话，也能提供回答建议👉学生学情分析：请尽可能详细地输入学生学情供助手进行分析👉模拟学生学情：助手根据输入内容随机生成学情，供老师们进行分析练习&#10;请点击下方按钮选择想调用的功能，并且根据提示输入对应内容若想使用其他功能，请点击或输入按钮上的文字进行调用很高兴与你交流~欢迎随时来找我&#10;&#10;---&#10;### 如何插入开场白&#10;- **第一步**：完成智能体开发后，点击右上角【预览】，在弹出的框里找到右下角的【管理→】&#10;- **第二步**：启动【对话开场白】，即可开始设置，还可以设计几个常用的开场问题，方便用户快速提问(*^▽^*)&#10;具体如下图所示：&#10;&#10;---"/>
-        <filter val="安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;（2）双击点卸载&#10;&#10;（3）输入安全助手卸载码（e2vPsv8$）后，运行卸载&#10;&#10;4、零信任安装指引&#10;（1）双击点击安装包打开------&gt;点“是” ，如下图&#10;&#10;（2）点—&gt;我同意，如下图&#10;&#10;（3）选择安装位置（可自定义选择安装位置）默认即可，点击—&gt;安装，如下图&#10;&#10;（4）等待安装完成即可，如下图&#10;&#10;（5）安装完成默认勾选运行零信任，桌面可看到零信任图标，如下图&#10;&#10;(6)打开零信任扫码登录，即可通过浏览器访问内部系统，如下图&#10;&#10;(7)如果第一次安装提示需要输入控制器地址，请输入sec.zy.com或124.71.208.207，点击确认后扫码登录使用&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;安全助手卸载和零信任工具安装指引&#10;&#10;注明：先卸载安全助手，后安装零信任工具，如果没有安全助手，可覆盖安装零信任工具&#10;&#10;1、零信任工具下载链接：&#10;Windows版本：&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe  （新版本下载链接）  &#10;&#10;2、管理员口令和安全助手卸载码都是e2vPsv8$&#10;&#10;3、安全助手卸载指引&#10;3.1、第一种卸载方式&#10;（1） 右键安全助手图标，点击进入特权模式，输入管理员口令（e2vPsv8$)即可进入特权模式&#10;&#10;（2）进入特权模式后，在本地电脑C:\Windows\LVUAAgentInstBaseRoot找到此文件运行卸载 &#10;&#10;输入安全助手卸载码（卸载密码默认 e2vPsv8$）&#10;&#10;3.2、第二种卸载方式&#10;（1）若是Win10 系统点击左下角，找到并打开文件夹“UniAccess安全助手”，右键点击“启动或显示托盘图标 ”，点击更多，点击打开文件位置&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;最佳设置&#10;1.2控制器地址：124.71.208.207&#10;&#10;1.3零信任软件推荐设置【重要：减少零信任被误关闭】&#10;&#10;2、零信任软件常见问题：&#10;1、提示不合法的用户名【返回上一级，选择快捷方式登录】&#10;提示会话已经过期，请重新登陆【返回上一级，选择快捷方式登录】&#10;扫码登录提示认证失败【返回上一级，选择快捷方式登录】&#10;&#10;2、登陆零信任后提示无无法访问此网页【关闭浏览器，重新登陆零信任并刷新策略】&#10;&#10;3、打开零信任扫码登录后提示开启私网DNS失败，请稍后重试【联系IT帮助台获取最新版本安装包并覆盖安装】&#10;&#10;4、网络及系统问题&#10;4.1退出零信任后无法访问外网【清除本地dns 127.0.0.1设置或修改为自动获取】&#10;macbook：&#10;Windwos：&#10;&#10;4.2退出零信任后可以登陆企微和微信，无法打开网页【修改Internet代理】&#10;&#10;4.3软件冲突--IOA【网络异常，卸载IOA（已不再使用）并重启电脑】&#10;&#10;4.3开机进入桌面很慢，自动弹窗警告【卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项】&#10;&#10;5、用户权限相关&#10;5.1打开零信任无OA访问窗口，空白&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;&#10;答案：&gt;零信任sdp_engine进程损坏，下载sdp_engine.exe文件，并替换sdp_engine.exe文件，重新打开零信任扫码登录&#10;下载地址：https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/sdp_engine.exe&#10;插图：（如有）&#10;找到下载文件sdp_engine.exe，复制这个文件拷贝到零信任安装目录替换文件sdp_engine.exe，比如C:\Program Files (x86)\TrustCyberLink\resources\app\engine&#10;&#10;问题：MacBook电脑安装完零信任打开需要输入密码进行提权，密码提示不对问题&#10;答案：&gt;由于mac未设置足够权限给SDP客户端导致，需要添加零信任权限&#10;路径：设置-隐私与安全性-添加零信任程序开启SDP相关的权限即可&#10;插图：（如有）&#10;&#10;如解决方法一仍然提示密码错误，检查密码是否有字符串，有的话把字符串修改后再重新打开，输入密码进行提取&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;1、下载和安装：&#10;Windows版本：下载链接https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe&#10;MAC版本：下载链接&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.120.dmg&#10;如需更最新版本，请企业微信联系IT帮助台获取"/>
-        <filter val="企业微信常见问题解答&#10;&#10;四、为什么会有多个企业身份/如何切换企业&#10;若被添加进多个企业，或者已经加入多个企业时，就可以在登录时或者在手机端【我-设置-切换身份】看到多个企业，可以在这个入口选择进入对应的企业&#10;五、如何修改绑定手机号&#10;手机端【我】-&gt;【个人信息】-&gt;【手机】-&gt;【更换手机号】&#10;&#10;六、企业微信可以发起群聊吗，是否有上限&#10;可以发起内部群或外部群客户群上限人数200、内部群上限人数2000，客户群默认50人，超过50人就要在OA系统提交账号权限申请，可授权的上限是200，内部群默认50人，超过50人就要提交账号权限申请，可授权的上限是2000；&#10;&#10;七、群主离职后如何转让群主&#10;目前群主在通讯录被管理员删除后，是否会自动转让群主，目前有三种情况&#10;1、内部群、在微信侧创建的互通群：在群主离职后会系统自动把群主转让给群内成员微信侧创建的互通群在群聊会话中可看见“由微信用户创建的字样”&#10;2、由于企业微信用户创建的外部群：在群主离职后会系统自动把群主转让给在这个群内，同企业的人，如果群里没有同企业的人，则不会触发转让群主 企业微信侧创建的互通群在群聊会话中可看见“由企业微信用户创建的字样”&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;小助手操作手册&#10;&#10;第⼀步：选择需要设置关键词的微信，点击关键词设置；&#10;&#10;第⼆步：编辑关键词，可以点击添加，编辑多个关键词，客户发送不同的关键词进⼊不同的群；&#10;第三步：选择微信群，可以选择多个微信群，通过设置“群满多少⼈进⼊下⼀个群”选项设置群⼈&#10;&#10;数，第⼀个达到⼈群设置值，会⾃动补群&#10;&#10; 5.5邀请⼊群&#10; 5.5.1邀请机器⼈⼊群&#10;这个功能是邀请群托进群，主要是烘托群的⽓氛群托⽬前只能是后台绑定的微信号&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;如何创建收集表&#10; 10、支持设置【可查看填写结果的人】，可以设置的人数上限为500人 11、收集表我的模板可添加上限为100个 12、收集表的在线填写人数暂无上限 13、一个收集表目前支持收集100万份结果 14、问答题输入框支持输入4000字 15、题目类型为下拉选项时，选项框内容不能超过30个字符上限 16、图片、文件题目支持设置保存到微盘的文件存储路径  六、成员发起的收集表，没有开启“定时提醒”，是否会发送填写提醒 （1）收集范围超过500人，可以正常发起收集表，但不会自动通知收集范围的人员填写收集表的，需要创建收集表的人自己手动转发收集表给人员们填写； （2）未超过500人，可以正常发起收集表，并且会自动下发通知 开启“允许成员创建全员收集”： 开启范围内的成员可以发起全员收集表（收集范围不限人数），并且支持自动通知收集范围的人员（即使开启“定时提醒”也支持） 注：微信联系人暂时不支持收到提醒填写的通知，企业微信联系人可以在微文档推送中收到提醒，家长则可在学校通知收到填写提醒 Tips：如使用中有其他问题，可联系 IT帮助台 或在 OA 上填写IT报障单&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;-如何发表客户朋友圈&#10;&#10;注：&#10;（1）企业群发的图片仅支持ipg格式，视频仅支持mp4格式企业群发暂无选择人数上限&#10;（2）管理端视频时长不超过30S且最大不超过10MB客户端视频帧率 30 FPS，视频码率 1.67 Mbps，视频时长不超过30S且最大不超过10MB；&#10;（3）目前发送的图片分为普通图片和长图&#10;普通图片是指长边/短边&lt;10的图片，普通图片短边不能超过1080，大小不能超过10m； 长图是指长边/短边&gt;=10的图片，长图长边不能超过10800，大小不能超过20m；&#10;发送的图片像素数不能超过1166.4W；&#10;超过以上限制图片的朋友圈发送后，用户侧会查看到被压缩后的图片&#10;（4）安卓端发表客户朋友圈从微盘中选取视频/图片时，大小超过10m的视频/图片会进行压缩，压缩后才可以发送&#10;（5）iOS端发表客户朋友圈从微盘中选取视频/图片时，不论大小是多少都会被压缩，压缩后才可以发送&#10;4、发表朋友圈时，支持选择可见的客户，可选择公开发表或按条件筛选客户按条件筛选时，支持设置“谁可以看”和“不给谁看”&#10;注：如果A客户同时在“谁可以看”和“不给谁看”里面，“谁可以看”的实际范围会把A剔除掉&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;如何创建收集表&#10; 三、提醒人员填写收集表 1、收集表收集范围 收集表权限范围是立即生效，如果新员工是在推送提醒后被设置到对应的部门， 新员工则需要等第二天才能收到提醒填写的卡片如果是在推送前被添加到组织架构，则被设置当前就可以收到填写提醒的卡片 2、提醒收集表指定对象 创建好的收集表，可以快速发送给同事或分享到微信，邀请他们填写还可以获取二维码、复制链接，将链接、二维码通过公告等方式分发给员工填写 当指定对象大于100人时，暂时不支持推送填写提醒给指定对象 3、收集表设置定时重复 设置定时重复后，收集表将按周期重复，在周期开始时发送填写提醒，每个周期的已填未填情况会分开统计（需要添加至少一个可填写人才能开启定时重复） 注：若在群聊中创建收集表，除家校企业外，其他行业在群聊中创建收集表不会有【定时重复】入口 四、收集表权限控制 管理员可以在【手机端-&gt;工作台-&gt;收集表-&gt;新建-&gt;最顶端-&gt;开启/关闭“允许成员创建全员收集”】 企业通讯录已有人数超过500人的企业才可见该入口，人数少于500人的企业看不到这个入口 五、收集表上限说明 1、图片/文件类问题，最多支持上传9个图片/文件"/>
-        <filter val="重置通行证密码&#10;通行证使用时不带@zy.com的后缀&#10;通行证密码不是邮箱密码&#10;企微点击【工作台】-【IT服务台】-【更多功能】-【通行证密码重置】&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;08卓越在线常见问题QA&#10;&#10;答：如选择【学员家长登录】，密码为通行证密码果是密码有误，忘记密码的同学，&#10;&#10;⑤我是学生/家长，为何登录不进去&#10;答：如果是密码有误，那么选择【忘记密码】，或者【验证码登录】、【微信登录】&#10;即可；&#10;&#10;如果【验证码登录】失败，那么老师需要去TMS 查询，该学生当前登录使用的手机&#10;号是否是学生的通行证手机号，如果不是，复制TMS 里学生的手机号给家长，进行&#10;&#10;如果微信登录也登录失败，那么则可能是该微信没有绑定孩子的通行证，去TMS 查&#10;询该孩子并发送通行证二维码给家长进行微信扫码、重新绑定即可&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【邮箱-4】重置邮箱密码&#10;重置密码：企业微信，点击【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【邮箱-10】263邮箱设置--Outlook篇&#10;【修改263邮箱登陆密码】&#10;&#10;【忘记邮箱密码重置办法】&#10;打开企业微信搜索【IT服务台】，更多功能→重置邮箱密码，按页面步骤进行密码修改&#10;&#10;【Outlook更新密码】&#10;&#10;【Outlook 邮件客户端配置263邮箱步骤】&#10;&#10;设置完成，测试邮件收发&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【邮箱-12】263邮箱设置--Macbook 邮件篇&#10;【修改263邮箱登陆密码】&#10;&#10;【忘记邮箱密码重置办法】&#10;重置密码：企业微信，点击【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】&#10;&#10;【Macbook 邮件更新密码步骤】&#10;&#10;【Macbook 邮件客户端配置263邮箱步骤】&#10;&#10;按图补充1~3点信息&#10;&#10;设置完成，测试邮件收发&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）"/>
-        <filter val="【零信任-4】mac零信任卸载手册&#10;卸载前确保零信任没有打开，否则无法卸载；&#10;&#10;退出零信任&#10;&#10;2.在电脑上面的菜单栏，找到前往，进入用用程序&#10;&#10;3.找到零信任，右键，移到废纸&#10;4.卸载完后，找到网络设置，找到DNS，如果有127.0.0.1，则删除保存，如果没有这一步可不管&#10;&#10;5.回到桌面，扎到菜单栏的实用工具&#10;&#10;找到终端&#10;&#10;6.在终端界面分别输入下面的命令&#10;过程将提示输入密码密码不会显示，直接输入后回车即可若密码不对，会提示错误重新输入&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.需要把本机网络的DNS127.0.0.1去掉即可，参考下图：&#10;&#10;1.10、问题：为什么我登录不了TMS、EVIP……，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;请先安装零信任，并扫码登录—登录后不能退出零信任&#10;参考下图：&#10;&#10;1.11、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;去到安装目录C:\Program Files (x86)\TrustCyberLink目录下打开TrustCyberLink.exe&#10;1.12、问题：打开零信任没有企业微信按钮 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新打开或者点击控制切换器—点击124.71.208.207或者sec.zy.com-点击确认即可&#10;1.13、问题：安装助手完成时零信任未安装成功 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新安装即可&#10;1.14、问题：提示 “由于找不到 UAADataCenter.dl，无法继续执行代码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;参考下图：&#10;&#10;1.5、问题：打开零信任时提示连接控制器失败，如下图：&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;选择控制器切换124.71.208.207地址；&#10;&#10;b.如a步骤切换控制器地址依然不解决的情况下，可选择重置控制器再输入124.71.208.207参考下图：&#10;&#10;1.6、问题：启动零信任时提示JavaScript错误，无法正常启动，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.打开终端—sudo vi /etc/hosts文件下添加127.0.0.1 localhost&#10;&#10;1.7、问题：nslookup正常解析域名情况下，使用safari、火狐浏览器访问应用报403，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.更换Google浏览器，即可正常访问应用&#10;&#10;1.8、问题：启动零信任时无快捷登录方式，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;随机输入一个用户名，再返回上一级，选择快捷登录方式，参考下图：&#10;&#10;1.9、问题：退出零信任后发现外网基本上不了例如：www.baidu.com&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;安全助手（零信任）客户端FAQ&#10;操作问题&#10;问题：登录零信任后访问应用时浏览器页面提示403forbidden，如下图：&#10;&#10;设备类型：&#10;Windows/macbook&#10;解决方案：&#10;使用其他浏览器访问&#10;设置浏览器后重新打开进行访问应用&#10;（1）Google浏览器&#10;&#10;（2）火狐浏览器&#10;&#10;问题：登录零信任后当访问应用时提示无法访问此网站，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10; 先关闭浏览器，点击刷新 重新获取策略（刷新一次未解决可以继续点击刷新）参考下图：&#10;&#10; 当a步骤重新获取策略后还是一样提示无法访问此网站时可退出登录零信任，再退出零信任客户端，重新打开扫码登录可参考下图：&#10;&#10;问题：打开零信任扫码登陆时，提示不合法的状态，如下图&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;a.返回上一级，去掉用户名，选择快捷方式登陆参考下图：&#10;&#10;1.4、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;返回上一级，重新选择快捷方式登陆&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;mac零信任卸载手册&#10;（OA系统地址：http://oa.zy.com ）"/>
-        <filter val="【打印机-3】MAC 连接打印机操作指引&#10;一、下载驱动包&#10;京瓷打印机mac系统驱动下载&#10;&#10;注：安装前需要先知道打印机IP地址，如下图所示：&#10;&#10;安装驱动&#10;双击驱动包&#10;&#10;若在桌面没有找到驱动，则使用“command+空格键”弹出的搜索框里输入“Kyocera OS X 10.9+ Web build 2024.05.16”，找到并双击驱动包&#10;&#10;双击安装程序&#10;&#10;一路安装&#10;&#10;安装完成后，需要重启电脑!!!&#10;&#10;二、添加打印机&#10;进入系统偏好设置&#10;&#10;进入打印机与扫描仪&#10;&#10;添加设置&#10;&#10;选择IP连接，输入对应打印机IP地址，选择连接协议&#10;&#10;（若电脑无法自动识别打印机型号，请检查打印机是否出现网络问题，例如网线松动等）&#10;&#10;完成添加，可以进行打印&#10;三、各协议解释&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-8】Windows系统安装京瓷打印机指引&#10;一、下载打印机驱动包存到电脑硬盘上&#10;驱动包下载地址：京瓷打印机驱动下载&#10;二、安装打印机&#10;注：安装前需要先收集打印机IP地址和型号（部分共用的打印机需要准备部门密码）&#10;打印机IP地址，图示&#10;&#10;查询打印机型号，图示&#10;&#10;1、解压驱动包&#10;&#10;2、打开安装程序, 按步骤安装&#10;进入文件夹，双击Setup.exe&#10;&#10;接受，选择自定义安装&#10;&#10;以下内容请根据打印机实际型号和IP填写&#10;&#10;添加打印机驱动和安装升级的组件&#10;&#10;打印机安装完成&#10;&#10;三、设置打印机&#10;1、修改名称、设置双面打印&#10;打开计算机，跳至控制面板，进入硬件设备&#10;&#10;右击，打印机属性&#10;&#10;修改打印机名称&#10;&#10;设置双面打印&#10;&#10;2、打印机显示脱机时，需要设置取消SNMP&#10;&#10;3、添加部门id&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-7】Windows修改打印机IP指引&#10;一、同时按“win+R”输入“control”&#10;&#10;弹出“控制面板”界面选择类别&#10;&#10;点击“查看设备和打印机”&#10;&#10;选择需要修改IP地址的打印机&#10;当前以“Kyocera TASKalfa 300i KX”打印机为例&#10;&#10;选择打印机，右键“打印机属性”&#10;&#10;选择”端口“，选中当前打印机端口&#10;&#10;选择”配置端口“&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址： http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-4】打印机IP地址查看及报修&#10;1.查看打印机IP地址：&#10;一般打印机IP地址都会粘贴或写在标签纸上，如下图：&#10;&#10;2.过程中遇到非驱动或网络问题，而是打印机出现不能开机、硒鼓、卡纸等等不能处理问题可拨打以下电话或者添加图中穗保客服报修&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-6】Windows系统添加一体打印机部门ID&#10;1、打开控制面板&#10;&#10;2、右击对应型号打印机 - 点打印机属性（型号可以在打印机面前看到）&#10;&#10;3、点最后一项设备设置 - 点管理员&#10;&#10;注：每机每部门的ID都不一样&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址： http://oa.zy.com ）"/>
-        <filter val="安全助手(零信任）客户端FAQ&#10;参考下图：&#10;&#10;1.5、问题：打开零信任时提示连接控制器失败，如下图：&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;选择控制器切换124.71.208.207地址；&#10;&#10;b.如a步骤切换控制器地址依然不解决的情况下，可选择重置控制器再输入124.71.208.207参考下图：&#10;&#10;1.6、问题：启动零信任时提示JavaScript错误，无法正常启动，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.打开终端—sudo vi /etc/hosts文件下添加127.0.0.1 localhost&#10;&#10;1.7、问题：nslookup正常解析域名情况下，使用safari、火狐浏览器访问应用报403，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.更换Google浏览器，即可正常访问应用&#10;&#10;1.8、问题：启动零信任时无快捷登录方式，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;随机输入一个用户名，再返回上一级，选择快捷登录方式，参考下图：&#10;&#10;1.9、问题：退出零信任后发现外网基本上不了例如：www.baidu.com&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;最佳设置&#10;1.2控制器地址：124.71.208.207&#10;&#10;1.3零信任软件推荐设置【重要：减少零信任被误关闭】&#10;&#10;2、零信任软件常见问题：&#10;1、提示不合法的用户名【返回上一级，选择快捷方式登录】&#10;提示会话已经过期，请重新登陆【返回上一级，选择快捷方式登录】&#10;扫码登录提示认证失败【返回上一级，选择快捷方式登录】&#10;&#10;2、登陆零信任后提示无无法访问此网页【关闭浏览器，重新登陆零信任并刷新策略】&#10;&#10;3、打开零信任扫码登录后提示开启私网DNS失败，请稍后重试【联系IT帮助台获取最新版本安装包并覆盖安装】&#10;&#10;4、网络及系统问题&#10;4.1退出零信任后无法访问外网【清除本地dns 127.0.0.1设置或修改为自动获取】&#10;macbook：&#10;Windwos：&#10;&#10;4.2退出零信任后可以登陆企微和微信，无法打开网页【修改Internet代理】&#10;&#10;4.3软件冲突--IOA【网络异常，卸载IOA（已不再使用）并重启电脑】&#10;&#10;4.3开机进入桌面很慢，自动弹窗警告【卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项】&#10;&#10;5、用户权限相关&#10;5.1打开零信任无OA访问窗口，空白&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;（2）双击点卸载&#10;&#10;（3）输入安全助手卸载码（e2vPsv8$）后，运行卸载&#10;&#10;4、零信任安装指引&#10;（1）双击点击安装包打开------&gt;点“是” ，如下图&#10;&#10;（2）点—&gt;我同意，如下图&#10;&#10;（3）选择安装位置（可自定义选择安装位置）默认即可，点击—&gt;安装，如下图&#10;&#10;（4）等待安装完成即可，如下图&#10;&#10;（5）安装完成默认勾选运行零信任，桌面可看到零信任图标，如下图&#10;&#10;(6)打开零信任扫码登录，即可通过浏览器访问内部系统，如下图&#10;&#10;(7)如果第一次安装提示需要输入控制器地址，请输入sec.zy.com或124.71.208.207，点击确认后扫码登录使用&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;零信任配置指引&#10;下载安装包&#10;Windows系统版本&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe&#10;&#10;Macbook版本&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250715/TrustCyberLink_PC_Setup_2.207.122.dmg&#10;&#10;2、安装完成后：&#10;控制器地址:124.71.208.207&#10;&#10;3、企业微信扫码登录后即可访问应用&#10;&#10;4、进来界面后单击设置按钮-勾选开机自动运行-勾选最小化到托盘或勾选退出TrustCyberLink&#10;&#10;5、退出登陆&#10;企业微信扫码登录后，在不使用零信任时可选择退出登录&#10;&#10;扫码登陆时认证失败&#10;重新进入扫码登陆界面即可&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;mac零信任卸载手册&#10;（OA系统地址：http://oa.zy.com ）"/>
-        <filter val="【邮箱-4】重置邮箱密码&#10;重置密码：企业微信，点击【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;重置通行证密码&#10;通行证使用时不带@zy.com的后缀&#10;通行证密码不是邮箱密码&#10;企微点击【工作台】-【IT服务台】-【更多功能】-【通行证密码重置】&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【邮箱-12】263邮箱设置--Macbook 邮件篇&#10;【修改263邮箱登陆密码】&#10;&#10;【忘记邮箱密码重置办法】&#10;重置密码：企业微信，点击【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】&#10;&#10;【Macbook 邮件更新密码步骤】&#10;&#10;【Macbook 邮件客户端配置263邮箱步骤】&#10;&#10;按图补充1~3点信息&#10;&#10;设置完成，测试邮件收发&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;新伙伴入职指引3&#10;&#10;若密码失效，可以在企业微信-工作台-(搜索)IT服务台(打开)-(右下角)更多功能-邮箱密码重置&#10;办公设施指引: IT帮助台;办公设施指引: 无;办公设施指引: 无;办公设施指引: 若有其他个人无法解决的系统问题，可在企业微信上咨询‘IT帮助台’解决；&#10;访问方式：通讯录-卓越教育-员工服务-IT帮助台&#10;办公设施指引: 工卡制作;办公设施指引: 工卡照片将采用您在线填写个人信息时所上传的照片（待企业微信开通后，可以联系对应HR老师进行领取）;办公设施指引: 工卡照片将采用您在线填写个人信息时所上传的照片（待企业微信开通后，可以联系对应HR老师进行领取）;办公设施指引: 工卡照片将采用您在线填写个人信息时所上传的照片（待企业微信开通后，可以联系对应HR老师进行领取）&#10;办公设施指引: 内部推荐;办公设施指引: 登入【企业微信-工作台-人力磁-内部推荐】，内推合适人选，将有500-3000元奖励哦;办公设施指引: 登入【企业微信-工作台-人力磁-内部推荐】，内推合适人选，将有500-3000元奖励哦&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【邮箱-10】263邮箱设置--Outlook篇&#10;【修改263邮箱登陆密码】&#10;&#10;【忘记邮箱密码重置办法】&#10;打开企业微信搜索【IT服务台】，更多功能→重置邮箱密码，按页面步骤进行密码修改&#10;&#10;【Outlook更新密码】&#10;&#10;【Outlook 邮件客户端配置263邮箱步骤】&#10;&#10;设置完成，测试邮件收发&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）"/>
-        <filter val="263邮箱使用指引&#10;如下图：&#10;&#10;2.2 捆绑263邮箱的旧手机号码已注销或不能收取短信验证码，需要在OA系统上发起账户/权限申请】流程进行捆绑手机号码的变更，按以下步骤操作：&#10;2.2.1登录OA系统，点击【发起流程】-【IT类】-【IT服务】-【账户/权限申请】，“系统”选择“263企业邮箱 ”，“描述”写清楚你的需求&#10;&#10;忘记263邮箱密码/修改263邮箱密码&#10;登录企业微信-【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】，如下图：&#10;&#10;企业微信绑定263邮箱进行使用&#10;登录企业微信-【工作台】-【263企业邮箱】，输入邮箱和密码就可以完成绑定&#10;重置邮箱密码之后也需要重新捆绑企业微信才可以正常使用&#10;&#10;登录263邮箱时候提示：用户邮箱状态异常&#10;需要先登录企业微信-【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】进行密码重置，然后再进行微信绑定&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;&#10;插图：&#10;&#10;问题：263企业邮箱发信提示人数受限&#10;答案：提交OA权限申请，登陆OA系统 &gt;搜索账户/权限申请 &gt;263邮箱 &gt;群发邮件最多收件人数权限开通 &gt;填写需要开通的数量&#10;插图：&#10;&#10;问题：263企业邮箱特殊人或专用邮箱开通&#10;答案：提交OA权限申请，登陆OA系统 &gt;搜索账户/权限申请 &gt;263邮箱 &gt;特殊用户邮箱开通 &gt;填写需要邮箱作用和计划开通邮箱账号&#10;插图：&#10;&#10;问题：263邮箱收到企业邮箱密码修改提醒&#10;答案：邮箱安全管理要求，第一次及每90天需要修改一次密码，请按照邮箱系统指引修改密码，如有Foxmail或Outlook请同步修改，特殊邮箱90天内未修改密码账号将停用&#10;插图：（如有）&#10;&#10;问题：263邮箱收到可疑邮件（钓鱼或病毒）如何处理&#10;答案：请不要点击邮件的任何链接和下载打开附件，并将邮件原件转发到sec-team@zy.com由安全专家审核回复&#10;插图：（如有）&#10;&#10;问题：263邮箱如何判断为可疑的钓鱼文件&#10;答案：1.1.看发件人地址：如果是公务邮件，发件人多数会使用工作邮箱，如果发现对方使用的是个人邮箱帐号或者邮箱账号拼写很奇怪，那么就需要提高警惕&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【邮箱-1】263邮箱使用指引&#10;新用户初次登录263邮箱&#10;新用户初次登录邮箱需要在电脑网页端登录，必须关联手机号码&#10;在浏览器复制并打开该网址： https://www.263.net/&#10;1.1点击【登录】-输入【邮箱】和【密码】（没有邮箱密码可以按忘记密码去重置）&#10;&#10;1.2 输入【手机号码】和【短信验证码】,提示【手机号验证成功】，表示已关联手机号，如下图：&#10;&#10;更换捆绑手机号&#10;2.1 旧手机号还能接收到短信验证码的情况，需要先解绑旧手机号码再重新绑定新手机号码，按以下步骤操作：&#10;2.1.1登录邮箱-点击右上角【账户】头像-【设置】,如下图：&#10;&#10;2.1.2点击【账户信息】-【点击这里绑定手机】,如下图：&#10;&#10;2.1.3点击【解除绑定】,如下图：&#10;&#10;2.1.4点击【获取验证码】并输入验证码后，点击【解除绑定】,如下图：&#10;&#10;2.1.5点击手机号码【绑定】,如下图：&#10;2.1.6输入【手机号码】和【验证码】,点击确定，就完成了新的手机号码捆绑邮箱&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;&#10;问题：263企业邮箱Outlook配置指引&#10;答案：详情见链接文档https://www.263.net/success/mail/clientowo/20231124/1911.html&#10;插图：&#10;&#10;问题：263企业邮箱Foxmail配置指引&#10;答案：详情见链接文档https://www.263.net/success/mail/client/20231124/1909.html&#10;插图：&#10;&#10;问题：263企业邮箱Mac客户配置指引&#10;答案：详情见链接文档https://www.263.net/success/mail/client/20231124/1910.html&#10;插图&#10;&#10;问题：263企业邮箱电脑、移动端客户端配置指引&#10;答案：详情见链接文档https://www.263.net/success/mail/mobilesettings/&#10;插图&#10;&#10;问题：263邮箱修改信任登陆地点（提示异地登陆）&#10;答案：通过网页登录邮箱，点击右上角头像 &gt;设置 &gt;账户安全 &gt;异地登陆地点 &gt;添加信任  城市&#10;插图&#10;&#10;问题：企业微信绑定263邮箱&#10;答案：在企业微信搜索263企业邮箱，输入账户密码绑定&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;）&#10;插图：（如有）&#10;&#10;问题：263邮箱登陆提示IP地址在黑名单&#10;答案：提交IT报障单申报故障，登陆OA &gt;发起流程 &gt;IT报障/预约服务单 &gt;服务/故障描述：263邮箱黑名单IP：xxx.xxx.xxx.xxx 邮箱账号：xxx@zy.com（按提示内容填写）&#10;插图：（如有）&#10;&#10;问题：手机号码丢失，修改邮箱绑定手机号码&#10;答案：提交IT报障单申报故障，登陆OA &gt;发起流程 &gt;IT报障/预约服务单 &gt;服务/故障描述：263邮箱修改绑定手机  原手机：1391234567 邮箱账号：xxx@zy.com（按提示内容填写）&#10;插图：（如有）&#10;&#10;问题：263邮箱发信提示，您发送的邮件大小超出了您的权限&#10;答案：上传附件超过30M，请通过web登陆邮箱使用云附件功能发送（上传的云附件有效期15天）&#10;插图：（如有）&#10;&#10;问题：263邮箱web登陆收不到验证码&#10;答案：提交IT报障单申报故障，登陆OA &gt;发起流程 &gt;IT报障/预约服务单 &gt;服务/故障描述：如：263邮箱收不到验证码  手机：1391234567 邮箱账号：xxx@zy.com  登陆时间：10:00~10:30&#10;插图：（如有）&#10;&#10;问题：办公电脑安装打印机&#10;答案：企微扫码进群，进群后@穗保客服  协助你连接打印机"/>
-        <filter val="安全助手(零信任）客户端FAQ&#10;&quot;&#10;1.19、问题：扫码登陆时认证失败 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;重新进入扫码登陆界面即可&#10;1.20、问题：登录了零信任，但是访问不了内网 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;1、确认电脑上没有IOA，或者有没登录IOA（建议卸载了，后续不会用了，原来限制的域名换到了新的零信任）&#10;2、处理掉IOA后，再次扫码登录零信任（退IOA前扫码了的话，也需要退出再扫一次码）&#10;3、登录超时了，退出零信任，重新登录&#10;参考下图：&#10;1.21、问题：开机进入系统很慢，运行慢，杀毒软件不断弹窗 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项&#10;1.22、问题：登录了零信任，点击应用提示“请求失败”  如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;退出零信任，重新登录&#10;1.23、问题：兼职老师登录零信任，应用列表是空白 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;因为零信任同步企微账号，分配组有问题，没有分配到与企微一致的组织架构下，而且分到默认组（需要绿盟排查原因），需要零信任管理员人工更改分组&#10;1.24、问题：部分应用无法访问，如ssoin.zy.com &#10;设备类型：&#10;mac&#10;解决方案：&#10;ping ssoin.zy.com的ip是10.12.81.44，但是在浏览器访问页面，发现请求ip是外网IP，暂未有解决根源的办法，临时办法：本地host绑定为10.12.81.44&#10;设备兼容性问题&#10;2.1、 问题：打开零信任扫码登录后提示开启私网DNS失败，请稍后重试&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;参考下图：&#10;&#10;1.5、问题：打开零信任时提示连接控制器失败，如下图：&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;选择控制器切换124.71.208.207地址；&#10;&#10;b.如a步骤切换控制器地址依然不解决的情况下，可选择重置控制器再输入124.71.208.207参考下图：&#10;&#10;1.6、问题：启动零信任时提示JavaScript错误，无法正常启动，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.打开终端—sudo vi /etc/hosts文件下添加127.0.0.1 localhost&#10;&#10;1.7、问题：nslookup正常解析域名情况下，使用safari、火狐浏览器访问应用报403，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.更换Google浏览器，即可正常访问应用&#10;&#10;1.8、问题：启动零信任时无快捷登录方式，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;随机输入一个用户名，再返回上一级，选择快捷登录方式，参考下图：&#10;&#10;1.9、问题：退出零信任后发现外网基本上不了例如：www.baidu.com&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;安全助手（零信任）客户端FAQ&#10;操作问题&#10;问题：登录零信任后访问应用时浏览器页面提示403forbidden，如下图：&#10;&#10;设备类型：&#10;Windows/macbook&#10;解决方案：&#10;使用其他浏览器访问&#10;设置浏览器后重新打开进行访问应用&#10;（1）Google浏览器&#10;&#10;（2）火狐浏览器&#10;&#10;问题：登录零信任后当访问应用时提示无法访问此网站，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10; 先关闭浏览器，点击刷新 重新获取策略（刷新一次未解决可以继续点击刷新）参考下图：&#10;&#10; 当a步骤重新获取策略后还是一样提示无法访问此网站时可退出登录零信任，再退出零信任客户端，重新打开扫码登录可参考下图：&#10;&#10;问题：打开零信任扫码登陆时，提示不合法的状态，如下图&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;a.返回上一级，去掉用户名，选择快捷方式登陆参考下图：&#10;&#10;1.4、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;返回上一级，重新选择快捷方式登陆&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.需要把本机网络的DNS127.0.0.1去掉即可，参考下图：&#10;&#10;1.10、问题：为什么我登录不了TMS、EVIP……，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;请先安装零信任，并扫码登录—登录后不能退出零信任&#10;参考下图：&#10;&#10;1.11、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;去到安装目录C:\Program Files (x86)\TrustCyberLink目录下打开TrustCyberLink.exe&#10;1.12、问题：打开零信任没有企业微信按钮 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新打开或者点击控制切换器—点击124.71.208.207或者sec.zy.com-点击确认即可&#10;1.13、问题：安装助手完成时零信任未安装成功 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新安装即可&#10;1.14、问题：提示 “由于找不到 UAADataCenter.dl，无法继续执行代码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;最佳设置&#10;1.2控制器地址：124.71.208.207&#10;&#10;1.3零信任软件推荐设置【重要：减少零信任被误关闭】&#10;&#10;2、零信任软件常见问题：&#10;1、提示不合法的用户名【返回上一级，选择快捷方式登录】&#10;提示会话已经过期，请重新登陆【返回上一级，选择快捷方式登录】&#10;扫码登录提示认证失败【返回上一级，选择快捷方式登录】&#10;&#10;2、登陆零信任后提示无无法访问此网页【关闭浏览器，重新登陆零信任并刷新策略】&#10;&#10;3、打开零信任扫码登录后提示开启私网DNS失败，请稍后重试【联系IT帮助台获取最新版本安装包并覆盖安装】&#10;&#10;4、网络及系统问题&#10;4.1退出零信任后无法访问外网【清除本地dns 127.0.0.1设置或修改为自动获取】&#10;macbook：&#10;Windwos：&#10;&#10;4.2退出零信任后可以登陆企微和微信，无法打开网页【修改Internet代理】&#10;&#10;4.3软件冲突--IOA【网络异常，卸载IOA（已不再使用）并重启电脑】&#10;&#10;4.3开机进入桌面很慢，自动弹窗警告【卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项】&#10;&#10;5、用户权限相关&#10;5.1打开零信任无OA访问窗口，空白"/>
-        <filter val="安全助手(零信任）客户端FAQ&#10;参考下图：&#10;&#10;1.5、问题：打开零信任时提示连接控制器失败，如下图：&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;选择控制器切换124.71.208.207地址；&#10;&#10;b.如a步骤切换控制器地址依然不解决的情况下，可选择重置控制器再输入124.71.208.207参考下图：&#10;&#10;1.6、问题：启动零信任时提示JavaScript错误，无法正常启动，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.打开终端—sudo vi /etc/hosts文件下添加127.0.0.1 localhost&#10;&#10;1.7、问题：nslookup正常解析域名情况下，使用safari、火狐浏览器访问应用报403，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.更换Google浏览器，即可正常访问应用&#10;&#10;1.8、问题：启动零信任时无快捷登录方式，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;随机输入一个用户名，再返回上一级，选择快捷登录方式，参考下图：&#10;&#10;1.9、问题：退出零信任后发现外网基本上不了例如：www.baidu.com&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&quot;&#10;1.19、问题：扫码登陆时认证失败 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;重新进入扫码登陆界面即可&#10;1.20、问题：登录了零信任，但是访问不了内网 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;1、确认电脑上没有IOA，或者有没登录IOA（建议卸载了，后续不会用了，原来限制的域名换到了新的零信任）&#10;2、处理掉IOA后，再次扫码登录零信任（退IOA前扫码了的话，也需要退出再扫一次码）&#10;3、登录超时了，退出零信任，重新登录&#10;参考下图：&#10;1.21、问题：开机进入系统很慢，运行慢，杀毒软件不断弹窗 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项&#10;1.22、问题：登录了零信任，点击应用提示“请求失败”  如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;退出零信任，重新登录&#10;1.23、问题：兼职老师登录零信任，应用列表是空白 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;因为零信任同步企微账号，分配组有问题，没有分配到与企微一致的组织架构下，而且分到默认组（需要绿盟排查原因），需要零信任管理员人工更改分组&#10;1.24、问题：部分应用无法访问，如ssoin.zy.com &#10;设备类型：&#10;mac&#10;解决方案：&#10;ping ssoin.zy.com的ip是10.12.81.44，但是在浏览器访问页面，发现请求ip是外网IP，暂未有解决根源的办法，临时办法：本地host绑定为10.12.81.44&#10;设备兼容性问题&#10;2.1、 问题：打开零信任扫码登录后提示开启私网DNS失败，请稍后重试&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;最佳设置&#10;1.2控制器地址：124.71.208.207&#10;&#10;1.3零信任软件推荐设置【重要：减少零信任被误关闭】&#10;&#10;2、零信任软件常见问题：&#10;1、提示不合法的用户名【返回上一级，选择快捷方式登录】&#10;提示会话已经过期，请重新登陆【返回上一级，选择快捷方式登录】&#10;扫码登录提示认证失败【返回上一级，选择快捷方式登录】&#10;&#10;2、登陆零信任后提示无无法访问此网页【关闭浏览器，重新登陆零信任并刷新策略】&#10;&#10;3、打开零信任扫码登录后提示开启私网DNS失败，请稍后重试【联系IT帮助台获取最新版本安装包并覆盖安装】&#10;&#10;4、网络及系统问题&#10;4.1退出零信任后无法访问外网【清除本地dns 127.0.0.1设置或修改为自动获取】&#10;macbook：&#10;Windwos：&#10;&#10;4.2退出零信任后可以登陆企微和微信，无法打开网页【修改Internet代理】&#10;&#10;4.3软件冲突--IOA【网络异常，卸载IOA（已不再使用）并重启电脑】&#10;&#10;4.3开机进入桌面很慢，自动弹窗警告【卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项】&#10;&#10;5、用户权限相关&#10;5.1打开零信任无OA访问窗口，空白&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;安全助手（零信任）客户端FAQ&#10;操作问题&#10;问题：登录零信任后访问应用时浏览器页面提示403forbidden，如下图：&#10;&#10;设备类型：&#10;Windows/macbook&#10;解决方案：&#10;使用其他浏览器访问&#10;设置浏览器后重新打开进行访问应用&#10;（1）Google浏览器&#10;&#10;（2）火狐浏览器&#10;&#10;问题：登录零信任后当访问应用时提示无法访问此网站，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10; 先关闭浏览器，点击刷新 重新获取策略（刷新一次未解决可以继续点击刷新）参考下图：&#10;&#10; 当a步骤重新获取策略后还是一样提示无法访问此网站时可退出登录零信任，再退出零信任客户端，重新打开扫码登录可参考下图：&#10;&#10;问题：打开零信任扫码登陆时，提示不合法的状态，如下图&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;a.返回上一级，去掉用户名，选择快捷方式登陆参考下图：&#10;&#10;1.4、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;返回上一级，重新选择快捷方式登陆&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.需要把本机网络的DNS127.0.0.1去掉即可，参考下图：&#10;&#10;1.10、问题：为什么我登录不了TMS、EVIP……，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;请先安装零信任，并扫码登录—登录后不能退出零信任&#10;参考下图：&#10;&#10;1.11、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;去到安装目录C:\Program Files (x86)\TrustCyberLink目录下打开TrustCyberLink.exe&#10;1.12、问题：打开零信任没有企业微信按钮 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新打开或者点击控制切换器—点击124.71.208.207或者sec.zy.com-点击确认即可&#10;1.13、问题：安装助手完成时零信任未安装成功 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新安装即可&#10;1.14、问题：提示 “由于找不到 UAADataCenter.dl，无法继续执行代码"/>
-        <filter val="重置通行证密码&#10;通行证使用时不带@zy.com的后缀&#10;通行证密码不是邮箱密码&#10;企微点击【工作台】-【IT服务台】-【更多功能】-【通行证密码重置】&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;08卓越在线常见问题QA&#10;&#10;答：如选择【学员家长登录】，密码为通行证密码果是密码有误，忘记密码的同学，&#10;&#10;⑤我是学生/家长，为何登录不进去&#10;答：如果是密码有误，那么选择【忘记密码】，或者【验证码登录】、【微信登录】&#10;即可；&#10;&#10;如果【验证码登录】失败，那么老师需要去TMS 查询，该学生当前登录使用的手机&#10;号是否是学生的通行证手机号，如果不是，复制TMS 里学生的手机号给家长，进行&#10;&#10;如果微信登录也登录失败，那么则可能是该微信没有绑定孩子的通行证，去TMS 查&#10;询该孩子并发送通行证二维码给家长进行微信扫码、重新绑定即可&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;TMK操作说明文档&#10;&#10;后台新增优惠券批次&#10;02 &#10;创建客服账号&#10;&#10;MK系统登录&#10;三种登录方式：&#10;1、输入通行证账号及密码，点击登录；&#10;账号登录&#10;&#10;2、点击右上角“二维码”，通过企业微信扫码；&#10;3、若无通行证账号，则需要通过“本地账号”&#10;登录，密码为管理员创建账号所设置的密码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【邮箱-4】重置邮箱密码&#10;重置密码：企业微信，点击【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;部分系统网址帐号密码&#10;系统类型：教学线; 系统名：E研发; 网址：pm.zy.com; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：E学校; 网址：sc.zy.com; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：E教学; 网址：zxx.zy.com/jx/; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：E教研; 网址：https://zxx.zy.com/jyy/resourceCenter; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：E测评; 网址：https://zxx.zy.com/assess-test/#/accountmanagement/index; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：在线测; 网址：https://zxx.zy.com/unitest-admin/; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：卓越在线; 网址：zxx.zy.com/op; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：华途加密; 网址：https://121.37.10.216:9444/dsm/admin/common/main —工作表1&#10;系统类型：教学线; 系统名：物流管理; 网址：http://www.opees.cn/ZX/ZX-login.aspx —工作表1&#10;系统类型：教学线; 系统名：教师库管理系统; 网址：https://teacher.beststudy.com/b/login; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：营运线; 系统名：TMS; 网址：tms.zy.com; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：营运线; 系统名：SCRM; 网址：https://yy.zy.com/scrm/#/dashboard; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：其他; 系统名：classin; 网址：https://console.eeo.cn/saas/school/index.html#/fullPage/Index —工作表1"/>
-        <filter val="安全助手(零信任）客户端FAQ&#10;参考下图：&#10;&#10;1.5、问题：打开零信任时提示连接控制器失败，如下图：&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;选择控制器切换124.71.208.207地址；&#10;&#10;b.如a步骤切换控制器地址依然不解决的情况下，可选择重置控制器再输入124.71.208.207参考下图：&#10;&#10;1.6、问题：启动零信任时提示JavaScript错误，无法正常启动，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.打开终端—sudo vi /etc/hosts文件下添加127.0.0.1 localhost&#10;&#10;1.7、问题：nslookup正常解析域名情况下，使用safari、火狐浏览器访问应用报403，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.更换Google浏览器，即可正常访问应用&#10;&#10;1.8、问题：启动零信任时无快捷登录方式，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;随机输入一个用户名，再返回上一级，选择快捷登录方式，参考下图：&#10;&#10;1.9、问题：退出零信任后发现外网基本上不了例如：www.baidu.com&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;最佳设置&#10;1.2控制器地址：124.71.208.207&#10;&#10;1.3零信任软件推荐设置【重要：减少零信任被误关闭】&#10;&#10;2、零信任软件常见问题：&#10;1、提示不合法的用户名【返回上一级，选择快捷方式登录】&#10;提示会话已经过期，请重新登陆【返回上一级，选择快捷方式登录】&#10;扫码登录提示认证失败【返回上一级，选择快捷方式登录】&#10;&#10;2、登陆零信任后提示无无法访问此网页【关闭浏览器，重新登陆零信任并刷新策略】&#10;&#10;3、打开零信任扫码登录后提示开启私网DNS失败，请稍后重试【联系IT帮助台获取最新版本安装包并覆盖安装】&#10;&#10;4、网络及系统问题&#10;4.1退出零信任后无法访问外网【清除本地dns 127.0.0.1设置或修改为自动获取】&#10;macbook：&#10;Windwos：&#10;&#10;4.2退出零信任后可以登陆企微和微信，无法打开网页【修改Internet代理】&#10;&#10;4.3软件冲突--IOA【网络异常，卸载IOA（已不再使用）并重启电脑】&#10;&#10;4.3开机进入桌面很慢，自动弹窗警告【卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项】&#10;&#10;5、用户权限相关&#10;5.1打开零信任无OA访问窗口，空白&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.需要把本机网络的DNS127.0.0.1去掉即可，参考下图：&#10;&#10;1.10、问题：为什么我登录不了TMS、EVIP……，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;请先安装零信任，并扫码登录—登录后不能退出零信任&#10;参考下图：&#10;&#10;1.11、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;去到安装目录C:\Program Files (x86)\TrustCyberLink目录下打开TrustCyberLink.exe&#10;1.12、问题：打开零信任没有企业微信按钮 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新打开或者点击控制切换器—点击124.71.208.207或者sec.zy.com-点击确认即可&#10;1.13、问题：安装助手完成时零信任未安装成功 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新安装即可&#10;1.14、问题：提示 “由于找不到 UAADataCenter.dl，无法继续执行代码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;安全助手（零信任）客户端FAQ&#10;操作问题&#10;问题：登录零信任后访问应用时浏览器页面提示403forbidden，如下图：&#10;&#10;设备类型：&#10;Windows/macbook&#10;解决方案：&#10;使用其他浏览器访问&#10;设置浏览器后重新打开进行访问应用&#10;（1）Google浏览器&#10;&#10;（2）火狐浏览器&#10;&#10;问题：登录零信任后当访问应用时提示无法访问此网站，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10; 先关闭浏览器，点击刷新 重新获取策略（刷新一次未解决可以继续点击刷新）参考下图：&#10;&#10; 当a步骤重新获取策略后还是一样提示无法访问此网站时可退出登录零信任，再退出零信任客户端，重新打开扫码登录可参考下图：&#10;&#10;问题：打开零信任扫码登陆时，提示不合法的状态，如下图&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;a.返回上一级，去掉用户名，选择快捷方式登陆参考下图：&#10;&#10;1.4、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;返回上一级，重新选择快捷方式登陆&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&quot;&#10;1.19、问题：扫码登陆时认证失败 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;重新进入扫码登陆界面即可&#10;1.20、问题：登录了零信任，但是访问不了内网 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;1、确认电脑上没有IOA，或者有没登录IOA（建议卸载了，后续不会用了，原来限制的域名换到了新的零信任）&#10;2、处理掉IOA后，再次扫码登录零信任（退IOA前扫码了的话，也需要退出再扫一次码）&#10;3、登录超时了，退出零信任，重新登录&#10;参考下图：&#10;1.21、问题：开机进入系统很慢，运行慢，杀毒软件不断弹窗 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项&#10;1.22、问题：登录了零信任，点击应用提示“请求失败”  如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;退出零信任，重新登录&#10;1.23、问题：兼职老师登录零信任，应用列表是空白 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;因为零信任同步企微账号，分配组有问题，没有分配到与企微一致的组织架构下，而且分到默认组（需要绿盟排查原因），需要零信任管理员人工更改分组&#10;1.24、问题：部分应用无法访问，如ssoin.zy.com &#10;设备类型：&#10;mac&#10;解决方案：&#10;ping ssoin.zy.com的ip是10.12.81.44，但是在浏览器访问页面，发现请求ip是外网IP，暂未有解决根源的办法，临时办法：本地host绑定为10.12.81.44&#10;设备兼容性问题&#10;2.1、 问题：打开零信任扫码登录后提示开启私网DNS失败，请稍后重试"/>
-        <filter val="重置通行证密码&#10;通行证使用时不带@zy.com的后缀&#10;通行证密码不是邮箱密码&#10;企微点击【工作台】-【IT服务台】-【更多功能】-【通行证密码重置】&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;系统操作指引&#10;&#10;三、E-研发操作指引&#10;1.登录系统&#10;E-研发网址：pm.zy.com 产品研发系统&#10;账号：内部通行证（姓名的拼音）&#10;密码：自己的通行证密码&#10;&#10;特别注意：使用账密登录需要3个月重置一次密码，如提示账号或密码错误，请点击“忘记密码”&#10;&#10;卓越教育丨E-研发&#10;这里切换账号登录&#10;企业微信扫码登录&#10;企业微信「扫一扫」，点击确认登录&#10;&#10;2.产品负责人操作指引：&#10;（1）新建产品：&#10;登陆后，您在【产品管理】模块下，点击产品列表上方的【新建产品】按钮&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;08卓越在线常见问题QA&#10;&#10;答：如选择【学员家长登录】，密码为通行证密码果是密码有误，忘记密码的同学，&#10;&#10;⑤我是学生/家长，为何登录不进去&#10;答：如果是密码有误，那么选择【忘记密码】，或者【验证码登录】、【微信登录】&#10;即可；&#10;&#10;如果【验证码登录】失败，那么老师需要去TMS 查询，该学生当前登录使用的手机&#10;号是否是学生的通行证手机号，如果不是，复制TMS 里学生的手机号给家长，进行&#10;&#10;如果微信登录也登录失败，那么则可能是该微信没有绑定孩子的通行证，去TMS 查&#10;询该孩子并发送通行证二维码给家长进行微信扫码、重新绑定即可&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【邮箱-4】重置邮箱密码&#10;重置密码：企业微信，点击【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;新伙伴入职指引3&#10;&#10;若密码失效，可以在企业微信-工作台-(搜索)IT服务台(打开)-(右下角)更多功能-邮箱密码重置&#10;办公设施指引: IT帮助台;办公设施指引: 无;办公设施指引: 无;办公设施指引: 若有其他个人无法解决的系统问题，可在企业微信上咨询‘IT帮助台’解决；&#10;访问方式：通讯录-卓越教育-员工服务-IT帮助台&#10;办公设施指引: 工卡制作;办公设施指引: 工卡照片将采用您在线填写个人信息时所上传的照片（待企业微信开通后，可以联系对应HR老师进行领取）;办公设施指引: 工卡照片将采用您在线填写个人信息时所上传的照片（待企业微信开通后，可以联系对应HR老师进行领取）;办公设施指引: 工卡照片将采用您在线填写个人信息时所上传的照片（待企业微信开通后，可以联系对应HR老师进行领取）&#10;办公设施指引: 内部推荐;办公设施指引: 登入【企业微信-工作台-人力磁-内部推荐】，内推合适人选，将有500-3000元奖励哦;办公设施指引: 登入【企业微信-工作台-人力磁-内部推荐】，内推合适人选，将有500-3000元奖励哦"/>
-        <filter val="安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;（2）双击点卸载&#10;&#10;（3）输入安全助手卸载码（e2vPsv8$）后，运行卸载&#10;&#10;4、零信任安装指引&#10;（1）双击点击安装包打开------&gt;点“是” ，如下图&#10;&#10;（2）点—&gt;我同意，如下图&#10;&#10;（3）选择安装位置（可自定义选择安装位置）默认即可，点击—&gt;安装，如下图&#10;&#10;（4）等待安装完成即可，如下图&#10;&#10;（5）安装完成默认勾选运行零信任，桌面可看到零信任图标，如下图&#10;&#10;(6)打开零信任扫码登录，即可通过浏览器访问内部系统，如下图&#10;&#10;(7)如果第一次安装提示需要输入控制器地址，请输入sec.zy.com或124.71.208.207，点击确认后扫码登录使用&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.需要把本机网络的DNS127.0.0.1去掉即可，参考下图：&#10;&#10;1.10、问题：为什么我登录不了TMS、EVIP……，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;请先安装零信任，并扫码登录—登录后不能退出零信任&#10;参考下图：&#10;&#10;1.11、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;去到安装目录C:\Program Files (x86)\TrustCyberLink目录下打开TrustCyberLink.exe&#10;1.12、问题：打开零信任没有企业微信按钮 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新打开或者点击控制切换器—点击124.71.208.207或者sec.zy.com-点击确认即可&#10;1.13、问题：安装助手完成时零信任未安装成功 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新安装即可&#10;1.14、问题：提示 “由于找不到 UAADataCenter.dl，无法继续执行代码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;安全助手卸载和零信任工具安装指引&#10;&#10;注明：先卸载安全助手，后安装零信任工具，如果没有安全助手，可覆盖安装零信任工具&#10;&#10;1、零信任工具下载链接：&#10;Windows版本：&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe  （新版本下载链接）  &#10;&#10;2、管理员口令和安全助手卸载码都是e2vPsv8$&#10;&#10;3、安全助手卸载指引&#10;3.1、第一种卸载方式&#10;（1） 右键安全助手图标，点击进入特权模式，输入管理员口令（e2vPsv8$)即可进入特权模式&#10;&#10;（2）进入特权模式后，在本地电脑C:\Windows\LVUAAgentInstBaseRoot找到此文件运行卸载 &#10;&#10;输入安全助手卸载码（卸载密码默认 e2vPsv8$）&#10;&#10;3.2、第二种卸载方式&#10;（1）若是Win10 系统点击左下角，找到并打开文件夹“UniAccess安全助手”，右键点击“启动或显示托盘图标 ”，点击更多，点击打开文件位置&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;最佳设置&#10;1.2控制器地址：124.71.208.207&#10;&#10;1.3零信任软件推荐设置【重要：减少零信任被误关闭】&#10;&#10;2、零信任软件常见问题：&#10;1、提示不合法的用户名【返回上一级，选择快捷方式登录】&#10;提示会话已经过期，请重新登陆【返回上一级，选择快捷方式登录】&#10;扫码登录提示认证失败【返回上一级，选择快捷方式登录】&#10;&#10;2、登陆零信任后提示无无法访问此网页【关闭浏览器，重新登陆零信任并刷新策略】&#10;&#10;3、打开零信任扫码登录后提示开启私网DNS失败，请稍后重试【联系IT帮助台获取最新版本安装包并覆盖安装】&#10;&#10;4、网络及系统问题&#10;4.1退出零信任后无法访问外网【清除本地dns 127.0.0.1设置或修改为自动获取】&#10;macbook：&#10;Windwos：&#10;&#10;4.2退出零信任后可以登陆企微和微信，无法打开网页【修改Internet代理】&#10;&#10;4.3软件冲突--IOA【网络异常，卸载IOA（已不再使用）并重启电脑】&#10;&#10;4.3开机进入桌面很慢，自动弹窗警告【卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项】&#10;&#10;5、用户权限相关&#10;5.1打开零信任无OA访问窗口，空白&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;&#10;答案：&gt;零信任sdp_engine进程损坏，下载sdp_engine.exe文件，并替换sdp_engine.exe文件，重新打开零信任扫码登录&#10;下载地址：https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/sdp_engine.exe&#10;插图：（如有）&#10;找到下载文件sdp_engine.exe，复制这个文件拷贝到零信任安装目录替换文件sdp_engine.exe，比如C:\Program Files (x86)\TrustCyberLink\resources\app\engine&#10;&#10;问题：MacBook电脑安装完零信任打开需要输入密码进行提权，密码提示不对问题&#10;答案：&gt;由于mac未设置足够权限给SDP客户端导致，需要添加零信任权限&#10;路径：设置-隐私与安全性-添加零信任程序开启SDP相关的权限即可&#10;插图：（如有）&#10;&#10;如解决方法一仍然提示密码错误，检查密码是否有字符串，有的话把字符串修改后再重新打开，输入密码进行提取"/>
-        <filter val="【打印机-8】Windows系统安装京瓷打印机指引&#10;一、下载打印机驱动包存到电脑硬盘上&#10;驱动包下载地址：京瓷打印机驱动下载&#10;二、安装打印机&#10;注：安装前需要先收集打印机IP地址和型号（部分共用的打印机需要准备部门密码）&#10;打印机IP地址，图示&#10;&#10;查询打印机型号，图示&#10;&#10;1、解压驱动包&#10;&#10;2、打开安装程序, 按步骤安装&#10;进入文件夹，双击Setup.exe&#10;&#10;接受，选择自定义安装&#10;&#10;以下内容请根据打印机实际型号和IP填写&#10;&#10;添加打印机驱动和安装升级的组件&#10;&#10;打印机安装完成&#10;&#10;三、设置打印机&#10;1、修改名称、设置双面打印&#10;打开计算机，跳至控制面板，进入硬件设备&#10;&#10;右击，打印机属性&#10;&#10;修改打印机名称&#10;&#10;设置双面打印&#10;&#10;2、打印机显示脱机时，需要设置取消SNMP&#10;&#10;3、添加部门id&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-3】MAC 连接打印机操作指引&#10;一、下载驱动包&#10;京瓷打印机mac系统驱动下载&#10;&#10;注：安装前需要先知道打印机IP地址，如下图所示：&#10;&#10;安装驱动&#10;双击驱动包&#10;&#10;若在桌面没有找到驱动，则使用“command+空格键”弹出的搜索框里输入“Kyocera OS X 10.9+ Web build 2024.05.16”，找到并双击驱动包&#10;&#10;双击安装程序&#10;&#10;一路安装&#10;&#10;安装完成后，需要重启电脑!!!&#10;&#10;二、添加打印机&#10;进入系统偏好设置&#10;&#10;进入打印机与扫描仪&#10;&#10;添加设置&#10;&#10;选择IP连接，输入对应打印机IP地址，选择连接协议&#10;&#10;（若电脑无法自动识别打印机型号，请检查打印机是否出现网络问题，例如网线松动等）&#10;&#10;完成添加，可以进行打印&#10;三、各协议解释&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-5】MAC系统添加一体打印机部门ID&#10;操作前请先确认是否已安装好打印机驱动，以下步骤需要安装好驱动才能实现&#10;操作步骤：&#10;打开前往&gt;应用程序，在应用程序中找到打印机程序并双击打开&#10;&#10;2、选对应IP打印机&#10;&#10;3、添加部门ID&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址： http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;打印机-理光、富士施乐、佳能驱动下载链接&#10;理光MPC5503：&#10;http://support.ricoh.com/bb/html/dr_ut_e/rcn1/model/mpc4503/mpc4503.htm&#10;&#10;理光MP6054：&#10;http://support.ricoh.com/bb/html/dr_ut_e/rcn1/model/mp2554/mp2554.htm?lang=cn&#10;&#10;富士施乐P288：&#10;https://m3support-fb.fujifilm-fb.com.cn/driver_downloads/www/&#10;&#10;富士施乐M288：&#10;https://m3support-fb.fujifilm-fb.com.cn/driver_downloads/www/&#10;&#10;佳能MF244/MF249（通用）：&#10;https://www.canon.com.cn/supports/download/sims/list/slist?fileTypeId=23&amp;categoryId=15&amp;seriesId=77&amp;modelId=1234&amp;OSName=Windows%2010%20(x64)&amp;channel=1&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;悦智学打印指引手册-打印机插件安装-0604&#10;打印机安装插件指引&#10;1. 打开火狐浏览器&#10;在地址栏输入：about:config 2. &#10;3. 在搜索框搜索：security.tls.version.min &#10;5. TMS点击执行安装&#10;&#10;警告：面临潜在的安全风险&#10;Firefox检测到潜在的安全威胁，因此没有继续访问localhost若您访问此网站，攻击者可能会尝试&#10;详细了解"/>
-        <filter val="263邮箱使用指引&#10;如下图：&#10;&#10;2.2 捆绑263邮箱的旧手机号码已注销或不能收取短信验证码，需要在OA系统上发起账户/权限申请】流程进行捆绑手机号码的变更，按以下步骤操作：&#10;2.2.1登录OA系统，点击【发起流程】-【IT类】-【IT服务】-【账户/权限申请】，“系统”选择“263企业邮箱 ”，“描述”写清楚你的需求&#10;&#10;忘记263邮箱密码/修改263邮箱密码&#10;登录企业微信-【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】，如下图：&#10;&#10;企业微信绑定263邮箱进行使用&#10;登录企业微信-【工作台】-【263企业邮箱】，输入邮箱和密码就可以完成绑定&#10;重置邮箱密码之后也需要重新捆绑企业微信才可以正常使用&#10;&#10;登录263邮箱时候提示：用户邮箱状态异常&#10;需要先登录企业微信-【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】进行密码重置，然后再进行微信绑定&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【邮箱-12】263邮箱设置--Macbook 邮件篇&#10;【修改263邮箱登陆密码】&#10;&#10;【忘记邮箱密码重置办法】&#10;重置密码：企业微信，点击【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】&#10;&#10;【Macbook 邮件更新密码步骤】&#10;&#10;【Macbook 邮件客户端配置263邮箱步骤】&#10;&#10;按图补充1~3点信息&#10;&#10;设置完成，测试邮件收发&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【邮箱-10】263邮箱设置--Outlook篇&#10;【修改263邮箱登陆密码】&#10;&#10;【忘记邮箱密码重置办法】&#10;打开企业微信搜索【IT服务台】，更多功能→重置邮箱密码，按页面步骤进行密码修改&#10;&#10;【Outlook更新密码】&#10;&#10;【Outlook 邮件客户端配置263邮箱步骤】&#10;&#10;设置完成，测试邮件收发&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【邮箱-11】263邮箱设置--Foxmail篇&#10;1、【修改263邮箱登陆密码】&#10;&#10;2、【忘记邮箱密码重置办法】&#10;重置密码：企业微信，点击【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】&#10;&#10;3、【Foxmail更新密码】&#10;&#10;4、【Foxmail 邮件客户端配置263邮箱步骤】&#10;Foxmail 邮件客户端下载：https://www.foxmail.com/&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;问题：263企业邮箱修改密码&#10;答案：自助修改密码路径：企业微信 &gt; 工作台 &gt; IT服务台 &gt; 更多功能 &gt;邮箱密码重置&#10;插图：&#10;&#10;问题：263企业邮箱修改密码（已绑定手机）&#10;答案：打开网址https://mm.263.com/wm2e/website/jsp/resetPassword.jsp&#10;插图：&#10;&#10;问题：263企业邮箱网页登陆地址&#10;答案：登陆网址https://www.263.net&#10;插图：&#10;&#10;问题：263企业邮箱修改密码规则&#10;答案：密码需要包含大小写、数字、符号，长度不小于8位，不能使用连续的字符，不能使用简单密码&#10;插图：&#10;&#10;问题：263企业邮箱客户端服务器地址&#10;答案：建议使用IMAP+SMTP组合，详情见附图&#10;插图：&#10;&#10;问题：如何在苹果mail邮件客户端中设置IMAP收发邮件"/>
-        <filter val="绩效系统操作手册（经理）-绩效评估篇V3&#10;&#10;绩效校准—&#10;—提交结果&#10;审核范围内所有人员的总等级确定后，可以查看到绩效等级的分布人数，确认无误后，点击“全部选&#10;&#10;结果提交后，会进入员工确认页面，员工可看到本次考核的等级及总评语，但不会看到调整内容&#10;&#10;绩效校准&#10;特殊情况处理&#10;&#10;Q1：我/我的团队成员刚转正，应该如何在系统中制定&#10;绩效计划&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【希沃白板-35】直播间初始化异常，请重试&#10;问题现象、&#10;进入云课堂教室，弹出如下提示，无法进入直播间&#10;&#10;可能原因&#10;系统组件异常&#10;解决方法&#10;退出希沃白板：系统右下角找到希沃白板图标，鼠标右键单击，选择退出；&#10;下载并安装修复工具：下载附件中的 EnableFipsAlgorithmPolicy.zip 文件，解压后双击运行其中的程序&#10;重启希沃白板：双击桌面上的 “希沃白板 5”图标，重启希沃白板软件&#10;附件下载EnableFipsAlgorithmPolicy.zip&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;绩效系统操作手册（经理）-绩效评估篇V3&#10;&#10;点击【我的待办】或者右上角的“小信封”图标，进入绩效待办事项&#10;&#10;直接上级评估&#10;进入待办列表页面，点击对应员工的姓名，可进入绩效详情页进行打分&#10;&#10;评估卓越教育2025年中非教绩效评估&#10;&#10;直接上级评估&#10;系统设置是与原绩效套表一致，评分对应绩效等级&#10;&#10;直接上级评估—工作成果评估&#10;进入评估页面后，对该员工的工作成果及关键绩效行为进行等级评定及填写评语（选填）&#10;&#10;在员工本人列可以看到员工自评的等级以及自我评语&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;绩效系统操作手册（员工）-2025目标管理篇&#10;&#10;绩效君测试部门&#10;查看历史目标&gt;&#10;仕务2&#10;十添加对齐&#10;计应为100%，否则无法&#10;提交&#10;2、绩效目标审批通过后&#10;+手动添加从指标库引入 复制目标&#10;1个人发展目标&#10;参考关键绩效行为或专业能力要求列出1或2个&#10;十添加对齐&#10;撤回功能&#10;&#10;注意&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;绩效系统操作手册（经理）-绩效评估篇V3&#10;&#10;绩效校准&#10;特殊情况处理&#10;&#10;绩效校准&#10;绩效校准在系统中的步骤称为“结果审核”，是基于绩效校准会的绩效结果校准，一般由团队负责&#10;人或部门负责人操作点击【我的待办】或者右上角的“小信封”图标，进入绩效校准页面&#10;&#10;绩效校准—查看当前等级分布情况&#10;进入结果审核页面，可查看每个等级下的人员等级情况，通过筛选条件，选择不同的部门、职级，&#10;应强分组人员的分布情况，方便您查看不同团队的等级分布情况，以及校准不同团队的绩效&#10;查看相结果"/>
-        <filter val="【打印机-8】Windows系统安装京瓷打印机指引&#10;一、下载打印机驱动包存到电脑硬盘上&#10;驱动包下载地址：京瓷打印机驱动下载&#10;二、安装打印机&#10;注：安装前需要先收集打印机IP地址和型号（部分共用的打印机需要准备部门密码）&#10;打印机IP地址，图示&#10;&#10;查询打印机型号，图示&#10;&#10;1、解压驱动包&#10;&#10;2、打开安装程序, 按步骤安装&#10;进入文件夹，双击Setup.exe&#10;&#10;接受，选择自定义安装&#10;&#10;以下内容请根据打印机实际型号和IP填写&#10;&#10;添加打印机驱动和安装升级的组件&#10;&#10;打印机安装完成&#10;&#10;三、设置打印机&#10;1、修改名称、设置双面打印&#10;打开计算机，跳至控制面板，进入硬件设备&#10;&#10;右击，打印机属性&#10;&#10;修改打印机名称&#10;&#10;设置双面打印&#10;&#10;2、打印机显示脱机时，需要设置取消SNMP&#10;&#10;3、添加部门id&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-3】MAC 连接打印机操作指引&#10;一、下载驱动包&#10;京瓷打印机mac系统驱动下载&#10;&#10;注：安装前需要先知道打印机IP地址，如下图所示：&#10;&#10;安装驱动&#10;双击驱动包&#10;&#10;若在桌面没有找到驱动，则使用“command+空格键”弹出的搜索框里输入“Kyocera OS X 10.9+ Web build 2024.05.16”，找到并双击驱动包&#10;&#10;双击安装程序&#10;&#10;一路安装&#10;&#10;安装完成后，需要重启电脑!!!&#10;&#10;二、添加打印机&#10;进入系统偏好设置&#10;&#10;进入打印机与扫描仪&#10;&#10;添加设置&#10;&#10;选择IP连接，输入对应打印机IP地址，选择连接协议&#10;&#10;（若电脑无法自动识别打印机型号，请检查打印机是否出现网络问题，例如网线松动等）&#10;&#10;完成添加，可以进行打印&#10;三、各协议解释&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-5】MAC系统添加一体打印机部门ID&#10;操作前请先确认是否已安装好打印机驱动，以下步骤需要安装好驱动才能实现&#10;操作步骤：&#10;打开前往&gt;应用程序，在应用程序中找到打印机程序并双击打开&#10;&#10;2、选对应IP打印机&#10;&#10;3、添加部门ID&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址： http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;悦智学打印指引手册-打印机插件安装-0604&#10;打印机安装插件指引&#10;1. 打开火狐浏览器&#10;在地址栏输入：about:config 2. &#10;3. 在搜索框搜索：security.tls.version.min &#10;5. TMS点击执行安装&#10;&#10;警告：面临潜在的安全风险&#10;Firefox检测到潜在的安全威胁，因此没有继续访问localhost若您访问此网站，攻击者可能会尝试&#10;详细了解&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;打印机-理光、富士施乐、佳能驱动下载链接&#10;理光MPC5503：&#10;http://support.ricoh.com/bb/html/dr_ut_e/rcn1/model/mpc4503/mpc4503.htm&#10;&#10;理光MP6054：&#10;http://support.ricoh.com/bb/html/dr_ut_e/rcn1/model/mp2554/mp2554.htm?lang=cn&#10;&#10;富士施乐P288：&#10;https://m3support-fb.fujifilm-fb.com.cn/driver_downloads/www/&#10;&#10;富士施乐M288：&#10;https://m3support-fb.fujifilm-fb.com.cn/driver_downloads/www/&#10;&#10;佳能MF244/MF249（通用）：&#10;https://www.canon.com.cn/supports/download/sims/list/slist?fileTypeId=23&amp;categoryId=15&amp;seriesId=77&amp;modelId=1234&amp;OSName=Windows%2010%20(x64)&amp;channel=1"/>
-        <filter val="安全助手(零信任）客户端FAQ&#10;参考下图：&#10;&#10;1.5、问题：打开零信任时提示连接控制器失败，如下图：&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;选择控制器切换124.71.208.207地址；&#10;&#10;b.如a步骤切换控制器地址依然不解决的情况下，可选择重置控制器再输入124.71.208.207参考下图：&#10;&#10;1.6、问题：启动零信任时提示JavaScript错误，无法正常启动，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.打开终端—sudo vi /etc/hosts文件下添加127.0.0.1 localhost&#10;&#10;1.7、问题：nslookup正常解析域名情况下，使用safari、火狐浏览器访问应用报403，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.更换Google浏览器，即可正常访问应用&#10;&#10;1.8、问题：启动零信任时无快捷登录方式，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;随机输入一个用户名，再返回上一级，选择快捷登录方式，参考下图：&#10;&#10;1.9、问题：退出零信任后发现外网基本上不了例如：www.baidu.com&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;安全助手（零信任）客户端FAQ&#10;操作问题&#10;问题：登录零信任后访问应用时浏览器页面提示403forbidden，如下图：&#10;&#10;设备类型：&#10;Windows/macbook&#10;解决方案：&#10;使用其他浏览器访问&#10;设置浏览器后重新打开进行访问应用&#10;（1）Google浏览器&#10;&#10;（2）火狐浏览器&#10;&#10;问题：登录零信任后当访问应用时提示无法访问此网站，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10; 先关闭浏览器，点击刷新 重新获取策略（刷新一次未解决可以继续点击刷新）参考下图：&#10;&#10; 当a步骤重新获取策略后还是一样提示无法访问此网站时可退出登录零信任，再退出零信任客户端，重新打开扫码登录可参考下图：&#10;&#10;问题：打开零信任扫码登陆时，提示不合法的状态，如下图&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;a.返回上一级，去掉用户名，选择快捷方式登陆参考下图：&#10;&#10;1.4、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;返回上一级，重新选择快捷方式登陆&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;最佳设置&#10;1.2控制器地址：124.71.208.207&#10;&#10;1.3零信任软件推荐设置【重要：减少零信任被误关闭】&#10;&#10;2、零信任软件常见问题：&#10;1、提示不合法的用户名【返回上一级，选择快捷方式登录】&#10;提示会话已经过期，请重新登陆【返回上一级，选择快捷方式登录】&#10;扫码登录提示认证失败【返回上一级，选择快捷方式登录】&#10;&#10;2、登陆零信任后提示无无法访问此网页【关闭浏览器，重新登陆零信任并刷新策略】&#10;&#10;3、打开零信任扫码登录后提示开启私网DNS失败，请稍后重试【联系IT帮助台获取最新版本安装包并覆盖安装】&#10;&#10;4、网络及系统问题&#10;4.1退出零信任后无法访问外网【清除本地dns 127.0.0.1设置或修改为自动获取】&#10;macbook：&#10;Windwos：&#10;&#10;4.2退出零信任后可以登陆企微和微信，无法打开网页【修改Internet代理】&#10;&#10;4.3软件冲突--IOA【网络异常，卸载IOA（已不再使用）并重启电脑】&#10;&#10;4.3开机进入桌面很慢，自动弹窗警告【卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项】&#10;&#10;5、用户权限相关&#10;5.1打开零信任无OA访问窗口，空白&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&quot;&#10;1.19、问题：扫码登陆时认证失败 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;重新进入扫码登陆界面即可&#10;1.20、问题：登录了零信任，但是访问不了内网 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;1、确认电脑上没有IOA，或者有没登录IOA（建议卸载了，后续不会用了，原来限制的域名换到了新的零信任）&#10;2、处理掉IOA后，再次扫码登录零信任（退IOA前扫码了的话，也需要退出再扫一次码）&#10;3、登录超时了，退出零信任，重新登录&#10;参考下图：&#10;1.21、问题：开机进入系统很慢，运行慢，杀毒软件不断弹窗 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项&#10;1.22、问题：登录了零信任，点击应用提示“请求失败”  如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;退出零信任，重新登录&#10;1.23、问题：兼职老师登录零信任，应用列表是空白 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;因为零信任同步企微账号，分配组有问题，没有分配到与企微一致的组织架构下，而且分到默认组（需要绿盟排查原因），需要零信任管理员人工更改分组&#10;1.24、问题：部分应用无法访问，如ssoin.zy.com &#10;设备类型：&#10;mac&#10;解决方案：&#10;ping ssoin.zy.com的ip是10.12.81.44，但是在浏览器访问页面，发现请求ip是外网IP，暂未有解决根源的办法，临时办法：本地host绑定为10.12.81.44&#10;设备兼容性问题&#10;2.1、 问题：打开零信任扫码登录后提示开启私网DNS失败，请稍后重试&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.需要把本机网络的DNS127.0.0.1去掉即可，参考下图：&#10;&#10;1.10、问题：为什么我登录不了TMS、EVIP……，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;请先安装零信任，并扫码登录—登录后不能退出零信任&#10;参考下图：&#10;&#10;1.11、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;去到安装目录C:\Program Files (x86)\TrustCyberLink目录下打开TrustCyberLink.exe&#10;1.12、问题：打开零信任没有企业微信按钮 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新打开或者点击控制切换器—点击124.71.208.207或者sec.zy.com-点击确认即可&#10;1.13、问题：安装助手完成时零信任未安装成功 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新安装即可&#10;1.14、问题：提示 “由于找不到 UAADataCenter.dl，无法继续执行代码"/>
-        <filter val="安全助手(零信任）客户端FAQ&#10;参考下图：&#10;&#10;1.5、问题：打开零信任时提示连接控制器失败，如下图：&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;选择控制器切换124.71.208.207地址；&#10;&#10;b.如a步骤切换控制器地址依然不解决的情况下，可选择重置控制器再输入124.71.208.207参考下图：&#10;&#10;1.6、问题：启动零信任时提示JavaScript错误，无法正常启动，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.打开终端—sudo vi /etc/hosts文件下添加127.0.0.1 localhost&#10;&#10;1.7、问题：nslookup正常解析域名情况下，使用safari、火狐浏览器访问应用报403，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.更换Google浏览器，即可正常访问应用&#10;&#10;1.8、问题：启动零信任时无快捷登录方式，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;随机输入一个用户名，再返回上一级，选择快捷登录方式，参考下图：&#10;&#10;1.9、问题：退出零信任后发现外网基本上不了例如：www.baidu.com&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;最佳设置&#10;1.2控制器地址：124.71.208.207&#10;&#10;1.3零信任软件推荐设置【重要：减少零信任被误关闭】&#10;&#10;2、零信任软件常见问题：&#10;1、提示不合法的用户名【返回上一级，选择快捷方式登录】&#10;提示会话已经过期，请重新登陆【返回上一级，选择快捷方式登录】&#10;扫码登录提示认证失败【返回上一级，选择快捷方式登录】&#10;&#10;2、登陆零信任后提示无无法访问此网页【关闭浏览器，重新登陆零信任并刷新策略】&#10;&#10;3、打开零信任扫码登录后提示开启私网DNS失败，请稍后重试【联系IT帮助台获取最新版本安装包并覆盖安装】&#10;&#10;4、网络及系统问题&#10;4.1退出零信任后无法访问外网【清除本地dns 127.0.0.1设置或修改为自动获取】&#10;macbook：&#10;Windwos：&#10;&#10;4.2退出零信任后可以登陆企微和微信，无法打开网页【修改Internet代理】&#10;&#10;4.3软件冲突--IOA【网络异常，卸载IOA（已不再使用）并重启电脑】&#10;&#10;4.3开机进入桌面很慢，自动弹窗警告【卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项】&#10;&#10;5、用户权限相关&#10;5.1打开零信任无OA访问窗口，空白&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.需要把本机网络的DNS127.0.0.1去掉即可，参考下图：&#10;&#10;1.10、问题：为什么我登录不了TMS、EVIP……，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;请先安装零信任，并扫码登录—登录后不能退出零信任&#10;参考下图：&#10;&#10;1.11、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;去到安装目录C:\Program Files (x86)\TrustCyberLink目录下打开TrustCyberLink.exe&#10;1.12、问题：打开零信任没有企业微信按钮 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新打开或者点击控制切换器—点击124.71.208.207或者sec.zy.com-点击确认即可&#10;1.13、问题：安装助手完成时零信任未安装成功 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新安装即可&#10;1.14、问题：提示 “由于找不到 UAADataCenter.dl，无法继续执行代码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;安全助手（零信任）客户端FAQ&#10;操作问题&#10;问题：登录零信任后访问应用时浏览器页面提示403forbidden，如下图：&#10;&#10;设备类型：&#10;Windows/macbook&#10;解决方案：&#10;使用其他浏览器访问&#10;设置浏览器后重新打开进行访问应用&#10;（1）Google浏览器&#10;&#10;（2）火狐浏览器&#10;&#10;问题：登录零信任后当访问应用时提示无法访问此网站，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10; 先关闭浏览器，点击刷新 重新获取策略（刷新一次未解决可以继续点击刷新）参考下图：&#10;&#10; 当a步骤重新获取策略后还是一样提示无法访问此网站时可退出登录零信任，再退出零信任客户端，重新打开扫码登录可参考下图：&#10;&#10;问题：打开零信任扫码登陆时，提示不合法的状态，如下图&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;a.返回上一级，去掉用户名，选择快捷方式登陆参考下图：&#10;&#10;1.4、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;返回上一级，重新选择快捷方式登陆&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;&#10;答案：&gt;零信任sdp_engine进程损坏，下载sdp_engine.exe文件，并替换sdp_engine.exe文件，重新打开零信任扫码登录&#10;下载地址：https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/sdp_engine.exe&#10;插图：（如有）&#10;找到下载文件sdp_engine.exe，复制这个文件拷贝到零信任安装目录替换文件sdp_engine.exe，比如C:\Program Files (x86)\TrustCyberLink\resources\app\engine&#10;&#10;问题：MacBook电脑安装完零信任打开需要输入密码进行提权，密码提示不对问题&#10;答案：&gt;由于mac未设置足够权限给SDP客户端导致，需要添加零信任权限&#10;路径：设置-隐私与安全性-添加零信任程序开启SDP相关的权限即可&#10;插图：（如有）&#10;&#10;如解决方法一仍然提示密码错误，检查密码是否有字符串，有的话把字符串修改后再重新打开，输入密码进行提取"/>
-        <filter val="【日常使用-12】C盘空间满了该如何清理&#10;方法一：&#10;win—&gt;磁盘清理&#10;&#10;方法二：&#10; 转移微信的个人数据文件&#10;  微信—&gt;设置—&gt;文件管理—&gt;文件管理（微信个人数据文件就在这个文件夹里）—&gt;更改 更改至 C盘 以外的盘符）&#10;   更改完成后C盘就会释放出很多的空间&#10;&#10;方法三：&#10;转移企微的个人数据文件&#10;企微—设置—存储管理&#10;&#10;方法四：&#10; win+r—%temp%  全选删除&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【一体机-7】教学一体机一键清理D盘文件指引&#10;在打开一体机的“此电脑”&#10;打开D盘&#10;在D盘下找到“清理D盘.bat”，双击运行清理工具&#10;&#10;清理工具运行中，请勿点击黑框，会停止运行&#10;&#10;清理结束标志“垃圾文件清理成功”，按任意键退出&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）"/>
-        <filter val="【监控-1】Edge浏览器查看监控&#10;指引文档介绍&#10;使用浏览器查看校区监控，需要满足以下要求：&#10;1.1、电脑系统：Win10以上版本；&#10;1.2、浏览器：Edge浏览器的Internet Explorer 模式&#10;Edge浏览器的设置步骤&#10;打开Edge浏览器，点击右上角的三个点，打开设置&#10;&#10;2、在搜索框输入：Explorer&#10;&#10;3、往下滑动找到‘允许在Internet Explorer模式下重新加载网站(IE模式)’选择允许&#10;&#10;4、右上角的三个点里面就会添加一个‘在Intermet Explorer模式下重新加载’&#10;&#10;5、在网页搜索框里面输入监控IP地址192.168.0.X（X范围一般为5~10）&#10;&#10;进入到登录界面后，先点击右上角三个点 选择在‘Intermet Explorer模式下重新加载’，再输入账号密码登录即可&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【监控-2】监控系统客户端安装指引&#10;（一）客户端下载地址&#10;iVMS-4200客户端下载地址（复制到浏览器打开并下载）：https://partners.hikvision.com/tools/tooldetail?id=599912121330368512&#10;&#10;（二）客户端安装步骤&#10;右击ivms-4200海康软件，选择【以管理员身份运行】选项，选择【是】&#10;&#10;勾选【我接受许可证协议条款】，然后单击【下一步】按钮&#10;&#10;如下图：“请选择要安装的功能”只需要勾选【视频】，“目标文件夹”选择切换到非C盘安装，然后单击【安装】按钮&#10;&#10;（三）设置账号和密码&#10;设置监控用户名：user ，密码：345110jk密保问题可以统一档案是1&#10;&#10;添加录像机&#10;设备管理—设备&#10;&#10;(有回放功能)普通用户1:userxq密码:345110xq&#10;(无回放功能)普通用户2:user密码:345110jk &#10;&#10;（五）主预览和远程回放&#10;打开程序默认进入主预览界面，如下图所示&#10;&#10;远程回放操作&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【监控-6】ivms-4200 Lite监控客户端设置&#10;添加校区监控&#10;&#10;设置 &#10;改成ntp.aliyun.com，防止IP变更（新装监控默认没设置）&#10;&#10;(有回放功能)普通用户1:  userxq  密码: 345110xq&#10;(无回放功能)普通用户2:  user  密码:  345110jk&#10;&#10;存储设置（默认）&#10;&#10;所有通道开启移动侦测，灵敏度4，布放打开（每个通道都要手动点一次）&#10;&#10;启动视频信号丢失功能，邮件联动（每个通道都要手动设置）&#10;&#10;异常报警，邮件联动&#10;设置移动侦测录像计划&#10;摄像头画面清晰度设置（不同型号的摄像头，可设置参数不一样，如出现有摄像头不能同时生效，需要再另外分批再设置一次）&#10;通过客户端给摄像头改名字&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【监控-3】校区监控录像操作(客户端版)&#10;双击桌面快捷方式iVMs-4200 Lite 客户端&#10;&#10;打开程序默认进入主预览界面，如下图所示&#10;&#10;3、 远程回放操作&#10;&#10;4、录像文件下载与保存位置（此操作需要先完成第3步）&#10;&#10;注：下载完的录像文件，存放于 C:\user\zy(当前用户)\video下，若没有找到，请查检是否下载完成或重新下载&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;监控系统客户端安装指引&#10;&#10;（六）录像文件下载与保存&#10;录像文件下载与保存位置（此操作需要先完成第3步）&#10;&#10;注：下载完的录像文件，存放于 C:\user\zy(当前用户)\video下，若没有找到，请查检是否下载完成或重新下载&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）"/>
-        <filter val="【监控-2】监控系统客户端安装指引&#10;（一）客户端下载地址&#10;iVMS-4200客户端下载地址（复制到浏览器打开并下载）：https://partners.hikvision.com/tools/tooldetail?id=599912121330368512&#10;&#10;（二）客户端安装步骤&#10;右击ivms-4200海康软件，选择【以管理员身份运行】选项，选择【是】&#10;&#10;勾选【我接受许可证协议条款】，然后单击【下一步】按钮&#10;&#10;如下图：“请选择要安装的功能”只需要勾选【视频】，“目标文件夹”选择切换到非C盘安装，然后单击【安装】按钮&#10;&#10;（三）设置账号和密码&#10;设置监控用户名：user ，密码：345110jk密保问题可以统一档案是1&#10;&#10;添加录像机&#10;设备管理—设备&#10;&#10;(有回放功能)普通用户1:userxq密码:345110xq&#10;(无回放功能)普通用户2:user密码:345110jk &#10;&#10;（五）主预览和远程回放&#10;打开程序默认进入主预览界面，如下图所示&#10;&#10;远程回放操作&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;云桌面及CMS用户手册&#10;&#10;Windows客户端&#10;&#10;下载安装MacOS客户端&#10;【操作步骤】&#10;解压下载安装包并双击准备好的锐捷工作空间安装包&#10;右键打开安装&#10;&#10;设置功能&#10;说明&#10;后续操作均以Windows客户端为例&#10;&#10;产品/版本支持情况&#10;MacOS客户端设置界面中仅包含“连接设置”、“登录设置”、“通用设置”和“软件信息”&#10;&#10;【前置条件】&#10;管理员已经部署好RG-CDC平台&#10;连接服务器&#10;【应用场景】&#10;用户安装锐捷工作空间后，需要更改服务器信息，可以通过连接设置功能更改服务器地址&#10;【操作步骤】&#10;在登录页面点击&lt;设置&gt;按钮，在弹出的[连接设置]页面设置服务器地址&#10;说明&#10;服务器与客户端在同一局域网：只需设置服务器地址&#10;服务器与客户端不在同一局域网：除了设置服务器地址之外，还需设置安全访问网关地址、端口以及是否开启内外网免切换&#10;&#10;设置服务器&#10;&#10;设置完成后，返回登录页面查看登录状态若无法连接服务器，可以通过客户端左下角重新配置服务器地址&#10;&#10;升级客户端&#10;【应用场景】&#10;用户可以开启自动更新功能，以确保始终无缝接入最新版本，免去手动下载和安装的繁琐步骤&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;云桌面及CMS用户手册&#10;&#10;请求协助/取消协助：开启请求协助后，RG-CDC管理平台会收到远程协助消息，管理员可以随时远程到此云桌面取消协助后，RG-CDC管理平台会收到取消协助消息，管理员无法直接远程到此桌面&#10;特殊按键：由于键盘特殊按会调出本地PC的系统程序，若要调用云桌面系统程序，可根据实际需求选择对应特殊按键&#10;分辨率设置：进入云桌面后，分辨率默认为自适应用户可以根据需求点击&lt;分辨率设置&gt;按钮进行分辨率自定义设置&#10;剪贴板：可将文字复制到云桌面，复制成功后可以在云桌面右键粘贴至任意地方&#10;&#10;登出网页客户端&#10;当用户需要更换登录账号时，可在云桌面列表界面上，点击&lt;注销&gt;按钮，回到登录界面&#10;注销&#10;&#10;使用桌面客户端&#10;安装锐捷工作空间&#10;在浏览器输入 https://121.14.61.33:25910/webclient/#/login ，点击&lt;下载客户端&gt;&#10;&#10;根据需要选择下载客户端版本&#10;&#10;下载安装Windows客户端&#10;【操作步骤】&#10;点击下载Windows客户端&#10;下载完成后，解压压缩包并双击打开锐捷工作空间安装包，勾选同意《用户协议》并选择路径后，开始安装&#10;等待安装完成，为保证功能正常使用需要重启"/>
-        <filter val="安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;安全助手卸载和零信任工具安装指引&#10;&#10;注明：先卸载安全助手，后安装零信任工具，如果没有安全助手，可覆盖安装零信任工具&#10;&#10;1、零信任工具下载链接：&#10;Windows版本：&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe  （新版本下载链接）  &#10;&#10;2、管理员口令和安全助手卸载码都是e2vPsv8$&#10;&#10;3、安全助手卸载指引&#10;3.1、第一种卸载方式&#10;（1） 右键安全助手图标，点击进入特权模式，输入管理员口令（e2vPsv8$)即可进入特权模式&#10;&#10;（2）进入特权模式后，在本地电脑C:\Windows\LVUAAgentInstBaseRoot找到此文件运行卸载 &#10;&#10;输入安全助手卸载码（卸载密码默认 e2vPsv8$）&#10;&#10;3.2、第二种卸载方式&#10;（1）若是Win10 系统点击左下角，找到并打开文件夹“UniAccess安全助手”，右键点击“启动或显示托盘图标 ”，点击更多，点击打开文件位置&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;（2）双击点卸载&#10;&#10;（3）输入安全助手卸载码（e2vPsv8$）后，运行卸载&#10;&#10;4、零信任安装指引&#10;（1）双击点击安装包打开------&gt;点“是” ，如下图&#10;&#10;（2）点—&gt;我同意，如下图&#10;&#10;（3）选择安装位置（可自定义选择安装位置）默认即可，点击—&gt;安装，如下图&#10;&#10;（4）等待安装完成即可，如下图&#10;&#10;（5）安装完成默认勾选运行零信任，桌面可看到零信任图标，如下图&#10;&#10;(6)打开零信任扫码登录，即可通过浏览器访问内部系统，如下图&#10;&#10;(7)如果第一次安装提示需要输入控制器地址，请输入sec.zy.com或124.71.208.207，点击确认后扫码登录使用&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【零信任-6】windows安全助手（零信任）卸载&#10;&#10;1   找到软件所在位置&#10;&#10;1.1 找到安装的软件的位置进行卸载&#10;&#10;a.通过桌面 win 键查找进入&#10;&#10;Win 键安全助手右键点击“ 启动或显示托盘图标”更多打开文件位置&#10;&#10;b.直接输入到安装目录进入&#10;&#10;C:\ProgramData\Microsoft\Windows\Start Menu\Programs\安全助手&#10;&#10;1.2 双击运行卸载&#10;&#10;1.3 管理员口令是e2vPsv8$&#10;&#10;1.4 完成卸载&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.需要把本机网络的DNS127.0.0.1去掉即可，参考下图：&#10;&#10;1.10、问题：为什么我登录不了TMS、EVIP……，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;请先安装零信任，并扫码登录—登录后不能退出零信任&#10;参考下图：&#10;&#10;1.11、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;去到安装目录C:\Program Files (x86)\TrustCyberLink目录下打开TrustCyberLink.exe&#10;1.12、问题：打开零信任没有企业微信按钮 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新打开或者点击控制切换器—点击124.71.208.207或者sec.zy.com-点击确认即可&#10;1.13、问题：安装助手完成时零信任未安装成功 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新安装即可&#10;1.14、问题：提示 “由于找不到 UAADataCenter.dl，无法继续执行代码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;安全助手（零信任）客户端FAQ&#10;操作问题&#10;问题：登录零信任后访问应用时浏览器页面提示403forbidden，如下图：&#10;&#10;设备类型：&#10;Windows/macbook&#10;解决方案：&#10;使用其他浏览器访问&#10;设置浏览器后重新打开进行访问应用&#10;（1）Google浏览器&#10;&#10;（2）火狐浏览器&#10;&#10;问题：登录零信任后当访问应用时提示无法访问此网站，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10; 先关闭浏览器，点击刷新 重新获取策略（刷新一次未解决可以继续点击刷新）参考下图：&#10;&#10; 当a步骤重新获取策略后还是一样提示无法访问此网站时可退出登录零信任，再退出零信任客户端，重新打开扫码登录可参考下图：&#10;&#10;问题：打开零信任扫码登陆时，提示不合法的状态，如下图&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;a.返回上一级，去掉用户名，选择快捷方式登陆参考下图：&#10;&#10;1.4、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;返回上一级，重新选择快捷方式登陆"/>
-        <filter val="系统操作指引&#10;&#10;操作如下：&#10;测试课件复制0530YMD--课程&#10;&#10;4.科组成员操作指引：&#10;上传资源：&#10;在校本课程的校本章节内，可以进行资源上传&#10;&#10;共70款相关课程&#10;&#10;四、FAQ&#10;1.我无法登录怎么办&#10;如果忘记账号密码，可以点击忘记密码进行密码重置；也点击切换到企业微信的扫码登录&#10;2.如果在新建课程后，不需要调整课程的章节，也需要审核吗"/>
-        <filter val="【监控-2】监控系统客户端安装指引&#10;（一）客户端下载地址&#10;iVMS-4200客户端下载地址（复制到浏览器打开并下载）：https://partners.hikvision.com/tools/tooldetail?id=599912121330368512&#10;&#10;（二）客户端安装步骤&#10;右击ivms-4200海康软件，选择【以管理员身份运行】选项，选择【是】&#10;&#10;勾选【我接受许可证协议条款】，然后单击【下一步】按钮&#10;&#10;如下图：“请选择要安装的功能”只需要勾选【视频】，“目标文件夹”选择切换到非C盘安装，然后单击【安装】按钮&#10;&#10;（三）设置账号和密码&#10;设置监控用户名：user ，密码：345110jk密保问题可以统一档案是1&#10;&#10;添加录像机&#10;设备管理—设备&#10;&#10;(有回放功能)普通用户1:userxq密码:345110xq&#10;(无回放功能)普通用户2:user密码:345110jk &#10;&#10;（五）主预览和远程回放&#10;打开程序默认进入主预览界面，如下图所示&#10;&#10;远程回放操作&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【监控-5】监控客户端切换账号指引&#10;注意：这个登录软件的账号，并非监控回放的账号，一般为了方便才设置成用户名：user密码：345110jk/it&#10;&#10;打开监控客户端“iVMS-4200 3.13.0.5 客户端”，主菜单界面的右边设备管理&#10;&#10;选择需要更改的监控，点击“笔形状图标”&#10;&#10;修改账号和密码，切换到有回放功能的账号，才可以看回放&#10;&#10;(有回放功能)普通用户1:  userxq  密码: 345110xq&#10;(无回放功能)普通用户2:  user  密码:  345110jk&#10;最后显示“在线”表示连接成功&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【监控-6】ivms-4200 Lite监控客户端设置&#10;添加校区监控&#10;&#10;设置 &#10;改成ntp.aliyun.com，防止IP变更（新装监控默认没设置）&#10;&#10;(有回放功能)普通用户1:  userxq  密码: 345110xq&#10;(无回放功能)普通用户2:  user  密码:  345110jk&#10;&#10;存储设置（默认）&#10;&#10;所有通道开启移动侦测，灵敏度4，布放打开（每个通道都要手动点一次）&#10;&#10;启动视频信号丢失功能，邮件联动（每个通道都要手动设置）&#10;&#10;异常报警，邮件联动&#10;设置移动侦测录像计划&#10;摄像头画面清晰度设置（不同型号的摄像头，可设置参数不一样，如出现有摄像头不能同时生效，需要再另外分批再设置一次）&#10;通过客户端给摄像头改名字&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【监控-3】校区监控录像操作(客户端版)&#10;双击桌面快捷方式iVMs-4200 Lite 客户端&#10;&#10;打开程序默认进入主预览界面，如下图所示&#10;&#10;3、 远程回放操作&#10;&#10;4、录像文件下载与保存位置（此操作需要先完成第3步）&#10;&#10;注：下载完的录像文件，存放于 C:\user\zy(当前用户)\video下，若没有找到，请查检是否下载完成或重新下载&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;&#10;插图：（如有）&#10;&#10;问题：希沃管理后台账号注册&#10;答案：&#10;注册希沃魔方账号：https://campus.seewo.com/login?redirect_url=https://campus.seewo.com/#/&#10;修改姓名及昵称信息为：校区+名字&#10;登陆提交OA权限申请，登陆OA系统 &gt;搜索账户/权限申请 &gt;希沃集控系统，按图例填写信息&#10;插图：（如有）&#10;&#10;问题：Seafile客户端下载&#10;答案：&#10;Windows挂载盘客户端：https://seafile-downloads.oss-cn-shanghai.aliyuncs.com/seadrive-3.0.9.msi&#10;Mac挂载盘客户端：&#10;https://seafile-downloads.oss-cn-shanghai.aliyuncs.com/seadrive-3.0.9.pkg&#10;插图：（如有）&#10;&#10;问题：Wps Office下载&#10;答案：下载链接：https://package.mac.wpscdn.cn/mac_wps_pkg/wps_installer/1.0.4.004/WPS_Office_Installer.zip&#10;&#10;插图：（如有）&#10;&#10;问题：用Edge打开监控网页&#10;答案：&#10;1、到Edge设置功能开启IE模式（如果已开启略过此步骤）；&#10;&#10;2、操作步骤：&#10;输入监控的网址--切换IE模式（直接关闭弹出的询问框即可）--输入监控网站的登录信息即可&#10;&#10;插图：（如有）&#10;&#10;问题：如何解除办公电脑的冰点还原软件&#10;答案：&#10;1、可以通过按住Shift键同时鼠标左键双击右下角的小白熊头像，&#10;2、或者按快捷键Ctrl+Alt+Shift+F6将冰点还原解锁界面调出来了 &#10;&#10;解锁密码：ballsir或public&#10;&#10;4、红框位置是选择设置冻结或解冻功能；&#10;插图：（如有）&#10;&#10;问题：企业微信扫码登录零信任成功后，零信任不能正常使用"/>
-        <filter val="预数系统简要操作指引V2&#10;预数系统简要操作指引&#10;V2.0&#10;&#10;1.系统访问&#10;2.系统流程介绍&#10;3.产品部操作篇&#10;5.校区操作篇&#10;6.预数审核篇&#10;7.采购部操作篇&#10;&#10;系统访问&#10;系统地址：&#10;https://jyys.zy.com/jyys/admin/login&#10;&#10;登录账号密码：&#10;使用员工通行证进行登录&#10;&#10;注：如果你改过密码且忘记了，通过下面地址找回：https://ucin.zy.com/forgot_password&#10;&#10;支持的浏览器：&#10;谷歌浏览器&#10;&#10;产品部操作篇&#10;&#10;1、配套资料类别维护&#10;在这里维护纸质的配套资料类别，比如：错题本、诊断卷、练习册等&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;预数系统简要操作指引V2&#10;&#10;校区接收到分校推送过来的预数模板，&#10;&#10;1、校区预数填写&#10;第2步&#10;预数按照课程主讲义+配套物料的方式进行；&#10;&#10;系统提供“去年同期招生科数”、“当期目标招生科数”、“当前实际招生科数”和“开班数量”作为填写预数参考；&#10;&#10;填写了主讲义的数量，配套物料的数量会自动填充相同的数值；&#10;覆盖掉当前下拉框选中的地址，但已经提交的预数配送地址不受影响；&#10;&#10;配送地址：第一次预数的时候需要【新增配送地址】，后面系统会自动记录使用过的地址，【修改地址】会&#10;【暂存】：你可以分多次暂存数据，但最后记得【提交】哦，暂存后你退出当前页面，重新点击【填写预&#10;预数填写&#10;&#10;数】，系统会将你暂存的数据加载出来；&#10;&#10;2、校区提交预数记录&#10;校区每次提交一次预数，会在这里生成一条记录&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;预数系统简要操作指引V2&#10;&#10;【首印加印】：选择“首印”，校区在预数截止时间之前只能提交一次预数；选择“加印”，可选择让校区每&#10;注：点【确定】之后，弹窗将会关闭，刚刚保存的数据还没有推送到校区，这时的状态为“构建中”，你&#10;&#10;需要在列表中找出刚才保存的数据，点【预数模板】按钮&#10;&#10;4、发起预数，生成预数模板推送到校区&#10;第3步&#10;在“预数模板”中，你需要确认哪些课程、主讲义（包括讲次范围）、配套资料在本次预数范围，将在本次&#10;&#10;预数范围的物料勾选上最后点击【保存并推送到校区】按钮&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;预数系统简要操作指引V2&#10;&#10;6、导出预数表格，送印&#10;第1步&#10;&#10;6、导出预数表格，送印&#10;第2步&#10;通过【预数明细】功能可以浏览各校区提交的预数明细&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;预数系统简要操作指引V2&#10;&#10;1、校区校长预数审核&#10;第2步&#10;校长审核预数时，可以直接修改预数后审批通过，也可以驳回给填写预数人员修改后重新提交&#10;&#10;2、分区区长预数审核&#10;第1步&#10;预数是否需要经过分区区长审核，系统是可以分别针对首印、加印进行配置的，如需要更改配置，请跟项目组&#10;联系"/>
-        <filter val="校区MAC系统共享文件夹连接指引&#10;输入完点连接就会自动弹出共享盘&#10;&#10;设置开机自动挂载共享盘：打开系统偏好设置，点选“用户和群组”&#10;&#10;在左侧列表中选择你的用户名，点选“登录项”标签&#10;将已经挂载的网络驱动器图标拖放到登录项列表中&#10;可选：点选“隐藏”框，这样系统启动和登录时挂载网络驱动器后，不会自动打开 Finder 窗口&#10;&#10;2.2共享文件夹创建快捷方式放置桌面&#10;需要创建快捷方式的文件夹上，点击【右键】，选择【创建快捷方式】，该文件夹的快捷访问路径就在桌面可查&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【共享-2】校区MAC系统共享文件夹连接指引&#10;指引文档介绍&#10;校区老师电脑&#10;访问共享文件夹的用户名和密码规则：&#10;业务对应的用户名:  成长-班辅（fdb ）  亲子-个辅（gf ）   志业（sgz）&#10;用户名：业务字母代表&#10;密码：zy+校区+业务缩写&#10;比如说鸟巢成长校区：用户名是fdb ，密码是zyncfdb&#10;（注意：成长（fdb ）  亲子（gf ）   志业（gz）的文件夹是有读写权限）&#10;校区的课室一体机&#10;课室共享文件夹ks（在一体机上使用）：&#10;用户名：ks&#10;密码：ks&#10;（注意：ks文件夹此时只有读的权限）&#10;&#10;映射共享网络磁盘&#10;2.1、访问共享文件夹&#10;(1) 在电脑的左上角，点击 【GO/前往】-【connect to server/连接服务器】，或者使用键盘快捷键【command+k】，&#10;&#10;输入校区共享盘地址 smb://192.168.0.26&#10;&#10;注：图中第2步 “+” 必需要操作&#10;输入账号密码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【共享-1】window系统共享文件夹连接指引&#10;指引文档介绍&#10;校区老师电脑&#10;访问共享文件夹的用户名和密码规则：&#10;业务对应的用户名:  成长-班辅（fdb ）  亲子-个辅（gf ）   志业（sgz）&#10;用户名：业务字母代表&#10;密码：zy+校区+业务缩写&#10;比如说鸟巢成长校区：用户名是fdb ，密码是zyncfdb&#10;（注意：成长（fdb ）  亲子（gf ）   志业（gz）的文件夹是有读写权限）&#10;校区的课室一体机&#10;课室共享文件夹ks（在一体机上使用）：&#10;用户名：ks&#10;密码：ks&#10;（注意：ks文件夹此时只有读的权限）&#10;&#10;映射共享网络磁盘&#10;2.1、访问共享文件夹&#10;（1）点击【我的电脑】或【此电脑】，点击左上角，输入校区共享IP地址 \\192.168.0.26，然后点击回车&#10;&#10;（2）见到共享文件夹，例如“ks”(课室共享) 、“班辅共享”或“个辅共享”，双击需要访问的共享文件夹，例如“班辅共享”，在弹出的安全验证窗口输入验证信息用户“fdb”、密码“zyqxlfdb”，并且勾选“记住我的凭据”（需按校区修改密码）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;window系统共享文件夹连接指引&#10;&#10;2.2、共享文件夹创建快捷方式放置桌面&#10;2.2.1、需要创建快捷方式的文件夹上，点击【右键】，选择【创建快捷方式】，该文件夹的快捷访问路径就在桌面可查&#10;&#10;无法正常连接共享盘&#10;背景：情况1：老师去其它校区教研或者教学，回到自己常驻校区发现共享盘连接不上&#10;      情况2：老师需要使用其它校区共享盘工作，连接不上共享盘&#10;3.1、删除Windows凭证，再进行重新连接&#10;按键盘 WIN( 田 ) + R , 运行框中输入‘control’-点击‘凭证管理器’&#10;&#10;点击‘window凭据’-点击‘192.168.0.26’-点击‘删除’&#10;&#10;删除后记得重启电脑，更新改动，重新连接共享文件夹&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;如何使用会议中的共享屏幕&#10;&#10;在Mac OS X 操作系统中，通过“启动台”可以在Mac上打开活动监视器，单击屏幕底部 Dock 上的“启动台”图标，然后在搜索栏中输入“活动监视器”并回车即可打开，使用“Spotlight 搜索”也可以在Mac上打开活动监视器，单击右上角的“Spotlight 搜索”图标（放大镜图标），在搜索栏中输入“活动监视器”并回车即可打开快捷键为 Command+Space&#10;5、会议共享屏幕后，在互动批注没有“批注跟随PowerPoint”入口&#10;需确认共享的是否是PowerPoint，若使用的是WPS是没有入口的，目前支持的是Office批注跟随，可更换使用PowerPoint后重试&#10;6、安卓用户在会议中共享屏幕后，打开“开课啦”应用参会人无法看到对方屏幕共享内容以及无法听到该应用播放的视频&#10;（1）当前开课啦暂不支持共享音频，给您带来了不便，非常抱歉感谢您的反馈&#10;（2）Android 10及以上屏幕分享的时候才会支持分享第三方App的声音"/>
-        <filter val="安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;（2）双击点卸载&#10;&#10;（3）输入安全助手卸载码（e2vPsv8$）后，运行卸载&#10;&#10;4、零信任安装指引&#10;（1）双击点击安装包打开------&gt;点“是” ，如下图&#10;&#10;（2）点—&gt;我同意，如下图&#10;&#10;（3）选择安装位置（可自定义选择安装位置）默认即可，点击—&gt;安装，如下图&#10;&#10;（4）等待安装完成即可，如下图&#10;&#10;（5）安装完成默认勾选运行零信任，桌面可看到零信任图标，如下图&#10;&#10;(6)打开零信任扫码登录，即可通过浏览器访问内部系统，如下图&#10;&#10;(7)如果第一次安装提示需要输入控制器地址，请输入sec.zy.com或124.71.208.207，点击确认后扫码登录使用&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;安全助手卸载和零信任工具安装指引&#10;&#10;注明：先卸载安全助手，后安装零信任工具，如果没有安全助手，可覆盖安装零信任工具&#10;&#10;1、零信任工具下载链接：&#10;Windows版本：&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe  （新版本下载链接）  &#10;&#10;2、管理员口令和安全助手卸载码都是e2vPsv8$&#10;&#10;3、安全助手卸载指引&#10;3.1、第一种卸载方式&#10;（1） 右键安全助手图标，点击进入特权模式，输入管理员口令（e2vPsv8$)即可进入特权模式&#10;&#10;（2）进入特权模式后，在本地电脑C:\Windows\LVUAAgentInstBaseRoot找到此文件运行卸载 &#10;&#10;输入安全助手卸载码（卸载密码默认 e2vPsv8$）&#10;&#10;3.2、第二种卸载方式&#10;（1）若是Win10 系统点击左下角，找到并打开文件夹“UniAccess安全助手”，右键点击“启动或显示托盘图标 ”，点击更多，点击打开文件位置&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.需要把本机网络的DNS127.0.0.1去掉即可，参考下图：&#10;&#10;1.10、问题：为什么我登录不了TMS、EVIP……，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;请先安装零信任，并扫码登录—登录后不能退出零信任&#10;参考下图：&#10;&#10;1.11、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;去到安装目录C:\Program Files (x86)\TrustCyberLink目录下打开TrustCyberLink.exe&#10;1.12、问题：打开零信任没有企业微信按钮 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新打开或者点击控制切换器—点击124.71.208.207或者sec.zy.com-点击确认即可&#10;1.13、问题：安装助手完成时零信任未安装成功 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新安装即可&#10;1.14、问题：提示 “由于找不到 UAADataCenter.dl，无法继续执行代码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【零信任-6】windows安全助手（零信任）卸载&#10;&#10;1   找到软件所在位置&#10;&#10;1.1 找到安装的软件的位置进行卸载&#10;&#10;a.通过桌面 win 键查找进入&#10;&#10;Win 键安全助手右键点击“ 启动或显示托盘图标”更多打开文件位置&#10;&#10;b.直接输入到安装目录进入&#10;&#10;C:\ProgramData\Microsoft\Windows\Start Menu\Programs\安全助手&#10;&#10;1.2 双击运行卸载&#10;&#10;1.3 管理员口令是e2vPsv8$&#10;&#10;1.4 完成卸载&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;安全助手（零信任）客户端FAQ&#10;操作问题&#10;问题：登录零信任后访问应用时浏览器页面提示403forbidden，如下图：&#10;&#10;设备类型：&#10;Windows/macbook&#10;解决方案：&#10;使用其他浏览器访问&#10;设置浏览器后重新打开进行访问应用&#10;（1）Google浏览器&#10;&#10;（2）火狐浏览器&#10;&#10;问题：登录零信任后当访问应用时提示无法访问此网站，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10; 先关闭浏览器，点击刷新 重新获取策略（刷新一次未解决可以继续点击刷新）参考下图：&#10;&#10; 当a步骤重新获取策略后还是一样提示无法访问此网站时可退出登录零信任，再退出零信任客户端，重新打开扫码登录可参考下图：&#10;&#10;问题：打开零信任扫码登陆时，提示不合法的状态，如下图&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;a.返回上一级，去掉用户名，选择快捷方式登陆参考下图：&#10;&#10;1.4、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;返回上一级，重新选择快捷方式登陆"/>
-        <filter val="【打印机-3】MAC 连接打印机操作指引&#10;一、下载驱动包&#10;京瓷打印机mac系统驱动下载&#10;&#10;注：安装前需要先知道打印机IP地址，如下图所示：&#10;&#10;安装驱动&#10;双击驱动包&#10;&#10;若在桌面没有找到驱动，则使用“command+空格键”弹出的搜索框里输入“Kyocera OS X 10.9+ Web build 2024.05.16”，找到并双击驱动包&#10;&#10;双击安装程序&#10;&#10;一路安装&#10;&#10;安装完成后，需要重启电脑!!!&#10;&#10;二、添加打印机&#10;进入系统偏好设置&#10;&#10;进入打印机与扫描仪&#10;&#10;添加设置&#10;&#10;选择IP连接，输入对应打印机IP地址，选择连接协议&#10;&#10;（若电脑无法自动识别打印机型号，请检查打印机是否出现网络问题，例如网线松动等）&#10;&#10;完成添加，可以进行打印&#10;三、各协议解释&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-8】Windows系统安装京瓷打印机指引&#10;一、下载打印机驱动包存到电脑硬盘上&#10;驱动包下载地址：京瓷打印机驱动下载&#10;二、安装打印机&#10;注：安装前需要先收集打印机IP地址和型号（部分共用的打印机需要准备部门密码）&#10;打印机IP地址，图示&#10;&#10;查询打印机型号，图示&#10;&#10;1、解压驱动包&#10;&#10;2、打开安装程序, 按步骤安装&#10;进入文件夹，双击Setup.exe&#10;&#10;接受，选择自定义安装&#10;&#10;以下内容请根据打印机实际型号和IP填写&#10;&#10;添加打印机驱动和安装升级的组件&#10;&#10;打印机安装完成&#10;&#10;三、设置打印机&#10;1、修改名称、设置双面打印&#10;打开计算机，跳至控制面板，进入硬件设备&#10;&#10;右击，打印机属性&#10;&#10;修改打印机名称&#10;&#10;设置双面打印&#10;&#10;2、打印机显示脱机时，需要设置取消SNMP&#10;&#10;3、添加部门id&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;电脑连上了打印机，但是显示程序已暂停？&#10;【打印机-2】电脑连上了打印机，但是显示程序已暂停&#10;电脑连上了打印机，但是显示程序已暂停&#10;解决办法：&#10;依次打开控制面板-硬件和声音-设备和打印机-双击已暂停的打印机-点击打印机-将暂停前面的√去掉即可&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-7】Windows修改打印机IP指引&#10;一、同时按“win+R”输入“control”&#10;&#10;弹出“控制面板”界面选择类别&#10;&#10;点击“查看设备和打印机”&#10;&#10;选择需要修改IP地址的打印机&#10;当前以“Kyocera TASKalfa 300i KX”打印机为例&#10;&#10;选择打印机，右键“打印机属性”&#10;&#10;选择”端口“，选中当前打印机端口&#10;&#10;选择”配置端口“&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址： http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-6】Windows系统添加一体打印机部门ID&#10;1、打开控制面板&#10;&#10;2、右击对应型号打印机 - 点打印机属性（型号可以在打印机面前看到）&#10;&#10;3、点最后一项设备设置 - 点管理员&#10;&#10;注：每机每部门的ID都不一样&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址： http://oa.zy.com ）"/>
-        <filter val="新伙伴入职指引3&#10;&#10;方式: 企业邮箱/企业微信跳转;具体流程: 企业邮箱/企业微信“绩效与学习平台”自动发送学习通知，可直接跳转链接学习&#10;方式: 企业门户;具体流程: 网址及登录详看【一、办公设备指引】&#10;学习路径：企业门户→绩效人才系统→我的学习&#10;方式: 登录Italent系统;具体流程: 网址：https://www.italent.cn/Login&#10;账号：企业邮箱账号&#10;密码：通过忘记密码重新设置&#10;&#10;微信号【卓越教育企业文化】&#10;—卓越er都看卓越文化: 微博号【卓越教育】&#10;—来互动，关注卓越微博;微信号【卓越会员微服务】&#10;—卓越会员都在这里: 微信【卓二代小助手】&#10;—有娃的卓越人赶紧加入吧&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;新伙伴入职指引3&#10;&#10;办公设施指引: 统一通行证;办公设施指引: 企业微信中的邮箱账号前缀;办公设施指引: 短信通知;办公设施指引: 实现多系统统一登录&#10;访问路径：企业微信-工作台-统一认证平台&#10;办公设施指引: 卓越企业门户;办公设施指引: 企业微信中的邮箱账号前缀;办公设施指引: 企微扫码/统一认证平台验证码;办公设施指引: https://ssoin.zy.com/login&#10;办公设施指引: 财务BPM系统;办公设施指引: 企业微信中的邮箱账号前缀;办公设施指引: 企微扫码/统一认证平台验证码;办公设施指引: 用于对公付款（1 万以下无合同 / 1 万以上关联合同）&#10;1、权限：入职自动开通，无需额外申请&#10;2、登录方式：&#10;（1）电脑端：网页登录【卓越企业门户】；&#10;（2）手机端：企业微信→工作台→【BPM】&#10;3、付款时间节点：&#10;（1）截单时间：7 号、14 号、21 号、27 号；&#10;（2）到账时间：审核通过后，对应11号、18号、25号、次月2号（周末节假日顺延）&#10;↓操作指引请扫码下方二维码获取&#10;&#10;办公设施指引: 自助报销系统;办公设施指引: 企业微信中的邮箱账号前缀;办公设施指引: 企微扫码/统一认证平台验证码;办公设施指引: 用于差旅、借支及垫付后报销&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;新伙伴入职指引3&#10;&#10;1、权限：入职自动开通，无需额外申请&#10;2、登录方式：&#10;（1）电脑端：网页登录【卓越企业门户】；&#10;（2）手机端：企业微信→工作台→【自助报销】&#10;3、付款时间节点：同上&#10;↑操作指引请扫码上方二维码获取&#10;办公设施指引: OA;办公设施指引: 企业微信中的邮箱账号前缀;办公设施指引: 企微扫码/统一认证平台验证码;办公设施指引: 卓越流程审批平台，提供休假、加班、销假、补签卡、转正、调动、补贴申请、用印申请、立项、申购、合同签批、IT报障等多种流程审批服https://oa.zy.com/&#10;办公设施指引: IT服务台;办公设施指引: 无;办公设施指引: 无;办公设施指引: 可重置通行证和263邮箱密码&#10;登录方式：企业微信-工作台-IT服务台-更多功能&#10;办公设施指引: 福利社;办公设施指引: 无;办公设施指引: 无;办公设施指引: 登录企业微信-工作台“福利社”-特有用，随时掌握各种丰富的福利资讯及活动&#10;办公设施指引: 秒懂财事;办公设施指引: 无;办公设施指引: 无;办公设施指引: 获取更多财务相关资讯和指引&#10;办公设施指引: 263邮箱;办公设施指引: 企业微信中的邮箱账号前缀@zy.com;办公设施指引: Zy+身份证后6位;办公设施指引: https://mail.263.net/（详情请留意手机短信）&#10;首次登录邮箱，必须使用网页浏览器登录，初始密码只能使用一次，首次登录邮箱后须立即更改个人密码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;绩效系统操作手册（员工）-2025目标管理篇&#10;绩效系统员工自助操作指南&#10;（员工版）&#10;—2025目标管理篇&#10;&#10;绩效计划制定&#10;登录系统&#10;绩效计划制定与审批&#10;&#10;目标修订&#10;目标管理与追踪&#10;&#10;登录系统&#10;登录企业门户&#10;推荐使用谷歌Chrome浏览器&#10;https://ssoin.zy.com/ogin&#10;登录企业门户：&#10;&#10;绩效计划制定&#10;登录系统&#10;绩效计划制定与审批&#10;&#10;目标修订&#10;目标管理与追踪&#10;&#10;绩效计划制定&#10;开始绩效计划制定&#10;首页中「我的待办」或者右上角的待办图标，&#10;&#10;绩效计划制定&#10;点击“去处理”后，即进入目标制定的界面，以下为界面示例&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;部分系统网址帐号密码&#10;系统类型：教学线; 系统名：E研发; 网址：pm.zy.com; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：E学校; 网址：sc.zy.com; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：E教学; 网址：zxx.zy.com/jx/; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：E教研; 网址：https://zxx.zy.com/jyy/resourceCenter; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：E测评; 网址：https://zxx.zy.com/assess-test/#/accountmanagement/index; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：在线测; 网址：https://zxx.zy.com/unitest-admin/; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：卓越在线; 网址：zxx.zy.com/op; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：教学线; 系统名：华途加密; 网址：https://121.37.10.216:9444/dsm/admin/common/main —工作表1&#10;系统类型：教学线; 系统名：物流管理; 网址：http://www.opees.cn/ZX/ZX-login.aspx —工作表1&#10;系统类型：教学线; 系统名：教师库管理系统; 网址：https://teacher.beststudy.com/b/login; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：营运线; 系统名：TMS; 网址：tms.zy.com; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：营运线; 系统名：SCRM; 网址：https://yy.zy.com/scrm/#/dashboard; 账号：通行证账号; 密码：通行证密码 —工作表1&#10;系统类型：其他; 系统名：classin; 网址：https://console.eeo.cn/saas/school/index.html#/fullPage/Index —工作表1"/>
-        <filter val="安全助手(零信任）客户端FAQ&#10;参考下图：&#10;&#10;1.5、问题：打开零信任时提示连接控制器失败，如下图：&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;选择控制器切换124.71.208.207地址；&#10;&#10;b.如a步骤切换控制器地址依然不解决的情况下，可选择重置控制器再输入124.71.208.207参考下图：&#10;&#10;1.6、问题：启动零信任时提示JavaScript错误，无法正常启动，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.打开终端—sudo vi /etc/hosts文件下添加127.0.0.1 localhost&#10;&#10;1.7、问题：nslookup正常解析域名情况下，使用safari、火狐浏览器访问应用报403，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.更换Google浏览器，即可正常访问应用&#10;&#10;1.8、问题：启动零信任时无快捷登录方式，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;随机输入一个用户名，再返回上一级，选择快捷登录方式，参考下图：&#10;&#10;1.9、问题：退出零信任后发现外网基本上不了例如：www.baidu.com&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【日常使用-8】解决MAC无法自动连接WIFI&#10;1、打开Automator程序&#10;&#10;2、选执行脚本，双击&#10;&#10;3、在窗口中输入命令&#10;networksetup -setairportnetwork en0 “SSID” “wifi密码”&#10;&#10;4、导出程序&#10;&#10;5、改名(自己定义），选位置，save&#10;&#10;6、之后，打开系统偏好设置，点用户&#10;&#10;7、点登录项&#10;&#10;8、添加&#10;&#10;9、选刚才导出的程序&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【希沃白板-24】无法连接服务器，错误码为：CertDateInvalid&#10;问题现象&#10;访问课件库、云课堂、知识胶囊、我的学校等模块，出现下面错误&#10;&#10;问题可能原因&#10;电脑日期或时间与现实时间不一致，导致证书验证出错&#10;解决方案&#10;查看系统右下角，确认日期与时间是否正确（需要精确到分钟），如果否，则同步系统时间&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;window系统共享文件夹连接指引&#10;&#10;2.2、共享文件夹创建快捷方式放置桌面&#10;2.2.1、需要创建快捷方式的文件夹上，点击【右键】，选择【创建快捷方式】，该文件夹的快捷访问路径就在桌面可查&#10;&#10;无法正常连接共享盘&#10;背景：情况1：老师去其它校区教研或者教学，回到自己常驻校区发现共享盘连接不上&#10;      情况2：老师需要使用其它校区共享盘工作，连接不上共享盘&#10;3.1、删除Windows凭证，再进行重新连接&#10;按键盘 WIN( 田 ) + R , 运行框中输入‘control’-点击‘凭证管理器’&#10;&#10;点击‘window凭据’-点击‘192.168.0.26’-点击‘删除’&#10;&#10;删除后记得重启电脑，更新改动，重新连接共享文件夹&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;（该群定期清理）&#10;插图：（如有）&#10;&#10;问题：新电脑故障，需要联系售后处理（维保内）&#10;答案：企微扫码进群，进群后@广州立诚捷安电子专注智能弱电工程 协助你处理保内故障（该群定期清理）&#10;插图：（如有）&#10;&#10;问题：Windows电脑校区电脑连接共享&#10;答案：打开任意文件夹，在地址栏输入\\192.168.0.26，在弹出对话框输入账户密码，勾选记住密码点击确认选择你要的文件夹右键发送快捷方式到桌面&#10;插图：（如有）&#10;&#10;问题：Mac电脑校区电脑连接共享&#10;答案：在Finder（访达）状态中 &gt;顶部菜单 &gt;前往 &gt;连接服务器，在弹出对话框选择注册用户后输入账户密码，勾选记住密码点击确认&#10;插图：（如有）&#10;&#10;问题：校区电脑连接共享提示多连接&#10;答案：注销或重启电脑&#10;插图：（如有）&#10;&#10;问题：打开企微的邮箱，提示“账号已被禁用，请联系企业管理员了解详情”&#10;答案：企微自带邮箱功能已禁用，请在企业微信搜索263企业邮箱，输入账户密码绑定&#10;插图：&#10;&#10;问题：各类系统账户及权限申请&#10;答案：登陆提交OA权限申请，登陆OA系统 &gt;搜索账户/权限申请 &gt;按需要选择系统及权限，如未能列明，请描述详细需求"/>
-        <filter val="安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;（2）双击点卸载&#10;&#10;（3）输入安全助手卸载码（e2vPsv8$）后，运行卸载&#10;&#10;4、零信任安装指引&#10;（1）双击点击安装包打开------&gt;点“是” ，如下图&#10;&#10;（2）点—&gt;我同意，如下图&#10;&#10;（3）选择安装位置（可自定义选择安装位置）默认即可，点击—&gt;安装，如下图&#10;&#10;（4）等待安装完成即可，如下图&#10;&#10;（5）安装完成默认勾选运行零信任，桌面可看到零信任图标，如下图&#10;&#10;(6)打开零信任扫码登录，即可通过浏览器访问内部系统，如下图&#10;&#10;(7)如果第一次安装提示需要输入控制器地址，请输入sec.zy.com或124.71.208.207，点击确认后扫码登录使用&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.需要把本机网络的DNS127.0.0.1去掉即可，参考下图：&#10;&#10;1.10、问题：为什么我登录不了TMS、EVIP……，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;请先安装零信任，并扫码登录—登录后不能退出零信任&#10;参考下图：&#10;&#10;1.11、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;去到安装目录C:\Program Files (x86)\TrustCyberLink目录下打开TrustCyberLink.exe&#10;1.12、问题：打开零信任没有企业微信按钮 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新打开或者点击控制切换器—点击124.71.208.207或者sec.zy.com-点击确认即可&#10;1.13、问题：安装助手完成时零信任未安装成功 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新安装即可&#10;1.14、问题：提示 “由于找不到 UAADataCenter.dl，无法继续执行代码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;葵花宝典之零信任篇--2025版&#10;&#10;最佳设置&#10;1.2控制器地址：124.71.208.207&#10;&#10;1.3零信任软件推荐设置【重要：减少零信任被误关闭】&#10;&#10;2、零信任软件常见问题：&#10;1、提示不合法的用户名【返回上一级，选择快捷方式登录】&#10;提示会话已经过期，请重新登陆【返回上一级，选择快捷方式登录】&#10;扫码登录提示认证失败【返回上一级，选择快捷方式登录】&#10;&#10;2、登陆零信任后提示无无法访问此网页【关闭浏览器，重新登陆零信任并刷新策略】&#10;&#10;3、打开零信任扫码登录后提示开启私网DNS失败，请稍后重试【联系IT帮助台获取最新版本安装包并覆盖安装】&#10;&#10;4、网络及系统问题&#10;4.1退出零信任后无法访问外网【清除本地dns 127.0.0.1设置或修改为自动获取】&#10;macbook：&#10;Windwos：&#10;&#10;4.2退出零信任后可以登陆企微和微信，无法打开网页【修改Internet代理】&#10;&#10;4.3软件冲突--IOA【网络异常，卸载IOA（已不再使用）并重启电脑】&#10;&#10;4.3开机进入桌面很慢，自动弹窗警告【卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项】&#10;&#10;5、用户权限相关&#10;5.1打开零信任无OA访问窗口，空白&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;安全助手卸载和零信任工具安装指引&#10;&#10;注明：先卸载安全助手，后安装零信任工具，如果没有安全助手，可覆盖安装零信任工具&#10;&#10;1、零信任工具下载链接：&#10;Windows版本：&#10;https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe  （新版本下载链接）  &#10;&#10;2、管理员口令和安全助手卸载码都是e2vPsv8$&#10;&#10;3、安全助手卸载指引&#10;3.1、第一种卸载方式&#10;（1） 右键安全助手图标，点击进入特权模式，输入管理员口令（e2vPsv8$)即可进入特权模式&#10;&#10;（2）进入特权模式后，在本地电脑C:\Windows\LVUAAgentInstBaseRoot找到此文件运行卸载 &#10;&#10;输入安全助手卸载码（卸载密码默认 e2vPsv8$）&#10;&#10;3.2、第二种卸载方式&#10;（1）若是Win10 系统点击左下角，找到并打开文件夹“UniAccess安全助手”，右键点击“启动或显示托盘图标 ”，点击更多，点击打开文件位置&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;安全助手（零信任）客户端FAQ&#10;操作问题&#10;问题：登录零信任后访问应用时浏览器页面提示403forbidden，如下图：&#10;&#10;设备类型：&#10;Windows/macbook&#10;解决方案：&#10;使用其他浏览器访问&#10;设置浏览器后重新打开进行访问应用&#10;（1）Google浏览器&#10;&#10;（2）火狐浏览器&#10;&#10;问题：登录零信任后当访问应用时提示无法访问此网站，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10; 先关闭浏览器，点击刷新 重新获取策略（刷新一次未解决可以继续点击刷新）参考下图：&#10;&#10; 当a步骤重新获取策略后还是一样提示无法访问此网站时可退出登录零信任，再退出零信任客户端，重新打开扫码登录可参考下图：&#10;&#10;问题：打开零信任扫码登陆时，提示不合法的状态，如下图&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;a.返回上一级，去掉用户名，选择快捷方式登陆参考下图：&#10;&#10;1.4、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;返回上一级，重新选择快捷方式登陆"/>
-        <filter val="绩效系统操作手册（经理）-绩效评估篇V3&#10;&#10;直接上级评估—关键行为评估&#10;关键绩效行为可参考对应的行为准则进行评定，在员工自评列可看到员工的&#10;自评结果&#10;&#10;直接上级评估—总等级与潜力等级评定&#10;在考核总览处，点击“评价”，填写该员工的工作成果等级、关键行为等级、总绩效等级，潜力级别，&#10;&#10;系统会根据绩效总等级和潜力级别给出对应的人才九宫格信息&#10;绩效等级说明及人才九宫格可参考附录1&#10;&#10;直接上级评估—总评语&#10;完成工作成果及关键绩效行为评定后，可填写对该员工的整体评语，例如强项与发展需要等&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;新伙伴入职指引3&#10;&#10;方式: 企业邮箱/企业微信跳转;具体流程: 企业邮箱/企业微信“绩效与学习平台”自动发送学习通知，可直接跳转链接学习&#10;方式: 企业门户;具体流程: 网址及登录详看【一、办公设备指引】&#10;学习路径：企业门户→绩效人才系统→我的学习&#10;方式: 登录Italent系统;具体流程: 网址：https://www.italent.cn/Login&#10;账号：企业邮箱账号&#10;密码：通过忘记密码重新设置&#10;&#10;微信号【卓越教育企业文化】&#10;—卓越er都看卓越文化: 微博号【卓越教育】&#10;—来互动，关注卓越微博;微信号【卓越会员微服务】&#10;—卓越会员都在这里: 微信【卓二代小助手】&#10;—有娃的卓越人赶紧加入吧&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;绩效系统操作手册（员工）-2025目标管理篇&#10;绩效系统员工自助操作指南&#10;（员工版）&#10;—2025目标管理篇&#10;&#10;绩效计划制定&#10;登录系统&#10;绩效计划制定与审批&#10;&#10;目标修订&#10;目标管理与追踪&#10;&#10;登录系统&#10;登录企业门户&#10;推荐使用谷歌Chrome浏览器&#10;https://ssoin.zy.com/ogin&#10;登录企业门户：&#10;&#10;绩效计划制定&#10;登录系统&#10;绩效计划制定与审批&#10;&#10;目标修订&#10;目标管理与追踪&#10;&#10;绩效计划制定&#10;开始绩效计划制定&#10;首页中「我的待办」或者右上角的待办图标，&#10;&#10;绩效计划制定&#10;点击“去处理”后，即进入目标制定的界面，以下为界面示例&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;绩效系统操作手册（经理）-绩效评估篇V3&#10;&#10;对于新入职的伙伴，需要在转正时登录绩效系统制定年度绩效计划，具体操作指引可咨询HRBP领取&#10;&#10;-【绩效系统员工自助操作指南—2025目标管理篇】文件&#10;&#10;绩效系统员工自助操作指南&#10;（员工版）&#10;一2025自标管理篇&#10;&#10;Q2：我/我的团队成员在年中岗位发生调动了，绩效计&#10;划已经做了调整，我应该怎么操作&#10;岗位发生调动的伙伴，绩效计划如需要调整，可知会员工撤回目标进行修改，也可由现直接上级对原&#10;绩效计划驳回后进行修订注意：新制定的绩效目标需完成目标审批才能进行年中/年末评估&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;绩效系统操作手册（经理）-绩效评估篇V3&#10;绩效系统员工自助操作指南&#10;（经理版）&#10;绩效考核篇&#10;—&#10;（注：经理身份泛指所有有团队的员工，此手册内容只针对经理需要进行的绩效评&#10;估及绩效校准等绩效管理工作制定个人目标制定及绩效自评，请参考对应的员工&#10;&#10;登录系统&#10;绩效校准&#10;特殊情况处理&#10;&#10;直接上级评估&#10;当绩效管理员发起绩效评估活动后，您的直接下属完成了个人自评后，您会收到TA的评估表"/>
-        <filter val="263邮箱Q&amp;A&#10;&#10;插图：&#10;&#10;问题：263企业邮箱发信提示人数受限&#10;答案：提交OA权限申请，登陆OA系统 &gt;搜索账户/权限申请 &gt;263邮箱 &gt;群发邮件最多收件人数权限开通 &gt;填写需要开通的数量&#10;插图：&#10;&#10;问题：263企业邮箱特殊人或专用邮箱开通&#10;答案：提交OA权限申请，登陆OA系统 &gt;搜索账户/权限申请 &gt;263邮箱 &gt;特殊用户邮箱开通 &gt;填写需要邮箱作用和计划开通邮箱账号&#10;插图：&#10;&#10;问题：263邮箱收到企业邮箱密码修改提醒&#10;答案：邮箱安全管理要求，第一次及每90天需要修改一次密码，请按照邮箱系统指引修改密码，如有Foxmail或Outlook请同步修改，特殊邮箱90天内未修改密码账号将停用&#10;插图：（如有）&#10;&#10;问题：263邮箱收到可疑邮件（钓鱼或病毒）如何处理&#10;答案：请不要点击邮件的任何链接和下载打开附件，并将邮件原件转发到sec-team@zy.com由安全专家审核回复&#10;插图：（如有）&#10;&#10;问题：263邮箱如何判断为可疑的钓鱼文件&#10;答案：1.1.看发件人地址：如果是公务邮件，发件人多数会使用工作邮箱，如果发现对方使用的是个人邮箱帐号或者邮箱账号拼写很奇怪，那么就需要提高警惕&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;）&#10;插图：（如有）&#10;&#10;问题：263邮箱登陆提示IP地址在黑名单&#10;答案：提交IT报障单申报故障，登陆OA &gt;发起流程 &gt;IT报障/预约服务单 &gt;服务/故障描述：263邮箱黑名单IP：xxx.xxx.xxx.xxx 邮箱账号：xxx@zy.com（按提示内容填写）&#10;插图：（如有）&#10;&#10;问题：手机号码丢失，修改邮箱绑定手机号码&#10;答案：提交IT报障单申报故障，登陆OA &gt;发起流程 &gt;IT报障/预约服务单 &gt;服务/故障描述：263邮箱修改绑定手机  原手机：1391234567 邮箱账号：xxx@zy.com（按提示内容填写）&#10;插图：（如有）&#10;&#10;问题：263邮箱发信提示，您发送的邮件大小超出了您的权限&#10;答案：上传附件超过30M，请通过web登陆邮箱使用云附件功能发送（上传的云附件有效期15天）&#10;插图：（如有）&#10;&#10;问题：263邮箱web登陆收不到验证码&#10;答案：提交IT报障单申报故障，登陆OA &gt;发起流程 &gt;IT报障/预约服务单 &gt;服务/故障描述：如：263邮箱收不到验证码  手机：1391234567 邮箱账号：xxx@zy.com  登陆时间：10:00~10:30&#10;插图：（如有）&#10;&#10;问题：办公电脑安装打印机&#10;答案：企微扫码进群，进群后@穗保客服  协助你连接打印机&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;（该群定期清理）&#10;插图：（如有）&#10;&#10;问题：新电脑故障，需要联系售后处理（维保内）&#10;答案：企微扫码进群，进群后@广州立诚捷安电子专注智能弱电工程 协助你处理保内故障（该群定期清理）&#10;插图：（如有）&#10;&#10;问题：Windows电脑校区电脑连接共享&#10;答案：打开任意文件夹，在地址栏输入\\192.168.0.26，在弹出对话框输入账户密码，勾选记住密码点击确认选择你要的文件夹右键发送快捷方式到桌面&#10;插图：（如有）&#10;&#10;问题：Mac电脑校区电脑连接共享&#10;答案：在Finder（访达）状态中 &gt;顶部菜单 &gt;前往 &gt;连接服务器，在弹出对话框选择注册用户后输入账户密码，勾选记住密码点击确认&#10;插图：（如有）&#10;&#10;问题：校区电脑连接共享提示多连接&#10;答案：注销或重启电脑&#10;插图：（如有）&#10;&#10;问题：打开企微的邮箱，提示“账号已被禁用，请联系企业管理员了解详情”&#10;答案：企微自带邮箱功能已禁用，请在企业微信搜索263企业邮箱，输入账户密码绑定&#10;插图：&#10;&#10;问题：各类系统账户及权限申请&#10;答案：登陆提交OA权限申请，登陆OA系统 &gt;搜索账户/权限申请 &gt;按需要选择系统及权限，如未能列明，请描述详细需求&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱使用指引&#10;如下图：&#10;&#10;2.2 捆绑263邮箱的旧手机号码已注销或不能收取短信验证码，需要在OA系统上发起账户/权限申请】流程进行捆绑手机号码的变更，按以下步骤操作：&#10;2.2.1登录OA系统，点击【发起流程】-【IT类】-【IT服务】-【账户/权限申请】，“系统”选择“263企业邮箱 ”，“描述”写清楚你的需求&#10;&#10;忘记263邮箱密码/修改263邮箱密码&#10;登录企业微信-【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】，如下图：&#10;&#10;企业微信绑定263邮箱进行使用&#10;登录企业微信-【工作台】-【263企业邮箱】，输入邮箱和密码就可以完成绑定&#10;重置邮箱密码之后也需要重新捆绑企业微信才可以正常使用&#10;&#10;登录263邮箱时候提示：用户邮箱状态异常&#10;需要先登录企业微信-【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】进行密码重置，然后再进行微信绑定&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;钓鱼邮件的发件人地址经常会进行伪造，比如伪造成本单位域名的邮箱账号或者系统管理员账号&#10;1.2.看邮件标题：大量钓鱼邮件主题关键字涉及“系统管理员”、“通知”、“订单”、“采购单”、“发票”、“会议日程”、“参会名单”、“历届会议回顾”等，收到此类关键词的邮件，需提高警惕&#10;1.3.看正文措辞：对使用“亲爱的用户”、“亲爱的同事”等一些泛化问候的邮件应保持警惕同时也要对任何制造紧急气氛的邮件提高警惕，如要求“请务必今日下班前完成”&#10;1.4.看正文目的：当心对方索要登录密码，一般正规的发件人所发送的邮件是不会索要收件人的邮箱登录账号和密码的，所以在收到邮件后要留意此类要求避免上当&#10;1.5.看正文内容：当心邮件内容中需要点击的链接地址，若包含“&amp;redirect”字段，很可能就是钓鱼链接;当心垃圾邮件的“退订”功能，有些垃圾邮件正文中的“退订”按钮可能是虚假的点击之后可能会收到更多的垃圾邮件，或者被植入恶意代码可以直接将发件人拉进黑名单，拒收后续邮件&#10;&#10;问题：新263邮箱初始密码是什么&#10;答案：邮箱密码规则：zy+身份证后六位（原来规则，需要更新"/>
-        <filter val="【打印机-8】Windows系统安装京瓷打印机指引&#10;一、下载打印机驱动包存到电脑硬盘上&#10;驱动包下载地址：京瓷打印机驱动下载&#10;二、安装打印机&#10;注：安装前需要先收集打印机IP地址和型号（部分共用的打印机需要准备部门密码）&#10;打印机IP地址，图示&#10;&#10;查询打印机型号，图示&#10;&#10;1、解压驱动包&#10;&#10;2、打开安装程序, 按步骤安装&#10;进入文件夹，双击Setup.exe&#10;&#10;接受，选择自定义安装&#10;&#10;以下内容请根据打印机实际型号和IP填写&#10;&#10;添加打印机驱动和安装升级的组件&#10;&#10;打印机安装完成&#10;&#10;三、设置打印机&#10;1、修改名称、设置双面打印&#10;打开计算机，跳至控制面板，进入硬件设备&#10;&#10;右击，打印机属性&#10;&#10;修改打印机名称&#10;&#10;设置双面打印&#10;&#10;2、打印机显示脱机时，需要设置取消SNMP&#10;&#10;3、添加部门id&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-3】MAC 连接打印机操作指引&#10;一、下载驱动包&#10;京瓷打印机mac系统驱动下载&#10;&#10;注：安装前需要先知道打印机IP地址，如下图所示：&#10;&#10;安装驱动&#10;双击驱动包&#10;&#10;若在桌面没有找到驱动，则使用“command+空格键”弹出的搜索框里输入“Kyocera OS X 10.9+ Web build 2024.05.16”，找到并双击驱动包&#10;&#10;双击安装程序&#10;&#10;一路安装&#10;&#10;安装完成后，需要重启电脑!!!&#10;&#10;二、添加打印机&#10;进入系统偏好设置&#10;&#10;进入打印机与扫描仪&#10;&#10;添加设置&#10;&#10;选择IP连接，输入对应打印机IP地址，选择连接协议&#10;&#10;（若电脑无法自动识别打印机型号，请检查打印机是否出现网络问题，例如网线松动等）&#10;&#10;完成添加，可以进行打印&#10;三、各协议解释&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;打印机-理光、富士施乐、佳能驱动下载链接&#10;理光MPC5503：&#10;http://support.ricoh.com/bb/html/dr_ut_e/rcn1/model/mpc4503/mpc4503.htm&#10;&#10;理光MP6054：&#10;http://support.ricoh.com/bb/html/dr_ut_e/rcn1/model/mp2554/mp2554.htm?lang=cn&#10;&#10;富士施乐P288：&#10;https://m3support-fb.fujifilm-fb.com.cn/driver_downloads/www/&#10;&#10;富士施乐M288：&#10;https://m3support-fb.fujifilm-fb.com.cn/driver_downloads/www/&#10;&#10;佳能MF244/MF249（通用）：&#10;https://www.canon.com.cn/supports/download/sims/list/slist?fileTypeId=23&amp;categoryId=15&amp;seriesId=77&amp;modelId=1234&amp;OSName=Windows%2010%20(x64)&amp;channel=1&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-5】MAC系统添加一体打印机部门ID&#10;操作前请先确认是否已安装好打印机驱动，以下步骤需要安装好驱动才能实现&#10;操作步骤：&#10;打开前往&gt;应用程序，在应用程序中找到打印机程序并双击打开&#10;&#10;2、选对应IP打印机&#10;&#10;3、添加部门ID&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址： http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【打印机-4】打印机IP地址查看及报修&#10;1.查看打印机IP地址：&#10;一般打印机IP地址都会粘贴或写在标签纸上，如下图：&#10;&#10;2.过程中遇到非驱动或网络问题，而是打印机出现不能开机、硒鼓、卡纸等等不能处理问题可拨打以下电话或者添加图中穗保客服报修&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）"/>
-        <filter val="263邮箱Q&amp;A&#10;&#10;插图：&#10;&#10;问题：263企业邮箱发信提示人数受限&#10;答案：提交OA权限申请，登陆OA系统 &gt;搜索账户/权限申请 &gt;263邮箱 &gt;群发邮件最多收件人数权限开通 &gt;填写需要开通的数量&#10;插图：&#10;&#10;问题：263企业邮箱特殊人或专用邮箱开通&#10;答案：提交OA权限申请，登陆OA系统 &gt;搜索账户/权限申请 &gt;263邮箱 &gt;特殊用户邮箱开通 &gt;填写需要邮箱作用和计划开通邮箱账号&#10;插图：&#10;&#10;问题：263邮箱收到企业邮箱密码修改提醒&#10;答案：邮箱安全管理要求，第一次及每90天需要修改一次密码，请按照邮箱系统指引修改密码，如有Foxmail或Outlook请同步修改，特殊邮箱90天内未修改密码账号将停用&#10;插图：（如有）&#10;&#10;问题：263邮箱收到可疑邮件（钓鱼或病毒）如何处理&#10;答案：请不要点击邮件的任何链接和下载打开附件，并将邮件原件转发到sec-team@zy.com由安全专家审核回复&#10;插图：（如有）&#10;&#10;问题：263邮箱如何判断为可疑的钓鱼文件&#10;答案：1.1.看发件人地址：如果是公务邮件，发件人多数会使用工作邮箱，如果发现对方使用的是个人邮箱帐号或者邮箱账号拼写很奇怪，那么就需要提高警惕&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱使用指引&#10;如下图：&#10;&#10;2.2 捆绑263邮箱的旧手机号码已注销或不能收取短信验证码，需要在OA系统上发起账户/权限申请】流程进行捆绑手机号码的变更，按以下步骤操作：&#10;2.2.1登录OA系统，点击【发起流程】-【IT类】-【IT服务】-【账户/权限申请】，“系统”选择“263企业邮箱 ”，“描述”写清楚你的需求&#10;&#10;忘记263邮箱密码/修改263邮箱密码&#10;登录企业微信-【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】，如下图：&#10;&#10;企业微信绑定263邮箱进行使用&#10;登录企业微信-【工作台】-【263企业邮箱】，输入邮箱和密码就可以完成绑定&#10;重置邮箱密码之后也需要重新捆绑企业微信才可以正常使用&#10;&#10;登录263邮箱时候提示：用户邮箱状态异常&#10;需要先登录企业微信-【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】进行密码重置，然后再进行微信绑定&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;问题：263企业邮箱修改密码&#10;答案：自助修改密码路径：企业微信 &gt; 工作台 &gt; IT服务台 &gt; 更多功能 &gt;邮箱密码重置&#10;插图：&#10;&#10;问题：263企业邮箱修改密码（已绑定手机）&#10;答案：打开网址https://mm.263.com/wm2e/website/jsp/resetPassword.jsp&#10;插图：&#10;&#10;问题：263企业邮箱网页登陆地址&#10;答案：登陆网址https://www.263.net&#10;插图：&#10;&#10;问题：263企业邮箱修改密码规则&#10;答案：密码需要包含大小写、数字、符号，长度不小于8位，不能使用连续的字符，不能使用简单密码&#10;插图：&#10;&#10;问题：263企业邮箱客户端服务器地址&#10;答案：建议使用IMAP+SMTP组合，详情见附图&#10;插图：&#10;&#10;问题：如何在苹果mail邮件客户端中设置IMAP收发邮件&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱使用指引&#10;如下图：&#10;&#10;修改邮件归档周期&#10;登录邮箱-点击右上角【账户】头像-【设置】-【文件夹管理】-【正常邮件归档时间】里面跟进自己需求进行选择，如下图&#10;&#10;263邮箱的手机版APP下载路径&#10;7.1  iPhone/苹果版的手机扫码下载263邮箱APP&#10;&#10;7.2 Android/安卓版的手机扫码下载263邮箱APP&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【邮箱-1】263邮箱使用指引&#10;新用户初次登录263邮箱&#10;新用户初次登录邮箱需要在电脑网页端登录，必须关联手机号码&#10;在浏览器复制并打开该网址： https://www.263.net/&#10;1.1点击【登录】-输入【邮箱】和【密码】（没有邮箱密码可以按忘记密码去重置）&#10;&#10;1.2 输入【手机号码】和【短信验证码】,提示【手机号验证成功】，表示已关联手机号，如下图：&#10;&#10;更换捆绑手机号&#10;2.1 旧手机号还能接收到短信验证码的情况，需要先解绑旧手机号码再重新绑定新手机号码，按以下步骤操作：&#10;2.1.1登录邮箱-点击右上角【账户】头像-【设置】,如下图：&#10;&#10;2.1.2点击【账户信息】-【点击这里绑定手机】,如下图：&#10;&#10;2.1.3点击【解除绑定】,如下图：&#10;&#10;2.1.4点击【获取验证码】并输入验证码后，点击【解除绑定】,如下图：&#10;&#10;2.1.5点击手机号码【绑定】,如下图：&#10;2.1.6输入【手机号码】和【验证码】,点击确定，就完成了新的手机号码捆绑邮箱"/>
-        <filter val="葵花宝典之零信任篇--2025版&#10;&#10;最佳设置&#10;1.2控制器地址：124.71.208.207&#10;&#10;1.3零信任软件推荐设置【重要：减少零信任被误关闭】&#10;&#10;2、零信任软件常见问题：&#10;1、提示不合法的用户名【返回上一级，选择快捷方式登录】&#10;提示会话已经过期，请重新登陆【返回上一级，选择快捷方式登录】&#10;扫码登录提示认证失败【返回上一级，选择快捷方式登录】&#10;&#10;2、登陆零信任后提示无无法访问此网页【关闭浏览器，重新登陆零信任并刷新策略】&#10;&#10;3、打开零信任扫码登录后提示开启私网DNS失败，请稍后重试【联系IT帮助台获取最新版本安装包并覆盖安装】&#10;&#10;4、网络及系统问题&#10;4.1退出零信任后无法访问外网【清除本地dns 127.0.0.1设置或修改为自动获取】&#10;macbook：&#10;Windwos：&#10;&#10;4.2退出零信任后可以登陆企微和微信，无法打开网页【修改Internet代理】&#10;&#10;4.3软件冲突--IOA【网络异常，卸载IOA（已不再使用）并重启电脑】&#10;&#10;4.3开机进入桌面很慢，自动弹窗警告【卸载第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师，禁用不必要的软件开机启动项】&#10;&#10;5、用户权限相关&#10;5.1打开零信任无OA访问窗口，空白&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;安全助手（零信任）客户端FAQ&#10;操作问题&#10;问题：登录零信任后访问应用时浏览器页面提示403forbidden，如下图：&#10;&#10;设备类型：&#10;Windows/macbook&#10;解决方案：&#10;使用其他浏览器访问&#10;设置浏览器后重新打开进行访问应用&#10;（1）Google浏览器&#10;&#10;（2）火狐浏览器&#10;&#10;问题：登录零信任后当访问应用时提示无法访问此网站，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10; 先关闭浏览器，点击刷新 重新获取策略（刷新一次未解决可以继续点击刷新）参考下图：&#10;&#10; 当a步骤重新获取策略后还是一样提示无法访问此网站时可退出登录零信任，再退出零信任客户端，重新打开扫码登录可参考下图：&#10;&#10;问题：打开零信任扫码登陆时，提示不合法的状态，如下图&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;a.返回上一级，去掉用户名，选择快捷方式登陆参考下图：&#10;&#10;1.4、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;返回上一级，重新选择快捷方式登陆&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;参考下图：&#10;&#10;1.5、问题：打开零信任时提示连接控制器失败，如下图：&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;选择控制器切换124.71.208.207地址；&#10;&#10;b.如a步骤切换控制器地址依然不解决的情况下，可选择重置控制器再输入124.71.208.207参考下图：&#10;&#10;1.6、问题：启动零信任时提示JavaScript错误，无法正常启动，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.打开终端—sudo vi /etc/hosts文件下添加127.0.0.1 localhost&#10;&#10;1.7、问题：nslookup正常解析域名情况下，使用safari、火狐浏览器访问应用报403，如下图：&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.更换Google浏览器，即可正常访问应用&#10;&#10;1.8、问题：启动零信任时无快捷登录方式，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;随机输入一个用户名，再返回上一级，选择快捷登录方式，参考下图：&#10;&#10;1.9、问题：退出零信任后发现外网基本上不了例如：www.baidu.com&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手(零信任）客户端FAQ&#10;&#10;设备类型：&#10;mac&#10;解决方案：&#10;a.需要把本机网络的DNS127.0.0.1去掉即可，参考下图：&#10;&#10;1.10、问题：为什么我登录不了TMS、EVIP……，如下图：&#10;&#10;设备类型：&#10;Windows/mac&#10;解决方案：&#10;请先安装零信任，并扫码登录—登录后不能退出零信任&#10;参考下图：&#10;&#10;1.11、问题：安装完成不显示&quot;零信任&quot;（IOA冲突） 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;去到安装目录C:\Program Files (x86)\TrustCyberLink目录下打开TrustCyberLink.exe&#10;1.12、问题：打开零信任没有企业微信按钮 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新打开或者点击控制切换器—点击124.71.208.207或者sec.zy.com-点击确认即可&#10;1.13、问题：安装助手完成时零信任未安装成功 如下图：&#10;&#10;设备类型：&#10;Windows10&#10;解决方案：&#10;重新安装即可&#10;1.14、问题：提示 “由于找不到 UAADataCenter.dl，无法继续执行代码&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;安全助手卸载&amp;零信任工具安装指引（Windows版）&#10;&#10;（2）双击点卸载&#10;&#10;（3）输入安全助手卸载码（e2vPsv8$）后，运行卸载&#10;&#10;4、零信任安装指引&#10;（1）双击点击安装包打开------&gt;点“是” ，如下图&#10;&#10;（2）点—&gt;我同意，如下图&#10;&#10;（3）选择安装位置（可自定义选择安装位置）默认即可，点击—&gt;安装，如下图&#10;&#10;（4）等待安装完成即可，如下图&#10;&#10;（5）安装完成默认勾选运行零信任，桌面可看到零信任图标，如下图&#10;&#10;(6)打开零信任扫码登录，即可通过浏览器访问内部系统，如下图&#10;&#10;(7)如果第一次安装提示需要输入控制器地址，请输入sec.zy.com或124.71.208.207，点击确认后扫码登录使用"/>
-        <filter val="BC迎检操作说明&#10;BC 迎检操作说明&#10;BC 迎检登录地址：http://demo.tms.gaofen.com/tms&#10;输入迎检账号/密码即可登录&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;迎检操作说明+-+补充合同查看&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;迎检操作说明+-+补充合同查看&#10;&#10;报名确认—&#10;—财务审批已提交报名信息&#10;路径：数据统计&gt;&gt;报名确认&#10;财务对校区&quot;报名&quot;名单中，已收款的信息进行审批&#10;点击&quot;不通过&quot;该信息将审批不通过，该信息从报名表中移除&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;迎检操作说明+-+补充合同查看&#10;&#10;点击&quot;通过&quot;即可审批通过报名信息，报名信息将会在&quot;团队名单&quot;中正常展示&#10;&#10;查询已确认收到款项的学生名&#10;团队名单&#10;—&#10;单、打印确认单（收据）、退费申请&#10;路径：数据统计&gt;&gt;团队名单&#10;1、查询已收款用户名单&#10;&#10;选择要查询的年份、校区（校区为必选），点击查询即可也可输入班级名称查询班级学&#10;员信息&#10;&#10;2、打印确认单&#10;选中需打印的数据，点击&quot;打印确认单&quot;即可进行确认单批量打印，打印格式如下&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;迎检操作说明+-+补充合同查看&#10;迎检操作说明-补充合同查看&#10;&#10;咨询报名—&#10;—报读操作&#10;路径：用户管理&gt;&gt;咨询报名&#10;&#10;填写完学生信息、团队信息，点击&quot;报名&quot;即可－可重复报名&#10;校区录入的&quot;报名&quot;信息，财务将会在第二点&quot;报名审批&quot;界面可查看&#10;团队信息，输入关键字，会从财务已提供导入系统的列表中自动读取，如未在列表中，也&#10;可直接新增团队报读（报名页面，填写团队名称、团队编号、开课日期）"/>
-        <filter val="【监控-1】Edge浏览器查看监控&#10;指引文档介绍&#10;使用浏览器查看校区监控，需要满足以下要求：&#10;1.1、电脑系统：Win10以上版本；&#10;1.2、浏览器：Edge浏览器的Internet Explorer 模式&#10;Edge浏览器的设置步骤&#10;打开Edge浏览器，点击右上角的三个点，打开设置&#10;&#10;2、在搜索框输入：Explorer&#10;&#10;3、往下滑动找到‘允许在Internet Explorer模式下重新加载网站(IE模式)’选择允许&#10;&#10;4、右上角的三个点里面就会添加一个‘在Intermet Explorer模式下重新加载’&#10;&#10;5、在网页搜索框里面输入监控IP地址192.168.0.X（X范围一般为5~10）&#10;&#10;进入到登录界面后，先点击右上角三个点 选择在‘Intermet Explorer模式下重新加载’，再输入账号密码登录即可&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;Edge浏览器查看监控&#10;&#10;(有回放功能)普通用户1:  userxq  密码: 345110xq&#10;(无回放功能)普通用户2:  user  密码:  345110jk&#10;&#10;7、首次使用会提示下载插件，根据提示下载即可&#10;8、左上角点开【e】标志，开启兼容性和下次在ie模式下打开&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【监控-5】监控客户端切换账号指引&#10;注意：这个登录软件的账号，并非监控回放的账号，一般为了方便才设置成用户名：user密码：345110jk/it&#10;&#10;打开监控客户端“iVMS-4200 3.13.0.5 客户端”，主菜单界面的右边设备管理&#10;&#10;选择需要更改的监控，点击“笔形状图标”&#10;&#10;修改账号和密码，切换到有回放功能的账号，才可以看回放&#10;&#10;(有回放功能)普通用户1:  userxq  密码: 345110xq&#10;(无回放功能)普通用户2:  user  密码:  345110jk&#10;最后显示“在线”表示连接成功&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【监控-2】监控系统客户端安装指引&#10;（一）客户端下载地址&#10;iVMS-4200客户端下载地址（复制到浏览器打开并下载）：https://partners.hikvision.com/tools/tooldetail?id=599912121330368512&#10;&#10;（二）客户端安装步骤&#10;右击ivms-4200海康软件，选择【以管理员身份运行】选项，选择【是】&#10;&#10;勾选【我接受许可证协议条款】，然后单击【下一步】按钮&#10;&#10;如下图：“请选择要安装的功能”只需要勾选【视频】，“目标文件夹”选择切换到非C盘安装，然后单击【安装】按钮&#10;&#10;（三）设置账号和密码&#10;设置监控用户名：user ，密码：345110jk密保问题可以统一档案是1&#10;&#10;添加录像机&#10;设备管理—设备&#10;&#10;(有回放功能)普通用户1:userxq密码:345110xq&#10;(无回放功能)普通用户2:user密码:345110jk &#10;&#10;（五）主预览和远程回放&#10;打开程序默认进入主预览界面，如下图所示&#10;&#10;远程回放操作&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【监控-4】监控自定义预览模式&#10;自定义预览模式&#10;在监控系统的使用过程中，同时打开多个监控预览图可能会导致卡顿或画面延迟现象这主要是因为大量图像数据的传输与处理对系统资源造成较大压力，进而影响系统的流畅运行基于此，建议采用自定义预览分组模式，按不同场景（前台、课室、过道/茶水间、楼层等）进行分组查看，每组画面不超过9个&#10;&#10;1、点击【设备管理】&#10;&#10;2、点击【设备管理】-【设备】-【添加】&#10;&#10;3、分别输入对应的【名称】【地址】【用户名】【密码】，最后点击【添加】&#10;&#10;4、成功添加设备后会显示【网络状态-在线】&#10;&#10;5、返回菜单点击【主预览】&#10;&#10;6、点击【自定义视图】右侧的“+”，根据视图分区进行命名如‘电梯间’‘通道’&#10;&#10;7、以‘电梯间’为例，双击‘电梯间’再将7F（总预览）中的电梯视图拖动至图中，再双击‘电梯间’在弹出的对话框中点击确定保存，即自定义视图完成&#10;&#10;8、如需要更改视图布局可以点击右下角【分割】，根据需要选择&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）"/>
-        <filter val="263邮箱使用指引&#10;如下图：&#10;&#10;2.2 捆绑263邮箱的旧手机号码已注销或不能收取短信验证码，需要在OA系统上发起账户/权限申请】流程进行捆绑手机号码的变更，按以下步骤操作：&#10;2.2.1登录OA系统，点击【发起流程】-【IT类】-【IT服务】-【账户/权限申请】，“系统”选择“263企业邮箱 ”，“描述”写清楚你的需求&#10;&#10;忘记263邮箱密码/修改263邮箱密码&#10;登录企业微信-【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】，如下图：&#10;&#10;企业微信绑定263邮箱进行使用&#10;登录企业微信-【工作台】-【263企业邮箱】，输入邮箱和密码就可以完成绑定&#10;重置邮箱密码之后也需要重新捆绑企业微信才可以正常使用&#10;&#10;登录263邮箱时候提示：用户邮箱状态异常&#10;需要先登录企业微信-【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】进行密码重置，然后再进行微信绑定&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;&#10;插图：&#10;&#10;问题：263企业邮箱发信提示人数受限&#10;答案：提交OA权限申请，登陆OA系统 &gt;搜索账户/权限申请 &gt;263邮箱 &gt;群发邮件最多收件人数权限开通 &gt;填写需要开通的数量&#10;插图：&#10;&#10;问题：263企业邮箱特殊人或专用邮箱开通&#10;答案：提交OA权限申请，登陆OA系统 &gt;搜索账户/权限申请 &gt;263邮箱 &gt;特殊用户邮箱开通 &gt;填写需要邮箱作用和计划开通邮箱账号&#10;插图：&#10;&#10;问题：263邮箱收到企业邮箱密码修改提醒&#10;答案：邮箱安全管理要求，第一次及每90天需要修改一次密码，请按照邮箱系统指引修改密码，如有Foxmail或Outlook请同步修改，特殊邮箱90天内未修改密码账号将停用&#10;插图：（如有）&#10;&#10;问题：263邮箱收到可疑邮件（钓鱼或病毒）如何处理&#10;答案：请不要点击邮件的任何链接和下载打开附件，并将邮件原件转发到sec-team@zy.com由安全专家审核回复&#10;插图：（如有）&#10;&#10;问题：263邮箱如何判断为可疑的钓鱼文件&#10;答案：1.1.看发件人地址：如果是公务邮件，发件人多数会使用工作邮箱，如果发现对方使用的是个人邮箱帐号或者邮箱账号拼写很奇怪，那么就需要提高警惕&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;263邮箱Q&amp;A&#10;问题：263企业邮箱修改密码&#10;答案：自助修改密码路径：企业微信 &gt; 工作台 &gt; IT服务台 &gt; 更多功能 &gt;邮箱密码重置&#10;插图：&#10;&#10;问题：263企业邮箱修改密码（已绑定手机）&#10;答案：打开网址https://mm.263.com/wm2e/website/jsp/resetPassword.jsp&#10;插图：&#10;&#10;问题：263企业邮箱网页登陆地址&#10;答案：登陆网址https://www.263.net&#10;插图：&#10;&#10;问题：263企业邮箱修改密码规则&#10;答案：密码需要包含大小写、数字、符号，长度不小于8位，不能使用连续的字符，不能使用简单密码&#10;插图：&#10;&#10;问题：263企业邮箱客户端服务器地址&#10;答案：建议使用IMAP+SMTP组合，详情见附图&#10;插图：&#10;&#10;问题：如何在苹果mail邮件客户端中设置IMAP收发邮件&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【邮箱-10】263邮箱设置--Outlook篇&#10;【修改263邮箱登陆密码】&#10;&#10;【忘记邮箱密码重置办法】&#10;打开企业微信搜索【IT服务台】，更多功能→重置邮箱密码，按页面步骤进行密码修改&#10;&#10;【Outlook更新密码】&#10;&#10;【Outlook 邮件客户端配置263邮箱步骤】&#10;&#10;设置完成，测试邮件收发&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）&lt;&lt;&lt;__CONTEXT_BLOCK__&gt;&gt;&gt;【邮箱-12】263邮箱设置--Macbook 邮件篇&#10;【修改263邮箱登陆密码】&#10;&#10;【忘记邮箱密码重置办法】&#10;重置密码：企业微信，点击【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】&#10;&#10;【Macbook 邮件更新密码步骤】&#10;&#10;【Macbook 邮件客户端配置263邮箱步骤】&#10;&#10;按图补充1~3点信息&#10;&#10;设置完成，测试邮件收发&#10;&#10;Tips：如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com ）"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="好的!关于**如何查看Tms迎检系统数据**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **登录TMS迎检系统**  &#10;   打开浏览器，输入登录地址：[http://demo.tms.gaofen.com/tms](http://demo.tms.gaofen.com/tms)，输入迎检账号和密码进行登录。&#10;&#10;2. **查看报名确认信息**  &#10;   路径：**数据统计 &gt;&gt; 报名确认**  &#10;   - 财务可对校区“报名”名单中已收款的信息进行审批。  &#10;   - 点击“通过”表示审批通过，该信息将在“团队名单”中正常展示。  &#10;   - 点击“不通过”则该信息将被移除。&#10;&#10;3. **查询已收款学生名单**  &#10;   路径：**数据统计 &gt;&gt; 团队名单**  &#10;   - 选择年份、校区（校区为必选），点击“查询”即可查看对应的学生名单。  &#10;   - 也可输入班级名称查询特定班级的学员信息。&#10;&#10;4. **打印确认单**  &#10;   - 在“团队名单”页面，选中需要打印的数据，点击“打印确认单”，即可批量打印收据格式的确认单。&#10;&#10;5. **查看或新增咨询报名信息**  &#10;   路径：**用户管理 &gt;&gt; 咨询报名**  &#10;   - 填写学生信息和团队信息后，点击“报名”即可提交。  &#10;   - 若团队信息不在系统列表中，可直接新增团队报读（填写团队名称、编号、开课日期）。&#10;&#10;**💡 提示**: 登录时请确保使用正确的迎检账号和密码，并根据权限访问相应模块。如需导出或打印数据，请注意选择正确的筛选条件以获取准确结果。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于在Windows系统上安装京瓷打印机驱动，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载打印机驱动包**  &#10;   访问【京瓷打印机驱动下载】页面，将驱动包保存到电脑硬盘。&#10;&#10;2. **解压驱动包**  &#10;   找到下载的驱动包并进行解压。&#10;&#10;3. **运行安装程序**  &#10;   进入解压后的文件夹，双击 `Setup.exe` 文件启动安装程序。&#10;&#10;4. **选择自定义安装**  &#10;   在安装过程中，点击“接受”，并选择“自定义安装”以根据需要添加组件。&#10;&#10;5. **填写打印机信息**  &#10;   根据提示输入打印机的实际型号和IP地址（可在打印机上查询）。&#10;&#10;6. **完成安装**  &#10;   安装完成后，系统会自动添加打印机驱动和相关组件。&#10;&#10;**设置打印机**&#10;&#10;1. **修改名称与设置双面打印**  &#10;   - 打开控制面板 &gt; 硬件和设备 &gt; 右键打印机 &gt; 选择“打印机属性”。  &#10;   - 修改打印机名称，并在选项中设置“双面打印”。&#10;&#10;2. **处理脱机问题**  &#10;   如果打印机显示为脱机状态，请进入打印机属性，取消SNMP设置。&#10;&#10;3. **添加部门ID（如需）**  &#10;   部分共享打印机需要输入部门密码或ID，按照提示操作即可。&#10;&#10;**💡 提示**: 安装前请确保已正确获取打印机的IP地址和型号。如果遇到网络连接问题，请检查网线是否松动或打印机是否正常联网。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**在校区电脑安装监控系统**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载客户端软件**&#10;   - 打开浏览器，访问以下链接下载iVMS-4200客户端：&#10;     ```&#10;     https://partners.hikvision.com/tools/tooldetail?id=599912121330368512&#10;     ```&#10;&#10;2. **以管理员身份运行安装程序**&#10;   - 右击下载的`ivms-4200海康软件`，选择【以管理员身份运行】选项，并点击【是】继续。&#10;&#10;3. **接受协议并选择安装内容**&#10;   - 勾选【我接受许可证协议条款】，然后单击【下一步】按钮。&#10;   - 在“请选择要安装的功能”界面中，仅勾选【视频】功能模块。&#10;   - 选择安装路径时，请将安装位置切换到非C盘（如D盘或E盘），然后点击【安装】按钮开始安装。&#10;&#10;4. **设置账号和密码**&#10;   - 安装完成后，打开客户端。&#10;   - 设置监控用户名为：`user`，密码为：`345110jk`。&#10;   - 如果需要回放功能，使用用户1：`userxq`，密码：`345110xq`。&#10;&#10;5. **添加录像机设备**&#10;   - 进入【设备管理】—【设备】，添加对应的校区监控设备。&#10;&#10;**💡 提示**:  &#10;- 推荐将NTP服务器设置为 `ntp.aliyun.com`，以防止IP地址变更导致连接问题。  &#10;- 所有通道建议开启移动侦测、灵敏度设为4，并启用布防状态。  &#10;- 如需下载录像文件，保存路径默认为 `C:\Users\zy(当前用户)\video`，请确保完成远程回放操作后再进行下载。  &#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**零信任无法进入问题**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **切换控制器地址**  &#10;   打开零信任客户端，选择控制器并切换为 `124.71.208.207` 地址。&#10;&#10;2. **重置控制器设置**  &#10;   如果切换控制器地址无效，尝试重置控制器后再输入 `124.71.208.207`。&#10;&#10;3. **卸载IOA软件**  &#10;   确认电脑上是否安装了 IOA（旧版网络控制软件），建议卸载 IOA（已不再使用），然后重新启动电脑。&#10;&#10;4. **检查第三方杀毒软件冲突**  &#10;   卸载可能影响系统性能的第三方杀毒软件，如：360安全卫士、金山毒霸、火绒安全、鲁大师等，并禁用不必要的开机启动项。&#10;&#10;5. **尝试快捷登录方式**  &#10;   在登录界面随机输入一个用户名，返回上一级后选择“快捷登录方式”。&#10;&#10;6. **重新安装零信任客户端**  &#10;   如果仍然无法打开零信任，前往安装目录重新运行安装程序或下载最新版本覆盖安装。&#10;&#10;**💡 提示**: 若以上方法仍无法解决，请联系IT帮助台获取进一步支持。"/>
-        <filter val="好的!关于**找回263邮箱密码**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业微信重置密码**  &#10;   登录企业微信，点击【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】，按照页面提示进行密码修改。&#10;&#10;2. **通过网页链接重置密码（已绑定手机）**  &#10;   打开网址：https://mm.263.com/wm2e/website/jsp/resetPassword.jsp，根据页面指引完成密码重置。&#10;&#10;**💡 提示**: 重置密码后，如果之前绑定了企业微信或邮件客户端（如Outlook、Macbook邮件等），需要重新登录并更新密码以确保正常使用。密码需满足规则：包含大小写字母、数字和符号，长度不小于8位，不能使用连续字符或简单密码。"/>
-        <filter val="好的!关于**如何填写零信任控制器地址**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **打开零信任客户端**&#10;   - 启动已安装的零信任工具。&#10;&#10;2. **进入控制器设置界面**&#10;   - 在登录界面或设置选项中，找到“控制器地址”或“Controller Address”的输入框。&#10;&#10;3. **填写控制器地址**&#10;   - 输入以下任意一个地址：&#10;     - `sec.zy.com`&#10;     - `124.71.208.207`&#10;&#10;4. **确认并保存**&#10;   - 点击“确认”或“保存”，然后继续扫码登录或进行下一步操作。&#10;&#10;**💡 提示**:  &#10;- 如果提示连接失败，可以尝试切换为 `124.71.208.207` 地址。  &#10;- 若仍然无法连接，可尝试重置控制器设置后重新输入地址。  &#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于如何连接电脑到打印机,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载并安装驱动**&#10;   - 根据操作系统（MAC或Windows）从【京瓷打印机驱动下载】页面获取对应驱动包&#10;   - MAC用户：双击驱动包进行安装，若未找到可使用“command+空格键”搜索驱动程序&#10;   - Windows用户：解压驱动包后，双击Setup.exe文件，按提示完成自定义安装&#10;&#10;2. **添加打印机**&#10;   - **MAC系统**：&#10;     - 进入“系统偏好设置” &gt; “打印机与扫描仪”&#10;     - 点击“+”号添加打印机&#10;     - 选择“IP地址连接”，输入打印机的IP地址，并选择正确的协议&#10;   - **Windows系统**：&#10;     - 打开“控制面板” &gt; “查看设备和打印机”&#10;     - 点击“添加打印机”，根据提示输入打印机IP地址和型号信息&#10;&#10;3. **检查网络连接**&#10;   - 如果无法识别打印机，请检查网线是否松动或打印机是否正常联网&#10;&#10;4. **完成配置**&#10;   - 安装完成后建议重启电脑以确保驱动生效&#10;   - 可在打印机属性中修改名称、设置双面打印等选项&#10;&#10;**💡 提示**:  &#10;- 安装前请确认已知打印机的IP地址和型号  &#10;- 若打印机显示“已暂停”，可在Windows的“设备和打印机”中取消暂停状态  &#10;- 如遇到问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何获取共享盘密码**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **确认业务类型和校区名称**  &#10;   共享盘的用户名和密码是根据业务类型和校区来设定的。例如：  &#10;   - 成长-班辅（用户名：`fdb`）  &#10;   - 亲子-个辅（用户名：`gf`）  &#10;   - 志业（用户名：`sgz`）  &#10;&#10;2. **按照规则生成密码**  &#10;   密码格式为：`zy + 校区缩写 + 业务缩写`  &#10;   举例说明：  &#10;   - 如果是“鸟巢成长校区”，则密码为 `zyncfdb`（zy + nc + fdb）。  &#10;   - 如果是“启航亲子校区”，则密码为 `zyqhg`（zy + qh + gf）。&#10;&#10;3. **特殊情况：课室一体机共享文件夹**  &#10;   - 用户名：`ks`  &#10;   - 密码：`ks`  &#10;   （注意：该文件夹只有读取权限，没有写入权限）&#10;&#10;**💡 提示**:  &#10;- 如果忘记密码或遇到连接问题，可以尝试删除系统中保存的凭证后重新连接。  &#10;- 如仍有问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何查看263邮箱账号是否被禁用**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业微信检查邮箱状态**&#10;   - 打开企业微信，进入【工作台】&#10;   - 点击【IT服务台】 &gt; 【更多功能】 &gt; 【邮箱密码重置】&#10;   - 如果提示“账号已被禁用，请联系企业管理员了解详情”，则说明该邮箱账号已被禁用&#10;&#10;2. **尝试登录263邮箱网页版**&#10;   - 访问263邮箱官网并尝试登录&#10;   - 如果提示“用户邮箱状态异常”或“账号已被禁用”，则表示账号存在问题&#10;&#10;3. **重新绑定企业微信邮箱**&#10;   - 登录企业微信，进入【工作台】 &gt; 【263企业邮箱】&#10;   - 输入邮箱和密码进行绑定&#10;   - 如果无法绑定且提示错误信息，则可能是账号被禁用&#10;&#10;**💡 提示**:  &#10;- 若发现账号被禁用，建议联系企业IT管理员或提交OA权限申请，请求协助恢复账号。  &#10;- 也可以在OA系统中发起【账户/权限申请】流程，描述详细需求。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何登录零信任系统**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **安装零信任客户端**  &#10;   下载并双击打开零信任安装包，点击“是” → 点击“我同意” → 选择安装位置（默认即可）→ 点击“安装”，等待安装完成。&#10;&#10;2. **运行零信任客户端**  &#10;   安装完成后，默认会在桌面生成图标。双击打开“零信任”客户端。&#10;&#10;3. **输入控制器地址**  &#10;   如果第一次安装提示需要输入控制器地址，请输入 `sec.zy.com` 或 `124.71.208.207`，点击确认。&#10;&#10;4. **扫码登录**  &#10;   在零信任客户端中进入“扫码登录”界面，使用企业微信扫描二维码进行登录。&#10;&#10;5. **访问内网应用**  &#10;   登录成功后，即可通过浏览器访问内部系统和应用。&#10;&#10;**💡 提示**:  &#10;- 如果扫码登录失败或提示认证错误，可尝试重新进入扫码登录界面。  &#10;- 若登录后无法访问某些应用，建议关闭浏览器并刷新策略，或退出零信任后重新登录。  &#10;- 若电脑上有IOA软件，建议卸载以避免冲突。  &#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何安装课室共享文件夹**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **访问共享文件夹**&#10;   - 点击【我的电脑】或【此电脑】，点击左上角，输入校区共享IP地址 `\\192.168.0.26`，然后点击回车。&#10;&#10;2. **输入账号密码连接共享**&#10;   - 在弹出的安全验证窗口中，输入用户名和密码：&#10;     - 用户名：`ks`&#10;     - 密码：`ks`&#10;   - 勾选“记住我的凭据”以便下次自动登录（如需）。&#10;&#10;3. **创建桌面快捷方式**&#10;   - 在需要创建快捷方式的共享文件夹上，点击【右键】，选择【创建快捷方式】。&#10;   - 此时会在桌面上生成该共享文件夹的快捷方式，方便快速访问。&#10;&#10;4. **设置开机自动挂载（可选）**&#10;   - 打开系统偏好设置，点选“用户和群组”。&#10;   - 在左侧列表中选择你的用户名，点选“登录项”标签。&#10;   - 将已经挂载的网络驱动器图标拖放到登录项列表中。&#10;   - 可选：勾选“隐藏”，这样系统启动和登录时挂载网络驱动器后，不会自动打开 Finder 窗口。&#10;&#10;**💡 提示**:  &#10;- 如果无法正常连接共享盘，请尝试删除Windows凭证并重新连接。方法是按 WIN + R，输入 `control`，进入“凭证管理器”，找到 `192.168.0.26` 并删除，重启电脑后重新连接。  &#10;- 如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何下载零信任系统**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **打开浏览器，访问下载链接**  &#10;   在浏览器中输入以下链接进行下载：  &#10;   `https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe`  &#10;&#10;2. **保存安装包**  &#10;   浏览器会提示你“是否保存文件”，点击“保存”按钮，选择一个合适的存储位置（如桌面或下载文件夹）。&#10;&#10;3. **开始安装**  &#10;   下载完成后，双击运行下载的安装包（`TrustCyberLink_PC_Setup_2.207.121.exe`），按照安装向导提示完成安装。&#10;&#10;**💡 提示**: 如果电脑上已安装安全助手，请先卸载安全助手再安装零信任工具。管理员口令和安全助手卸载码均为 `e2vPsv8$`。"/>
-        <filter val="好的!关于**如何重置TMS通行证密码**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业微信进入IT服务台**  &#10;   打开企业微信，依次点击【工作台】-【IT服务台】-【更多功能】-【通行证密码重置】&#10;&#10;2. **按照指引完成密码重置流程**  &#10;   进入通行证密码重置页面后，根据系统提示填写相关信息并提交，完成密码重置。&#10;&#10;**💡 提示**: 如果在使用中有其他问题，可以联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**在笔记本安装海康4200客户端设置**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载客户端**&#10;   - 打开浏览器，复制并粘贴以下链接进行下载：&#10;     ```&#10;     https://partners.hikvision.com/tools/tooldetail?id=599912121330368512&#10;     ```&#10;&#10;2. **以管理员身份运行安装程序**&#10;   - 右击下载的 `ivms-4200` 安装文件，选择【以管理员身份运行】。&#10;   - 在弹出的提示框中点击【是】继续。&#10;&#10;3. **接受协议并下一步**&#10;   - 勾选【我接受许可证协议条款】，然后点击【下一步】按钮。&#10;&#10;4. **选择安装功能和路径**&#10;   - 在“请选择要安装的功能”界面，仅勾选【视频】选项。&#10;   - 在“目标文件夹”中，建议将安装路径切换到非C盘（如D盘或E盘），然后点击【安装】按钮开始安装。&#10;&#10;5. **设置账号和密码**&#10;   - 安装完成后打开软件。&#10;   - 设置监控用户名为：`user`，密码为：`345110jk`。&#10;   - 如果需要添加录像机设备，进入【设备管理】—【设备】进行添加。&#10;&#10;6. **主预览与远程回放**&#10;   - 程序默认进入主预览界面。&#10;   - 如需进行远程回放，请根据系统指引操作。&#10;&#10;**💡 提示**:  &#10;- 为了保证系统稳定性，建议不要将软件安装在C盘。  &#10;- 若遇到登录问题，请确认输入的用户名和密码是否正确，并检查网络连接是否正常。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何获取零信任控制地址**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **安装零信任客户端**&#10;   - 下载并运行零信任安装包。&#10;   - 双击打开安装包，点击“我同意”并选择安装位置（默认即可）。&#10;   - 等待安装完成，系统会默认勾选运行零信任。&#10;&#10;2. **首次启动零信任时输入控制器地址**&#10;   - 安装完成后，第一次打开零信任时会提示输入控制器地址。&#10;   - 输入以下任意一个地址：&#10;     - `sec.zy.com`&#10;     - `124.71.208.207`&#10;   - 点击确认后即可扫码登录使用。&#10;&#10;3. **切换控制器地址（如需要）**&#10;   - 如果连接失败或遇到问题，可以在零信任界面中选择“切换控制器”。&#10;   - 手动输入 `124.71.208.207` 或 `sec.zy.com` 作为控制器地址。&#10;&#10;**💡 提示**:  &#10;- 控制器地址是零信任软件连接到企业网络的核心配置，确保输入正确。  &#10;- 如仍有问题，建议联系IT帮助台获取最新版本安装包并覆盖安装。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于如何获取企业门户网址,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过电脑端登录**  &#10;   直接在浏览器中输入网址：【卓越企业门户】，即可访问。&#10;&#10;2. **通过手机端登录**  &#10;   打开企业微信 → 进入“工作台” → 找到并点击【BPM】或相关系统入口。&#10;&#10;**💡 提示**: 如果无法直接访问，请确认是否已开通权限（入职时会自动开通）。如遇到登录问题，可通过企业微信-工作台-IT服务台-更多功能联系IT服务台协助处理。"/>
-        <filter val="好的!关于**零信任控制器连接失败问题**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **切换控制器地址**  &#10;   打开零信任客户端，选择“控制器”选项，将地址切换为 `124.71.208.207`。&#10;&#10;2. **重置控制器并重新输入地址**  &#10;   如果切换控制器地址后仍然无法连接，尝试以下步骤：  &#10;   - 在客户端中选择“重置控制器”功能；  &#10;   - 重置完成后，再次手动输入控制器地址 `124.71.208.207`。&#10;&#10;**💡 提示**: 如果以上方法仍无法解决，请检查网络是否正常，并确保防火墙或安全软件没有拦截相关端口。如有需要，可联系IT支持进一步排查。"/>
-        <filter val="好的!关于在Windows系统上安装京瓷打印机驱动，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载打印机驱动包**  &#10;   访问【京瓷打印机驱动下载】页面，将驱动包保存到电脑硬盘。&#10;&#10;2. **解压驱动包**  &#10;   找到下载的驱动包并进行解压。&#10;&#10;3. **运行安装程序**  &#10;   进入解压后的文件夹，双击 `Setup.exe` 文件启动安装程序。&#10;&#10;4. **选择自定义安装**  &#10;   在安装过程中，点击“接受”，并选择“自定义安装”以根据需要添加组件。&#10;&#10;5. **填写打印机信息**  &#10;   根据提示输入打印机的实际型号和IP地址（可在打印机上查询）。&#10;&#10;6. **完成安装**  &#10;   安装完成后，系统会自动添加打印机驱动和相关组件。&#10;&#10;**设置打印机**&#10;&#10;1. **修改名称与设置双面打印**  &#10;   - 打开控制面板 &gt; 硬件和设备 &gt; 右键打印机 &gt; 选择“打印机属性”。  &#10;   - 修改打印机名称，并在选项中设置“双面打印”。&#10;&#10;2. **处理脱机问题**  &#10;   如果打印机显示为脱机状态，请进入打印机属性，取消SNMP设置。&#10;&#10;3. **添加部门ID（如需）**  &#10;   部分共用打印机需要输入部门密码或ID，按照提示操作即可。&#10;&#10;**💡 提示**: 安装前请确保已正确获取打印机的IP地址和型号。如果遇到网络连接问题，请检查网线是否松动或打印机是否正常联网。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何安装零信任系统**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载安装包**  &#10;   访问以下链接下载零信任工具安装包：  &#10;   `https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe`&#10;&#10;2. **运行安装程序**  &#10;   双击打开下载的安装包，点击“是”继续安装。&#10;&#10;3. **同意协议**  &#10;   在安装界面中点击“我同意”。&#10;&#10;4. **选择安装位置（可选）**  &#10;   你可以自定义安装路径，也可以使用默认路径。点击“安装”继续。&#10;&#10;5. **等待安装完成**  &#10;   安装过程可能需要几分钟，请耐心等待直到提示安装完成。&#10;&#10;6. **启动零信任**  &#10;   安装完成后，默认会勾选“运行零信任”，桌面上会出现零信任图标。你也可以手动双击图标启动。&#10;&#10;7. **扫码登录**  &#10;   打开零信任后，使用二维码进行扫码登录，即可通过浏览器访问内部系统。&#10;&#10;8. **输入控制器地址（如需）**  &#10;   如果第一次安装时提示需要输入控制器地址，请输入 `sec.zy.com` 或 `124.71.208.207`，然后点击确认并扫码登录。&#10;&#10;**💡 提示**:  &#10;- 如果安装过程中遇到问题，可以尝试重新安装。  &#10;- 若安装后未显示零信任图标，可能是与IOA冲突，建议前往安装目录 `C:\Program Files (x86)\TrustCyberLink` 下手动运行 `TrustCyberLink.exe`。  &#10;- 登录后请勿退出零信任，否则可能导致无法访问内部系统。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何安装打印机驱动**,具体操作如下:&#10;&#10;---&#10;&#10;### **操作步骤**&#10;&#10;#### 1. **下载打印机驱动包**&#10;- 根据您的操作系统（Windows 或 MAC）和打印机型号，前往对应官网下载驱动：&#10;  - **京瓷打印机驱动下载**：适用于 Windows 系统&#10;  - **京瓷打印机 Mac 驱动下载**：适用于 MAC 系统&#10;  - 其他品牌如理光、富士施乐、佳能等，可参考以下链接：&#10;    - [理光MPC5503](http://support.ricoh.com/bb/html/dr_ut_e/rcn1/model/mp4503/mp4503.htm)&#10;    - [理光MP6054](http://support.ricoh.com/bb/html/dr_ut_e/rcn1/model/mp2554/mp2554.htm?lang=cn)&#10;    - [富士施乐P288/M288](https://m3support-fb.fujifilm-fb.com.cn/driver_downloads/www/)&#10;    - [佳能MF244/MF249](https://www.canon.com.cn/supports/download/sims/list/slist?fileTypeId=23&amp;categoryId=15&amp;seriesId=77&amp;modelId=1234&amp;OSName=Windows%2010%20(x64)&amp;channel=1)&#10;&#10;---&#10;&#10;#### 2. **安装打印机驱动（以 Windows 为例）**&#10;1. 解压下载的驱动包。&#10;2. 双击进入文件夹，运行 `Setup.exe` 安装程序。&#10;3. 按照提示进行安装，选择“自定义安装”。&#10;4. 在安装过程中填写正确的打印机 IP 地址和型号信息。&#10;5. 安装完成后，建议设置打印机名称和双面打印功能：&#10;   - 打开控制面板 &gt; 硬件和设备 &gt; 打印机 &gt; 右键目标打印机 &gt; 属性 &gt; 修改名称/设置双面打印。&#10;&#10;---&#10;&#10;#### 3. **安装打印机驱动（以 MAC 为例）**&#10;1. 下载并解压驱动包。&#10;2. 双击安装程序开始安装。如果桌面找不到驱动，可通过快捷键 `Command + 空格键` 搜索驱动程序。&#10;3. 一路点击“继续”完成安装。&#10;4. 安装完成后，重启电脑。&#10;5. 添加打印机：&#10;   - 进入系统偏好设置 &gt; 打印机与扫描仪 &gt; 添加 &gt; 输入打印机 IP 地址和协议类型。&#10;&#10;---&#10;&#10;### **💡 提示**&#10;- 安装前请确保已获取打印机的 IP 地址和型号。&#10;- 如果打印机无法连接，请检查网络是否正常（例如网线是否松动）。&#10;- 如使用中有其他问题，可联系 IT 帮助台或在 OA 上填写 IT 报障单（OA 系统地址：[http://oa.zy.com](http://oa.zy.com)）。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何在MAC安装零信任**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载零信任安装包**  &#10;   访问以下链接下载适用于Mac的零信任安装文件：  &#10;   [https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.120.dmg](https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.120.dmg)&#10;&#10;2. **挂载并打开安装包**  &#10;   下载完成后，双击 `.dmg` 文件进行挂载。系统会自动弹出安装程序窗口。&#10;&#10;3. **将零信任图标拖入“应用程序”文件夹**  &#10;   在弹出的窗口中，将“零信任”图标拖拽到“Applications（应用程序）”文件夹中，完成安装。&#10;&#10;4. **启动零信任**  &#10;   打开“应用程序”文件夹，找到“零信任”，双击运行。首次启动时可能需要确认权限或输入密码以提权。&#10;&#10;5. **扫码登录**  &#10;   启动后，使用企业微信扫码登录即可访问内部系统。&#10;&#10;6. **设置DNS（如需）**  &#10;   如果网络设置中 DNS 包含 `127.0.0.1`，建议将其删除以避免冲突：&#10;   - 打开“系统设置” &gt; “网络” &gt; 选择当前网络 &gt; 点击“高级” &gt; DNS&#10;   - 删除 `127.0.0.1` 并保存&#10;&#10;**💡 提示**:  &#10;- 如果提示密码错误，请检查是否设置了复杂密码字符串，可尝试修改密码后再试。&#10;- 若未显示企业微信按钮，可点击控制切换器，输入 `sec.zy.com` 或 `124.71.208.207` 解决问题。"/>
-        <filter val="好的!关于在Windows系统上安装打印机，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载并解压驱动包**  &#10;   从【京瓷打印机驱动下载】页面获取对应型号的驱动包，并将其保存到电脑硬盘。解压该驱动包。&#10;&#10;2. **启动安装程序**  &#10;   进入解压后的文件夹，双击 `Setup.exe` 文件以启动安装程序。&#10;&#10;3. **选择自定义安装**  &#10;   在安装过程中，点击“接受”协议，然后选择“自定义安装”。&#10;&#10;4. **填写打印机信息**  &#10;   根据提示输入打印机的实际型号和IP地址（可在打印机屏幕或网络设置中查询）。&#10;&#10;5. **完成驱动安装**  &#10;   安装过程中会添加打印机驱动并安装相关组件，直至安装完成。&#10;&#10;6. **设置打印机属性**  &#10;   - 打开【控制面板】 → 【硬件和设备】 → 右键目标打印机 → 选择【打印机属性】。&#10;   - 修改打印机名称、设置双面打印等选项。&#10;&#10;**💡 提示**:  &#10;- 如果打印机显示脱机，请尝试取消SNMP设置。  &#10;- 若需要添加部门ID，请参考额外指引进行配置。  &#10;- 安装完成后建议重启电脑以确保驱动生效。  &#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于在Windows上安装零信任,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载安装包**  &#10;   访问零信任工具的下载链接：  &#10;   `https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe`  &#10;&#10;2. **运行安装程序**  &#10;   双击打开下载的安装包，点击“是”继续安装。&#10;&#10;3. **同意协议**  &#10;   在安装界面中点击“我同意”。&#10;&#10;4. **选择安装位置（可选）**  &#10;   你可以自定义安装位置，也可以使用默认路径。点击“安装”继续。&#10;&#10;5. **等待安装完成**  &#10;   安装过程中请耐心等待，直到提示安装完成。&#10;&#10;6. **启动零信任**  &#10;   安装完成后，默认会勾选运行零信任。你可以在桌面上看到零信任图标。&#10;&#10;7. **扫码登录**  &#10;   打开零信任客户端，使用二维码进行扫码登录，即可通过浏览器访问内部系统。&#10;&#10;8. **输入控制器地址（如需）**  &#10;   如果第一次安装时提示需要输入控制器地址，请输入 `sec.zy.com` 或 `124.71.208.207`，然后点击确认并扫码登录。&#10;&#10;**💡 提示**: 如果安装后未显示零信任图标，可以前往安装目录 `C:\Program Files (x86)\TrustCyberLink` 下手动运行 `TrustCyberLink.exe`。如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何卸载零信任系统**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **打开控制面板**  &#10;   按下 `Win + R` 键，输入 `control`，然后按回车。&#10;&#10;2. **进入卸载程序界面**  &#10;   在控制面板中点击“卸载程序”或“程序和功能”。&#10;&#10;3. **双击卸载**  &#10;   找到“零信任”程序，双击进行卸载。&#10;&#10;4. **完成卸载流程**  &#10;   按照提示完成卸载过程，直至卸载成功。&#10;&#10;**💡 提示**: 如果在使用过程中遇到问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何查看浏览器监控信息**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **确保系统和浏览器要求**&#10;   - 电脑系统为 Windows 10 或以上版本&#10;   - 使用 Microsoft Edge 浏览器，并启用 Internet Explorer 模式&#10;&#10;2. **设置Edge浏览器的IE模式**&#10;   - 打开 Edge 浏览器，点击右上角的 **三个点**，进入 **设置**&#10;   - 在搜索框中输入 **Explorer**&#10;   - 向下滚动找到 **“允许在 Internet Explorer 模式下重新加载网站”**，选择 **允许**&#10;   - 此时，右上角的 **三个点** 菜单中会出现一个选项：**“在 Internet Explorer 模式下重新加载”**&#10;&#10;3. **访问监控IP地址**&#10;   - 在网页搜索框中输入监控 IP 地址（如 `192.168.0.X`，X范围一般为5~10）&#10;   - 进入登录界面后，先点击右上角 **三个点**，选择 **“在 Internet Explorer 模式下重新加载”**&#10;   - 然后输入账号密码进行登录&#10;&#10;4. **首次使用提示下载插件**&#10;   - 首次使用可能会提示下载插件，根据页面提示完成下载即可&#10;   - 左上角点击 **【e】标志**，开启兼容性并设置下次自动在 IE 模式下打开&#10;&#10;**💡 提示**:  &#10;- 登录账号可参考以下：&#10;  - (有回放功能)普通用户1: `userxq` 密码: `345110xq`&#10;  - (无回放功能)普通用户2: `user` 密码: `345110jk`&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何安装零信任系统**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载安装包**  &#10;   访问以下链接下载零信任工具安装包：  &#10;   `https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe`&#10;&#10;2. **运行安装程序**  &#10;   双击打开下载的安装包，点击“是”继续安装。&#10;&#10;3. **同意协议**  &#10;   在安装界面中点击“我同意”。&#10;&#10;4. **选择安装位置（可选）**  &#10;   你可以自定义安装路径，也可以使用默认路径。点击“安装”继续。&#10;&#10;5. **等待安装完成**  &#10;   安装过程可能需要几分钟，请耐心等待直到提示安装完成。&#10;&#10;6. **启动零信任**  &#10;   安装完成后，默认会勾选“运行零信任”，桌面上会出现零信任图标。你也可以手动双击图标启动。&#10;&#10;7. **扫码登录**  &#10;   打开零信任后，使用二维码进行扫码登录，即可通过浏览器访问内部系统。&#10;&#10;8. **输入控制器地址（如需）**  &#10;   如果第一次安装时提示需要输入控制器地址，请输入 `sec.zy.com` 或 `124.71.208.207`，然后确认并扫码登录。&#10;&#10;**💡 提示**:  &#10;- 如果安装过程中遇到问题，可以尝试重新安装。  &#10;- 若安装后未显示零信任图标或功能异常，可参考安装目录下的 `C:\Program Files (x86)\TrustCyberLink` 路径下运行 `TrustCyberLink.exe`。  &#10;- 如遇网络设置冲突（如DNS设置为127.0.0.1），请清除该设置以确保正常联网。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何安装零信任**，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载安装包**  &#10;   访问以下链接下载零信任工具安装包：  &#10;   `https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe`&#10;&#10;2. **运行安装程序**  &#10;   双击打开下载的安装包，点击“是”继续安装。&#10;&#10;3. **同意协议**  &#10;   在安装界面中点击“我同意”。&#10;&#10;4. **选择安装位置（可选）**  &#10;   你可以自定义安装位置，也可以使用默认路径。点击“安装”继续。&#10;&#10;5. **等待安装完成**  &#10;   安装过程会自动进行，等待提示“安装完成”。&#10;&#10;6. **启动零信任**  &#10;   安装完成后，默认勾选运行零信任。你可以在桌面上看到“零信任”图标。&#10;&#10;7. **扫码登录**  &#10;   打开零信任客户端，使用二维码扫描登录即可访问内部系统。&#10;&#10;8. **输入控制器地址（如需）**  &#10;   如果第一次安装时提示需要输入控制器地址，请输入 `sec.zy.com` 或 `124.71.208.207`，然后点击确认并扫码登录。&#10;&#10;**💡 提示**:  &#10;- 如果安装过程中遇到问题，可以尝试重新安装。  &#10;- 若安装后未显示零信任图标，可能是与IOA冲突，建议前往安装目录 `C:\Program Files (x86)\TrustCyberLink` 下手动运行 `TrustCyberLink.exe`。  &#10;- 推荐设置控制器地址为 `124.71.208.207` 以获得最佳体验。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何获取预数系统账号密码**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **使用员工通行证登录**  &#10;   预数系统的登录账号和密码是通过员工通行证进行认证的，无需单独注册。&#10;&#10;2. **找回密码**  &#10;   如果你修改过密码并忘记了，可以通过以下链接找回：  &#10;   https://ucin.zy.com/forgot_password&#10;&#10;**💡 提示**: 系统仅支持谷歌浏览器访问，建议使用最新版本的谷歌浏览器以确保兼容性。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何清理C盘空间**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **使用系统自带的磁盘清理工具**  &#10;   按下 `Win` 键，搜索并打开“磁盘清理”，选择C盘进行清理。&#10;&#10;2. **转移微信个人数据文件**  &#10;   打开微信 → 点击“设置” → 选择“文件管理” → 进入“文件管理”文件夹 → 点击“更改” → 将存储位置更改为C盘以外的其他盘符。这样可以释放大量C盘空间。&#10;&#10;3. **清理临时文件（%temp%）**  &#10;   按下 `Win + R` → 输入 `%temp%` → 全选所有文件并删除。&#10;&#10;4. **手动清理微信缓存文件**  &#10;   登录微信 → 点击左下角按钮 → 进入“设置” → 点击“文件管理” → 打开FileStorage文件夹 → 分别进入以下子文件夹进行按月份删除：&#10;   - **Cache**：可选择性或全部删除缓存文件&#10;   - **Files**：删除不需要的Word、Excel等文件&#10;   - **Image**：删除加密图片（注意不能直接查看）&#10;   - **Video**：删除占用较大的视频文件&#10;&#10;5. **提前清理C盘空间以避免程序报错**  &#10;   如果发现C盘空间已满，请在运行某些软件前先清理出一部分空间，以免出现如“程序文件缺失 CefSharp”等错误提示。&#10;&#10;**💡 提示**: 清理前请确保重要文件已备份，删除后无法恢复。如有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）。"/>
-        <filter val="好的!关于**如何登录监控系统4200客户端**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载并安装客户端**  &#10;   打开浏览器，访问海康客户端的下载地址：https://partners.hikvision.com/tools/tooldetail?id=599912121330368512  &#10;   下载完成后，右击安装包，选择【以管理员身份运行】，点击【是】继续安装。&#10;&#10;2. **设置安装选项**  &#10;   - 勾选【我接受许可证协议条款】，点击【下一步】。  &#10;   - 在“请选择要安装的功能”界面，仅勾选【视频】功能。  &#10;   - 选择安装路径为非C盘（如D盘或E盘），然后点击【安装】按钮完成安装。&#10;&#10;3. **启动客户端并添加设备**  &#10;   - 双击桌面快捷方式打开 `iVMS-4200` 客户端。  &#10;   - 进入主界面后，点击右侧的【设备管理】&gt;【设备】。  &#10;   - 点击【添加】按钮，输入监控设备的IP地址、端口号等信息。&#10;&#10;4. **设置账号和密码**  &#10;   - 在设备管理界面中，选择需要配置的监控设备，点击【笔形状图标】进行编辑。  &#10;   - 输入以下账号之一：&#10;     - (有回放功能) 普通用户1: `userxq` 密码: `345110xq`  &#10;     - (无回放功能) 普通用户2: `user` 密码: `345110jk`&#10;&#10;5. **确认连接状态**  &#10;   - 设置完成后，如果设备状态显示为【在线】，表示连接成功，可以正常使用监控功能。&#10;&#10;**💡 提示**: 如果遇到问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**零信任无法连接控制器**的问题,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **切换控制器地址**  &#10;   打开零信任客户端，找到控制器设置选项，将控制器地址切换为 `124.71.208.207` 或 `sec.zy.com`。&#10;&#10;2. **重置控制器并重新输入地址**  &#10;   如果切换控制器地址后问题仍未解决，尝试选择“重置控制器”功能，然后再次输入 `124.71.208.207` 或 `sec.zy.com`。&#10;&#10;**💡 提示**:  &#10;- 确保网络连接正常，并且没有防火墙或代理限制访问该地址。  &#10;- 如果仍然无法连接，请联系IT帮助台获取进一步支持。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**在希沃一体机更换壁纸**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **进入“壁纸”文件夹**  &#10;   打开教学一体机的D盘，找到名为“壁纸”的文件夹并进入。&#10;&#10;2. **准备壁纸图片**  &#10;   - 确保要设置的壁纸为 **jpg格式**。如果不是，请先将其转换为jpg格式。&#10;   - 将图片重命名为 **“1.jpg”**（注意：必须使用这个名称）。&#10;&#10;3. **备份旧壁纸（可选）**  &#10;   如果需要保留当前壁纸作为备份，可以将原来的“1.jpg”重命名为“3.jpg”。&#10;&#10;4. **替换壁纸**  &#10;   将新准备好的“1.jpg”复制到“壁纸”文件夹中，覆盖原有的文件。&#10;&#10;5. **等待生效**  &#10;   返回教学一体机桌面，等待约 **1分钟**，新的壁纸将会自动显示。&#10;&#10;**💡 提示**:  &#10;- 壁纸图片建议尺寸与屏幕匹配，以获得最佳显示效果。  &#10;- 如有其他问题，可联系IT帮助台或在OA上填写IT报障单（[OA系统地址](http://oa.zy.com)）。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于苹果电脑无法连接零信任控制器问题,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **切换控制器地址**  &#10;   打开零信任客户端，进入控制器设置，将控制器地址切换为 `124.71.208.207`。&#10;&#10;2. **重置控制器并重新输入地址**  &#10;   如果切换控制器地址后仍无法连接，尝试选择“重置控制器”，然后再次输入 `124.71.208.207` 进行连接。&#10;&#10;3. **修改 hosts 文件（适用于 JavaScript 错误）**  &#10;   打开终端，执行命令：  &#10;   ```&#10;   sudo vi /etc/hosts&#10;   ```  &#10;   在文件中添加以下内容：  &#10;   ```&#10;   127.0.0.1 localhost&#10;   ```  &#10;   保存并退出，然后重启零信任客户端。&#10;&#10;4. **清除本地 DNS 设置**  &#10;   如果退出零信任后无法访问外网，检查是否设置了本地 DNS 为 `127.0.0.1`。请将其删除或改为自动获取 DNS 设置。&#10;&#10;5. **卸载冲突软件**  &#10;   卸载可能与零信任冲突的第三方杀毒软件（如火绒、360等），并禁用不必要的开机启动项。&#10;&#10;**💡 提示**: 如果以上方法均无效，建议联系IT帮助台获取最新版本安装包并覆盖安装。"/>
-        <filter val="好的!关于在Windows系统安装零信任,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载安装包**  &#10;   访问零信任工具的下载链接：  &#10;   `https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe`  &#10;&#10;2. **运行安装程序**  &#10;   双击打开下载的安装包，点击“是”继续安装。&#10;&#10;3. **同意协议**  &#10;   在安装界面中点击“我同意”。&#10;&#10;4. **选择安装位置（可选）**  &#10;   你可以自定义安装位置，也可以使用默认路径。点击“安装”继续。&#10;&#10;5. **等待安装完成**  &#10;   安装过程中请耐心等待，直到提示安装完成。&#10;&#10;6. **启动零信任**  &#10;   安装完成后，默认会勾选运行零信任。你可以在桌面上看到零信任图标。&#10;&#10;7. **扫码登录**  &#10;   打开零信任客户端，使用二维码进行扫码登录，即可通过浏览器访问内部系统。&#10;&#10;8. **输入控制器地址（如需）**  &#10;   如果第一次安装时提示需要输入控制器地址，请输入 `sec.zy.com` 或 `124.71.208.207`，然后点击确认并扫码登录。&#10;&#10;**💡 提示**: 如果安装后未显示零信任图标，可以前往安装目录 `C:\Program Files (x86)\TrustCyberLink` 下手动运行 `TrustCyberLink.exe`。如有其他问题，可联系IT帮助台或在OA上填写IT报障单。"/>
-        <filter val="好的!关于**在零信任输入控制器地址**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **打开零信任客户端**&#10;   - 启动已安装的零信任工具。&#10;&#10;2. **切换控制器地址**&#10;   - 在登录界面或设置中找到“控制器地址”选项。&#10;   - 将默认地址更改为 `124.71.208.207`（推荐使用此地址）。&#10;&#10;3. **确认并保存设置**&#10;   - 输入完成后点击“确认”或“应用”，确保更改生效。&#10;&#10;4. **重新扫码登录**&#10;   - 使用企业微信或其他方式重新扫码登录，以使新设置生效。&#10;&#10;**💡 提示**:  &#10;- 如果更改后仍无法连接，请尝试重置控制器设置后再重新输入地址。  &#10;- 若问题仍未解决，建议联系IT帮助台获取进一步支持。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何使用263邮箱**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **登录263邮箱**&#10;   - 打开浏览器，访问 [https://www.263.net](https://www.263.net)&#10;   - 输入您的企业邮箱账号和密码&#10;   - 如果是首次登录，需要绑定手机号码：&#10;     - 输入有效的手机号码并获取短信验证码&#10;     - 验证成功后即可完成登录&#10;&#10;2. **发送邮件**&#10;   - 登录后点击【写信】按钮&#10;   - 填写收件人、主题和正文内容&#10;   - 点击【发送】按钮&#10;&#10;3. **修改密码**&#10;   - 通过企业微信修改密码：&#10;     - 登录企业微信 &gt; 【工作台】&gt;【IT服务台】&gt;【更多功能】&gt;【邮箱密码重置】&#10;   - 或通过网页自助修改：&#10;     - 访问 [https://mm.263.com/wm2e/website/jsp/resetPassword.jsp](https://mm.263.com/wm2e/website/jsp/resetPassword.jsp)&#10;&#10;4. **设置IMAP/SMTP服务器**&#10;   - 推荐使用 IMAP + SMTP 组合方式&#10;   - 在邮箱客户端中配置服务器地址（详见官方指引或联系IT支持）&#10;&#10;5. **处理可疑邮件**&#10;   - 如收到钓鱼或病毒邮件，请不要点击任何链接或附件&#10;   - 将邮件原件转发至 `sec-team@zy.com` 由安全专家审核&#10;&#10;6. **更换绑定手机号**&#10;   - 如果旧手机号无法接收验证码，需在OA系统提交申请：&#10;     - 登录 OA 系统 &gt; 搜索【账户/权限申请】&gt; 选择【263邮箱】&gt; 提交手机号变更请求&#10;&#10;7. **使用手机APP**&#10;   - 下载263邮箱APP：&#10;     - iPhone 用户：扫描二维码下载&#10;     - Android 用户：扫描二维码下载&#10;&#10;8. **设置邮件归档周期**&#10;   - 登录邮箱 &gt; 点击右上角【账户】头像 &gt;【设置】&gt;【文件夹管理】&#10;   - 设置【正常邮件归档时间】&#10;&#10;**💡 提示**:  &#10;- 密码规则要求包含大小写字母、数字和符号，长度不少于8位，不能使用简单或连续字符。  &#10;- 若遇到邮箱状态异常，请先通过企业微信重置密码并重新绑定。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何清理电脑C盘满问题**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **使用系统自带磁盘清理工具**  &#10;   按下 `Win` 键，搜索并打开“磁盘清理”，选择C盘进行清理。&#10;&#10;2. **转移微信个人数据文件**  &#10;   打开微信—&gt;进入“设置”—&gt;选择“文件管理”—&gt;点击“更改”将微信的个人数据文件存储位置更改为C盘以外的其他盘符。&#10;&#10;3. **转移企业微信个人数据文件**  &#10;   打开企业微信—&gt;进入“设置”—&gt;选择“存储管理”，将数据存储路径修改为非C盘的位置。&#10;&#10;4. **清理临时文件**  &#10;   按下 `Win + R` 键，输入 `%temp%` 并回车，全选临时文件夹中的内容并删除。&#10;&#10;5. **手动删除无用文件或程序**  &#10;   定期检查C盘中是否有不再需要的大文件或安装包，并手动删除。也可以卸载不常用的软件以释放空间。&#10;&#10;**💡 提示**: 清理前建议备份重要数据，避免误删；如仍有问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何获取监控系统账号密码**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **使用默认账号登录**&#10;   - (有回放功能)普通用户1:  &#10;     **用户名**: `userxq`  &#10;     **密码**: `345110xq`&#10;   - (无回放功能)普通用户2:  &#10;     **用户名**: `user`  &#10;     **密码**: `345110jk`&#10;&#10;2. **切换账号（在客户端中）**&#10;   - 打开监控客户端“iVMS-4200 3.13.0.5 客户端”&#10;   - 在主菜单界面的右边找到“设备管理”&#10;   - 选择需要更改的监控，点击“笔形状图标”&#10;   - 修改账号和密码，切换到有回放功能的账号&#10;&#10;3. **添加或删除录像机时使用的账号**&#10;   - 添加/删除录像机时，同样可以使用上述两个账号之一进行操作&#10;&#10;**💡 提示**: 如果遇到无法登录或其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）。"/>
-        <filter val="好的!关于**零信任无法连接控制器问题**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **切换控制器地址**  &#10;   打开零信任客户端，选择“控制器”选项，将地址切换为 `124.71.208.207`。&#10;&#10;2. **重置控制器并重新输入地址**  &#10;   如果切换控制器地址后仍然无法解决，尝试以下步骤：  &#10;   - 在零信任客户端中选择“重置控制器”；  &#10;   - 重置完成后，再次手动输入控制器地址 `124.71.208.207`。&#10;&#10;**💡 提示**: 如果以上方法仍无效，建议联系IT帮助台进一步排查网络或软件问题。"/>
-        <filter val="好的!关于**零信任无法连接怎么解决**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **切换控制器地址**  &#10;   打开零信任客户端，选择控制器并切换为 `124.71.208.207` 地址。&#10;&#10;2. **重置控制器设置**  &#10;   如果切换控制器地址后仍无法连接，尝试重置控制器后再输入 `124.71.208.207`。&#10;&#10;3. **使用快捷登录方式**  &#10;   如果扫码登录提示“不合法的状态”或认证失败，返回上一级，去掉用户名，选择快捷登录方式。&#10;&#10;4. **检查IOA冲突**  &#10;   确认电脑上是否安装了 IOA（如已不再使用），建议卸载 IOA 并重启电脑。如果之前登录过 IOA，退出零信任后重新扫码登录。&#10;&#10;5. **清除本地DNS设置**  &#10;   如果退出零信任后无法访问外网，检查 DNS 设置：&#10;   - macOS：删除本地 DNS 中的 `127.0.0.1` 或设置为自动获取。&#10;   - Windows：同样修改为自动获取 DNS 设置。&#10;&#10;6. **卸载第三方杀毒软件**  &#10;   如果系统运行缓慢或弹窗频繁，卸载 360 安全卫士、火绒安全等第三方杀毒软件，并禁用不必要的开机启动项。&#10;&#10;7. **联系IT支持**  &#10;   如果以上方法均无效，可能是版本问题，建议联系 IT 帮助台获取最新版本安装包并覆盖安装。&#10;&#10;**💡 提示**: 在进行任何网络设置更改前，建议先备份当前配置；若涉及企业微信账号权限问题，可能需要管理员协助调整分组。"/>
-        <filter val="好的!关于**如何连接打印机**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载驱动包**  &#10;   根据您的系统（MAC 或 Windows）前往【京瓷打印机驱动下载】页面，下载对应的驱动包。&#10;&#10;2. **安装驱动**  &#10;   - **MAC 系统**: 双击驱动包进行安装。如果桌面找不到驱动，可通过“Command + 空格键”搜索驱动名称并双击安装。&#10;   - **Windows 系统**: 解压驱动包后，双击 `Setup.exe` 文件，选择自定义安装，并根据提示完成安装。&#10;&#10;3. **添加打印机**  &#10;   - **MAC 系统**:  &#10;     进入“系统偏好设置” &gt; “打印机与扫描仪” &gt; 点击“+”号添加打印机。选择“IP 地址连接”，输入打印机的 IP 地址和协议类型，完成添加。&#10;     &#10;   - **Windows 系统**:  &#10;     打开“控制面板” &gt; “查看设备和打印机” &gt; 点击“添加打印机”，按照提示输入打印机的 IP 地址和型号，完成添加。&#10;&#10;4. **检查网络连接**  &#10;   如果无法自动识别打印机，请检查打印机是否联网正常（如网线是否松动、IP 地址是否正确等）。&#10;&#10;5. **重启电脑**  &#10;   安装完成后建议重启电脑以确保驱动生效。&#10;&#10;**💡 提示**:  &#10;- 打印机的 IP 地址通常贴在打印机上或标签纸上。  &#10;- 如遇到问题，可联系 IT 帮助台或在 OA 上填写 IT 报障单（OA 系统地址：http://oa.zy.com）。  &#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何登录绩效与学习平台**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业门户登录**&#10;   - 打开浏览器，访问企业门户网址：https://ssoin.zy.com/login&#10;   - 使用您的企业邮箱账号和密码登录（如忘记密码可通过“忘记密码”功能重新设置）&#10;&#10;2. **进入绩效与学习平台**&#10;   - 登录后，在企业门户首页找到并点击「绩效人才系统」&#10;   - 在绩效人才系统中，选择「我的学习」即可进入学习平台&#10;&#10;3. **通过Italent系统登录**&#10;   - 直接在浏览器中输入网址：https://www.italent.cn/Login&#10;   - 输入您的企业邮箱账号和密码进行登录（首次使用可能需要重置密码）&#10;&#10;4. **通过企业微信跳转**&#10;   - 打开企业微信，查找“绩效与学习平台”的通知或链接&#10;   - 点击链接后可直接跳转至学习平台页面&#10;&#10;**💡 提示**:  &#10;- 推荐使用谷歌Chrome浏览器以获得最佳体验。  &#10;- 若是新员工，也可通过企业邮箱接收自动发送的学习通知，并点击链接直接进入学习平台。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于如何重置内部通行证密码,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **打开企业微信**&#10;   - 确保您已登录企业微信应用。&#10;&#10;2. **进入IT服务台**&#10;   - 点击【工作台】-【IT服务台】-【更多功能】-【通行证密码重置】&#10;&#10;**💡 提示**: 通行证密码与邮箱密码不同，且在使用时不需要输入@zy.com后缀。如遇到其他问题，可联系IT帮助台或在OA系统上填写IT报障单（OA地址：http://oa.zy.com）。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何获取兼职老师账号**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **登录企业微信后台**&#10;   - 打开浏览器，访问网址：[work.weixin.qq.com/login](https://work.weixin.qq.com/login)&#10;   - 使用企业微信扫码登录&#10;   - 如果未完成授权，系统会提示“当前微信号未注册企业”，请根据提示完成实名认证&#10;&#10;2. **添加兼职老师账号**&#10;   - 登录后台后，选择左侧导航栏的【老师管理-老师列表】&#10;   - 点击【新建老师】按钮&#10;   - 输入老师的手机号（作为账号），系统将自动为该老师创建一个学员账号，密码默认为手机尾号六位数字&#10;   - 点击【确认新增】，完成教师添加&#10;&#10;3. **权限生效**&#10;   - 添加完成后，兼职老师需要在企业微信手机端接收【企微微信团队】应用推送消息，并进行扫脸实名认证，权限才能正式生效&#10;&#10;**💡 提示**: 请确保兼职老师的手机号已绑定企业微信，并完成所有授权和实名认证流程。如有其他问题随时问我！"/>
-        <filter val="好的!关于**在mac上安装零信任**，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载安装包**  &#10;   从公司内部提供的资源或OA系统（地址：http://oa.zy.com）中下载零信任客户端的安装包。&#10;&#10;2. **打开安装包**  &#10;   双击下载的安装包，按照提示完成安装过程。如果安装后未显示“零信任”图标，请参考后续解决方案。&#10;&#10;3. **启动零信任**  &#10;   安装完成后，在应用程序中找到“零信任”，双击打开客户端。&#10;&#10;4. **扫码登录**  &#10;   打开零信任后，使用企业微信或其他指定方式扫码登录。如遇到登录问题，可尝试以下方法：&#10;   - 如果提示“不合法的状态”，返回上一级，去掉用户名，选择快捷登录方式。&#10;   - 如果无法显示快捷登录方式，可以随机输入一个用户名，再返回上一级选择快捷登录。&#10;&#10;5. **设置控制器地址（如需）**  &#10;   如果提示“连接控制器失败”，请在客户端中切换控制器地址为 `124.71.208.207` 或 `sec.zy.com`。若仍无法解决，可尝试重置控制器并重新输入该地址。&#10;&#10;6. **检查网络设置**  &#10;   确保本机网络的 DNS 设置中没有 `127.0.0.1`，如有请删除并保存。&#10;&#10;**💡 提示**:  &#10;- 若安装后未显示“零信任”图标，可能是与IOA冲突，建议前往安装目录 `/Applications/TrustCyberLink.app` 重新启动程序。  &#10;- 登录后访问应用时，如出现 403 错误，建议更换浏览器（如 Google Chrome 或 Firefox）进行访问。  &#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**零信任无法正常使用**，具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **检查控制器地址设置**  &#10;   打开零信任客户端，选择控制器并切换为 `124.71.208.207` 地址。&#10;&#10;2. **重置控制器设置**  &#10;   如果切换控制器地址后仍无法解决，可尝试重置控制器后再输入 `124.71.208.207`。&#10;&#10;3. **处理IOA冲突问题**  &#10;   - 确认电脑上是否安装了 IOA（如已不再使用，建议卸载）。&#10;   - 卸载 IOA 后重新启动电脑，并重新扫码登录零信任。&#10;&#10;4. **更换浏览器访问应用**  &#10;   - 如果提示 403 Forbidden 或无法访问网页，尝试使用 Google 浏览器或火狐浏览器访问。&#10;   - 关闭当前浏览器，重新打开零信任并刷新策略。&#10;&#10;5. **清除本地 DNS 设置**  &#10;   - 如果退出零信任后无法访问外网，需清除本地 DNS 设置：&#10;     - macOS：删除 `127.0.0.1` 的 DNS 设置，改为自动获取。&#10;     - Windows：同样修改为自动获取 DNS。&#10;&#10;6. **卸载第三方软件干扰**  &#10;   - 卸载可能影响的第三方杀毒软件，例如：360 安全卫士、金山毒霸、火绒安全、鲁大师等。&#10;   - 禁用不必要的开机启动项以提升系统性能。&#10;&#10;7. **重新登录或安装**  &#10;   - 如果仍然无法正常访问，尝试退出零信任并重新登录。&#10;   - 若问题依旧，可尝试卸载后重新安装最新版本的零信任客户端。&#10;&#10;8. **快捷登录方式**  &#10;   - 如果扫码登录失败或提示“不合法的状态”，返回上一级，去掉用户名，选择快捷登录方式。&#10;&#10;9. **联系IT支持**  &#10;   - 如果以上方法均无效，建议联系 IT 帮助台获取进一步协助。&#10;&#10;**💡 提示**: 在进行任何网络设置更改前，请确保了解当前配置，以便在需要时恢复。"/>
-        <filter val="好的!关于**如何登录绩效人才系统**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业门户登录**  &#10;   访问企业门户网址：https://ssoin.zy.com/login，使用企业邮箱账号和密码登录。&#10;&#10;2. **进入绩效人才系统**  &#10;   登录后，在企业门户中依次点击：**绩效人才系统 → 我的学习**，即可进入相关学习或评估模块。&#10;&#10;3. **直接登录Italent系统**  &#10;   如果需要访问Italent系统，可直接在浏览器输入网址：https://www.italent.cn/Login，使用企业邮箱账号登录，并根据提示重置密码（如忘记密码）。&#10;&#10;**💡 提示**: 推荐使用谷歌Chrome浏览器进行登录，以确保系统兼容性和稳定性。如有登录问题，可联系HRBP获取进一步帮助。"/>
-        <filter val="好的!关于企业微信群人数上限,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **了解群类型和人数限制**&#10;   - **内部群**: 默认上限为50人，超过50人后需要在OA系统提交账号权限申请，最高可授权至2000人。&#10;   - **外部群（客户群）**: 默认上限为50人，超过50人后也需要在OA系统提交账号权限申请，最高可授权至200人。&#10;&#10;2. **创建或管理群聊时注意人数限制**&#10;   - 在创建群聊时，如果接近或达到默认人数上限，需提前准备权限申请。&#10;   - 如果是管理员，可以在OA系统中提交账号权限申请以提升群人数上限。&#10;&#10;**💡 提示**: 企业微信支持内部群和外部群的区分，不同类型的群有不同的上限规则。如需扩大群规模，请确保提前完成权限申请流程。"/>
-        <filter val="好的!关于**如何重置通行证密码**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业微信进入IT服务台**  &#10;   打开企业微信，点击【工作台】-【IT服务台】-【更多功能】-【通行证密码重置】&#10;&#10;2. **按照页面提示进行密码重置**  &#10;   进入通行证密码重置页面后，根据系统提示完成身份验证，并设置新的通行证密码。&#10;&#10;**💡 提示**: 通行证密码与邮箱密码不同，使用时不需要添加@zy.com后缀。如遇到其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）。"/>
-        <filter val="好的!关于如何访问监控系统网址,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **使用Edge浏览器开启IE模式**&#10;   - 打开Edge浏览器，点击右上角的三个点，打开设置&#10;   - 在搜索框输入：Explorer&#10;   - 往下滑动找到‘允许在Internet Explorer 模式下重新加载网站(IE模式)’选择允许&#10;   - 右上角的三个点里面就会添加一个‘在Intermet Explorer模式下重新加载’&#10;&#10;2. **输入监控IP地址并切换IE模式**&#10;   - 在网页搜索框里面输入监控IP地址192.168.0.X（X范围一般为5~10）&#10;   - 进入到登录界面后，先点击右上角三个点 选择在‘Intermet Explorer模式下重新加载’，再输入账号密码登录即可&#10;&#10;**💡 提示**: 如果已开启IE模式可直接跳过第一步。如使用中有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）"/>
-        <filter val="好的!关于**无法连接控制器问题**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **切换控制器地址**  &#10;   打开零信任客户端，选择控制器并切换为 `124.71.208.207` 地址。&#10;&#10;2. **重置控制器并重新输入地址**  &#10;   如果切换地址后仍无法解决，尝试在客户端中选择“重置控制器”，然后再次输入 `124.71.208.207`。&#10;&#10;**💡 提示**: 如果仍然无法连接，请检查网络是否正常，并确保防火墙或代理没有阻止相关端口。如有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何清理C盘空间**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **使用系统自带的磁盘清理工具**  &#10;   按下 `Win` 键，搜索并打开“磁盘清理”，选择C盘进行清理。&#10;&#10;2. **转移微信个人数据文件**  &#10;   打开微信 → 点击“设置” → 选择“文件管理” → 进入“文件管理”界面（微信个人数据文件所在位置） → 点击“更改” → 将存储路径更改为C盘以外的其他盘符。这样可以释放大量C盘空间。&#10;&#10;3. **转移企业微信个人数据文件**  &#10;   打开企业微信 → 点击“设置” → 选择“存储管理” → 更改存储路径至C盘以外的其他盘符。&#10;&#10;4. **清理临时文件**  &#10;   按下 `Win + R` → 输入 `%temp%` → 回车 → 全选所有文件并删除。&#10;&#10;5. **手动删除无用文件**  &#10;   定期检查C盘中的大体积文件或不再需要的程序安装包、日志等，手动删除。&#10;&#10;**💡 提示**: 如果发现C盘空间已满，请在执行任何大型操作前先清理出一部分空间；如果遇到安全软件误报问题，请允许相关操作（正常情况下不会误报）。如有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何获取零信任控制器地址**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **查看官方文档或FAQ**&#10;   - 零信任控制器的推荐地址为：**124.71.208.207**。&#10;   - 该地址在多个指引中被明确提及，是默认和推荐使用的控制器地址。&#10;&#10;2. **安装或配置零信任时手动输入**&#10;   - 在首次安装或重新配置零信任客户端时，系统可能会提示需要输入控制器地址。&#10;   - 此时直接输入：**124.71.208.207** 即可。&#10;&#10;3. **切换控制器地址（如遇连接问题）**&#10;   - 如果打开零信任时提示“连接控制器失败”，可以尝试手动切换控制器地址为 **124.71.208.207**。&#10;   - 操作路径通常在客户端设置或网络配置选项中。&#10;&#10;**💡 提示**:  &#10;- 控制器地址 **124.71.208.207** 是官方推荐的稳定地址。  &#10;- 如遇到无法连接的情况，建议先检查网络是否正常，并确保没有本地DNS冲突（如设置了127.0.0.1）。  &#10;- 若仍无法解决，可联系IT帮助台进一步协助。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何下载打印机驱动**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **确定打印机品牌和型号**  &#10;   查看打印机机身或标签纸上的品牌（如京瓷、理光、富士施乐、佳能等）及型号。&#10;&#10;2. **访问对应驱动下载链接**  &#10;   根据打印机品牌，选择以下链接进行下载：&#10;   - **京瓷打印机驱动下载**：适用于Windows系统&#10;   - **京瓷打印机mac系统驱动下载**：适用于Mac系统&#10;   - **理光MPC5503驱动下载**：[点击下载](http://support.ricoh.com/bb/html/dr_ut_e/rcn1/model/mpc4503/mpc4503.htm)&#10;   - **理光MP6054驱动下载**：[点击下载](http://support.ricoh.com/bb/html/dr_ut_e/rcn1/model/mp2554/mp2554.htm?lang=cn)&#10;   - **富士施乐P288驱动下载**：[点击下载](https://m3support-fb.fujifilm-fb.com.cn/driver_downloads/www/)&#10;   - **富士施乐M288驱动下载**：[点击下载](https://m3support-fb.fujifilm-fb.com.cn/driver_downloads/www/)&#10;   - **佳能MF244/MF249驱动下载**：[点击下载](https://www.canon.com.cn/supports/download/sims/list/slist?fileTypeId=23&amp;categoryId=15&amp;seriesId=77&amp;modelId=1234&amp;OSName=Windows%2010%20(x64)&amp;channel=1)&#10;&#10;3. **保存驱动包到电脑硬盘**  &#10;   下载完成后，将驱动包保存在本地磁盘中，便于后续安装使用。&#10;&#10;**💡 提示**: 如果不确定打印机IP地址或型号，可以查看打印机上的标签纸或通过打印机设置界面查询。如有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）。"/>
-        <filter val="好的!关于**零信任控制器无法连接问题**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **切换控制器地址**  &#10;   打开零信任客户端，选择“控制器”选项，将地址切换为 `124.71.208.207`。&#10;&#10;2. **重置控制器并重新输入地址**  &#10;   如果切换控制器地址后仍然无法连接，尝试以下步骤：  &#10;   - 在客户端中选择“重置控制器”功能。  &#10;   - 重置完成后，再次手动输入控制器地址 `124.71.208.207`。&#10;&#10;**💡 提示**: 如果以上方法仍无法解决，请检查网络是否正常，并确保防火墙或安全软件没有阻止零信任的连接。如有需要，可联系IT帮助台进一步协助。"/>
-        <filter val="好的!关于**在Windows安装零信任工具**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载零信任工具安装包**  &#10;   访问以下链接下载Windows版本的零信任工具：  &#10;   [https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe](https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe)&#10;&#10;2. **运行安装程序**  &#10;   双击下载的安装包，点击“是”继续安装。&#10;&#10;3. **同意协议并选择安装位置**  &#10;   - 点击“我同意”。  &#10;   - 选择安装位置（可自定义或使用默认路径），然后点击“安装”。&#10;&#10;4. **等待安装完成**  &#10;   安装过程中请耐心等待，直到提示安装成功。&#10;&#10;5. **启动零信任工具**  &#10;   安装完成后，默认会自动运行零信任工具，并在桌面显示图标。如果没有自动运行，可以手动打开桌面图标。&#10;&#10;6. **扫码登录**  &#10;   打开零信任工具后，通过扫码登录即可访问内部系统。&#10;&#10;7. **输入控制器地址（如需）**  &#10;   如果第一次安装时提示需要输入控制器地址，请输入 `sec.zy.com` 或 `124.71.208.207`，然后确认并扫码登录。&#10;&#10;**💡 提示**:  &#10;- 安装前请确保已卸载旧版安全助手（如有）。  &#10;- 若安装后未显示零信任图标，可前往安装目录 `C:\Program Files (x86)\TrustCyberLink` 下手动运行 `TrustCyberLink.exe`。  &#10;- 登录后请勿退出零信任工具，否则可能无法正常访问内部应用。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何解决连接共享问题**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **删除Windows凭证并重新连接**&#10;   - 按下键盘上的 `WIN(田) + R`，打开运行框。&#10;   - 输入 `control` 并回车，进入控制面板。&#10;   - 点击“凭据管理器” &gt; 选择“Windows凭据”。&#10;   - 找到与共享服务器相关的条目（如 `192.168.0.26`），点击“删除”。&#10;   - 删除后重启电脑，然后重新尝试连接共享文件夹。&#10;&#10;2. **通过地址栏手动连接共享文件夹**&#10;   - 打开任意一个文件夹，在地址栏输入：  &#10;     ```&#10;     \\192.168.0.26&#10;     ```&#10;   - 回车后会弹出登录窗口，输入正确的账户和密码，并勾选“记住密码”，点击确认。&#10;&#10;3. **创建快捷方式到桌面**&#10;   - 在成功连接的共享文件夹上点击【右键】，选择【创建快捷方式】。&#10;   - 快捷方式将出现在桌面上，方便下次快速访问。&#10;&#10;4. **处理提示“多连接”的情况**&#10;   - 如果连接时提示“已有多个连接”，请尝试：&#10;     - 注销当前用户账号；&#10;     - 或者重启电脑以清除之前的连接记录。&#10;&#10;5. **设置开机自动挂载共享盘（适用于Mac系统）**&#10;   - 打开“系统偏好设置” &gt; 点选“用户和群组”。&#10;   - 在左侧选择你的用户名，切换到“登录项”标签页。&#10;   - 将已挂载的网络驱动器图标拖放到登录项列表中。&#10;   - 可选：勾选“隐藏”，这样启动时不会自动打开 Finder 窗口。&#10;&#10;**💡 提示**:  &#10;- 共享文件夹的用户名和密码需根据校区及业务类型确定。例如：成长类为 `fdb`，密码为 `zy+校区+业务缩写`。  &#10;- 如遇到权限问题或无法连接，请联系IT帮助台或在OA系统提交报障单（OA地址：http://oa.zy.com）。  &#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**重置企业邮箱密码失败**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业微信尝试重置密码**  &#10;   打开企业微信 &gt; 【工作台】 &gt; 【IT服务台】 &gt; 【更多功能】 &gt; 【邮箱密码重置】，按照页面提示进行密码修改。&#10;&#10;2. **检查密码规则是否符合要求**  &#10;   263企业邮箱的密码需满足以下条件：  &#10;   - 包含大小写字母、数字和符号  &#10;   - 长度不少于8位  &#10;   - 不能使用连续字符（如123456）或简单密码（如password）  &#10;&#10;3. **确认手机号绑定状态正常**  &#10;   如果提示短信验证码无法接收，请在OA系统上发起【账户/权限申请】流程，将旧手机号变更为当前可用号码。  &#10;   操作路径：登录OA系统 &gt; 【发起流程】 &gt; 【IT类】 &gt; 【IT服务】 &gt; 【账户/权限申请】  &#10;   - “系统”选择“263企业邮箱”  &#10;   - 在“描述”中写明需求（例如：更换绑定手机号）&#10;&#10;4. **重新绑定企业微信**  &#10;   重置密码后，需要重新在企业微信中绑定邮箱：  &#10;   登录企业微信 &gt; 【工作台】 &gt; 【263企业邮箱】 &gt; 输入邮箱和新密码完成绑定&#10;&#10;**💡 提示**: 如果多次尝试仍无法成功重置密码，建议联系IT帮助台或在OA系统填写IT报障单寻求进一步协助（OA地址：http://oa.zy.com）。"/>
-        <filter val="好的!关于**如何连接共享文件夹**,具体操作如下:&#10;&#10;---&#10;&#10;### **Windows系统操作步骤**&#10;&#10;1. **访问共享文件夹**&#10;   - 打开【此电脑】或【我的电脑】&#10;   - 在左上角地址栏输入共享IP地址：`\\192.168.0.26`，然后按回车&#10;&#10;2. **输入用户名和密码**&#10;   - 弹出安全验证窗口后，输入对应的用户名和密码（根据业务类型）：&#10;     - 成长-班辅：用户名 `fdb`，密码格式为 `zy+校区+业务缩写`（如 `zyncfdb`）&#10;     - 亲子-个辅：用户名 `gf`，密码格式为 `zy+校区+gf`&#10;     - 志业：用户名 `sgz`，密码格式为 `zy+校区+sgz`&#10;   - 勾选【记住我的凭据】以便下次自动登录&#10;&#10;3. **创建桌面快捷方式**&#10;   - 在需要创建快捷方式的共享文件夹上点击【右键】&#10;   - 选择【创建快捷方式】，快捷方式将出现在桌面上&#10;&#10;4. **删除旧凭证并重新连接（如无法连接）**&#10;   - 按下 `Win + R`，输入 `control` 并回车&#10;   - 点击【凭据管理器】→【Windows凭据】&#10;   - 找到 `192.168.0.26`，点击【删除】&#10;   - 重启电脑后重新尝试连接&#10;&#10;---&#10;&#10;### **Mac系统操作步骤**&#10;&#10;1. **连接服务器**&#10;   - 点击左上角菜单栏【前往】→【连接服务器】，或使用快捷键 `Command + K`&#10;   - 输入服务器地址：`smb://192.168.0.26`&#10;&#10;2. **输入用户名和密码**&#10;   - 使用与Windows相同的用户名和密码规则&#10;   - 点击【连接】&#10;&#10;3. **设置开机自动挂载共享盘**&#10;   - 打开【系统偏好设置】→【用户与群组】&#10;   - 选择你的用户名 → 点击【登录项】标签&#10;   - 将已挂载的网络驱动器图标拖入登录项列表中&#10;   - 可勾选【隐藏】以避免启动时打开 Finder 窗口&#10;&#10;---&#10;&#10;### **💡 提示**&#10;- 如果遇到连接问题，请先删除旧的Windows凭证并重启电脑。&#10;- 不建议勾选“记住密码”，以免因密码过期导致连接失败。&#10;- 如仍有问题，可联系IT帮助台或在OA系统提交报障单（[OA系统地址](http://oa.zy.com)）。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何获取悦智学安装包**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **访问官网下载页面**  &#10;   打开浏览器，输入网址 `https://zxx.zy.com/download` 进入下载页面。&#10;&#10;2. **选择适合的安装包格式**  &#10;   - 如果是**安卓设备**，请下载 `.apk` 格式的安装包。  &#10;   - 如果是**Windows系统**，可以选择 `.exe` 安装包进行下载。&#10;&#10;3. **下载完成后进行安装**  &#10;   - 对于**安卓用户**：点击下载好的 `.apk` 文件开始安装；如果遇到安装失败，请参考以下提示。&#10;   - 对于**iOS用户**：前往 App Store 搜索“卓越在线”进行下载安装。&#10;&#10;4. **解决安装问题（如需）**  &#10;   - 如果在华为等设备上安装失败，请进入“设置 &gt; 安全和隐私 &gt; 更多安全设置”，关闭“外部来源应用检查”后再尝试安装。&#10;   - 若无法通过网页下载，可将安装包直接发送给家长或学生进行安装。&#10;&#10;**💡 提示**:  &#10;- 如果下载了 Windows 的 `.exe` 安装包但无法安装，建议改用安卓的 `.apk` 安装包。  &#10;- iOS 用户若遇到支付提示，可以参考相关视频教程完成下载。  &#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**在Windows安装零信任系统**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **下载安装包**  &#10;   访问以下链接下载零信任工具的Windows版本安装包：  &#10;   `https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe`&#10;&#10;2. **运行安装程序**  &#10;   双击打开下载的安装包，点击“是”继续安装。&#10;&#10;3. **同意协议**  &#10;   在安装界面中点击“我同意”。&#10;&#10;4. **选择安装位置（可选）**  &#10;   你可以自定义安装位置，也可以使用默认路径。点击“安装”继续。&#10;&#10;5. **等待安装完成**  &#10;   安装过程可能需要几分钟时间，请耐心等待直到提示安装完成。&#10;&#10;6. **启动零信任工具**  &#10;   安装完成后，默认会勾选运行零信任工具，并在桌面上显示图标。如果没有自动运行，可以手动双击桌面图标启动。&#10;&#10;7. **扫码登录**  &#10;   打开零信任工具后，使用企业微信扫码登录即可访问内部系统。&#10;&#10;8. **输入控制器地址（如需）**  &#10;   如果第一次安装时提示需要输入控制器地址，请输入 `sec.zy.com` 或 `124.71.208.207`，然后点击确认并扫码登录。&#10;&#10;**💡 提示**:  &#10;- 安装前请确保已卸载安全助手（如有），以避免冲突。  &#10;- 若安装过程中遇到问题，可尝试重新安装或联系IT帮助台寻求支持。  &#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**零信任控制器地址怎么查**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **打开零信任客户端**&#10;   - 启动已安装的零信任客户端程序。&#10;&#10;2. **查看控制器设置**&#10;   - 在客户端界面中找到“控制器”或“服务器地址”相关的设置选项。&#10;   - 通常在登录前的配置页面或设置菜单中可以查看当前使用的控制器地址。&#10;&#10;3. **默认控制器地址**&#10;   - 如果未手动更改过，零信任客户端的默认控制器地址为：**124.71.208.207**（参考官方推荐设置）。&#10;&#10;4. **修改控制器地址（如需要）**&#10;   - 如需切换控制器地址，可在控制器设置中手动输入新的地址（例如：sec.zy.com 或 124.71.208.207）。&#10;&#10;**💡 提示**:  &#10;- 如果无法访问或连接失败，建议尝试切换回官方推荐的控制器地址 `124.71.208.207`。  &#10;- 更多问题可联系IT帮助台或参考OA系统上的报障流程。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何下载seafile**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **访问下载页面**  &#10;   打开浏览器，输入 seafile 的官方下载地址：https://www.seafile.com/download/&#10;&#10;2. **选择适合的客户端版本**  &#10;   根据你的操作系统（Windows 或 Mac）选择对应的桌面客户端进行下载。例如：&#10;   - Windows 客户端下载链接：https://seafile-downloads.oss-cn-shanghai.aliyuncs.com/seadrive-3.0.9.msi&#10;   - Mac 客户端下载链接：https://seafile-downloads.oss-cn-shanghai.aliyuncs.com/seadrive-3.0.9.pkg&#10;&#10;3. **安装客户端**  &#10;   下载完成后，双击安装文件，按照提示进行安装。建议使用默认设置进行安装。&#10;&#10;4. **设置资料保存路径**  &#10;   安装过程中会提示你选择一个用于存储同步资料的文件夹。建议不要选择 C 盘，尽量选择容量较大的磁盘，并为该文件夹起一个容易识别的名字。&#10;&#10;5. **登录 Seafile 账号**  &#10;   安装完成后打开 Seafile 客户端，输入你的部门云盘网站、邮箱和密码（通常是 OA 密码），完成登录。&#10;&#10;**💡 提示**: 如果在使用中有其他问题，可以联系 IT 帮助台或通过 OA 系统提交 IT 报障单。"/>
-        <filter val="好的!关于**如何重置内部信息系统密码**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业微信进入IT服务台**  &#10;   打开企业微信，点击【工作台】- 搜索并进入【IT服务台】。&#10;&#10;2. **选择“更多功能”中的密码重置选项**  &#10;   在【IT服务台】中找到并点击【更多功能】，然后根据需要选择：&#10;   - 【邮箱密码重置】：用于重置邮箱系统的密码。&#10;   - 【通行证密码重置】：用于重置通行证系统的密码（注意：通行证密码与邮箱密码不同）。&#10;&#10;3. **按照页面提示完成密码修改**  &#10;   根据系统引导填写新密码，并确认提交。&#10;&#10;**💡 提示**: 如果在操作过程中遇到问题，可以联系企业微信中的【IT帮助台】或访问OA系统（http://oa.zy.com）填写IT报障单寻求帮助。"/>
-        <filter val="```&#10;好的!关于如何获取金蝶账号密码,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **忘记密码重置**  &#10;   如果您忘记了密码，可以在登录页面点击“忘记密码”选项，按照提示进行密码重置。&#10;&#10;2. **扫码登录**  &#10;   您也可以选择切换到企业微信的扫码登录方式，通过企业微信扫描二维码完成登录，无需手动输入账号密码。&#10;&#10;**💡 提示**: 如果您仍然无法解决登录问题，建议联系您的管理员或技术支持团队协助处理。&#10;```"/>
-        <filter val="好的!关于**如何下载零信任安装包**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **打开浏览器并访问下载链接**  &#10;   在浏览器中输入以下链接，进入下载页面：  &#10;   - Windows版本下载地址:  &#10;     `https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.121.exe`  &#10;   - macOS版本下载地址:  &#10;     `https://obs-secure-poc.obs.cn-south-1.myhuaweicloud.com/20250903/TrustCyberLink_PC_Setup_2.207.120.dmg`&#10;&#10;2. **开始下载安装包**  &#10;   点击链接后，系统会自动开始下载安装文件。确保网络连接稳定，并等待下载完成。&#10;&#10;3. **保存安装包到本地**  &#10;   下载完成后，找到安装包（如 `TrustCyberLink_PC_Setup_2.207.121.exe` 或 `.dmg` 文件），建议将其保存在易于查找的位置，例如桌面或“下载”文件夹。&#10;&#10;**💡 提示**:  &#10;- 如果无法直接访问下载链接，请联系IT帮助台获取最新版本的安装包。  &#10;- 安装前请确保已卸载安全助手（如有安装）以避免冲突。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于如何登录263邮箱,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过网页端登录**&#10;   - 打开浏览器，访问网址：https://www.263.net/&#10;   - 点击【登录】按钮&#10;   - 输入您的**邮箱账号**和**密码**（如忘记密码，请参考“忘记密码”相关指引进行重置）&#10;&#10;2. **绑定手机号码**&#10;   - 登录后，系统会提示您输入**手机号码**并获取**短信验证码**&#10;   - 输入正确的验证码后，点击确认，完成手机号的绑定&#10;&#10;3. **企业微信绑定263邮箱**&#10;   - 打开企业微信，进入【工作台】&#10;   - 点击【263企业邮箱】应用&#10;   - 输入您的邮箱账号和密码，完成绑定&#10;&#10;**💡 提示**: 如果首次登录或更换设备，可能会提示异地登录。请在邮箱设置中添加信任城市以避免频繁验证。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**在Mac上连接共享文件夹**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **打开“连接服务器”界面**  &#10;   在电脑的左上角，点击【Go/前往】-【Connect to Server/连接服务器】，或者使用键盘快捷键【Command + K】&#10;&#10;2. **输入共享服务器地址**  &#10;   在弹出的窗口中输入校区共享盘地址：`smb://192.168.0.26`&#10;&#10;3. **输入账号密码进行连接**  &#10;   点击“+”号添加服务器后，输入对应的用户名和密码（例如成长校区班辅用户：用户名为 `fdb`，密码为 `zyncfdb`），然后点击“连接”&#10;&#10;4. **查看并访问共享文件夹**  &#10;   连接成功后，会自动弹出共享盘，您可以在 Finder 中看到共享文件夹（如“ks”、“班辅共享”等），双击即可访问&#10;&#10;5. **设置开机自动挂载共享盘**  &#10;   - 打开系统偏好设置，点选“用户与群组”&#10;   - 在左侧列表中选择你的用户名，切换到“登录项”标签&#10;   - 将已经挂载的网络驱动器图标拖放到登录项列表中&#10;   - 可选：勾选“隐藏”，这样系统启动时不会自动打开 Finder 窗口&#10;&#10;6. **创建桌面快捷方式**  &#10;   - 在需要创建快捷方式的共享文件夹上，点击【右键】，选择【创建快捷方式】&#10;   - 该文件夹的快捷访问路径就会出现在桌面上&#10;&#10;**💡 提示**:  &#10;- 如果无法正常连接共享盘，请检查是否输入了正确的用户名和密码，并确保网络连接正常。  &#10;- 如遇到问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何设置打铃系统响铃**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **打开打铃系统程序**  &#10;   - 双击桌面快捷方式打开程序（适用于自动版或雨花石版）。&#10;&#10;2. **暂停当前任务并进入管理界面**  &#10;   - 在操作界面中，先点击“暂停任务”，然后点击“管理”按钮，进入打铃计划的设置界面。&#10;&#10;3. **添加或修改打铃计划**  &#10;   - 根据需求设定单日任务计划，包括具体的响铃时间。&#10;   - 如果需要重复设置，可使用“复制到其他星期”功能（适用于自动版）。&#10;&#10;4. **启用打铃计划**  &#10;   - 完成设置后，记得点击“启用”按钮，使计划生效。&#10;&#10;**💡 提示**: &#10;- 雨花石版本安装时建议安装在D盘，并确保以管理员模式运行程序，否则可能导致注册不生效。&#10;- 如遇到问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**如何使用传屏助手**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **安装希象传屏软件**  &#10;   - 接收端：在一体机上找到桌面图标“无线传屏”，打开即可获得投屏码。  &#10;   - 发送端：点击下载Windows或Mac版本的希象传屏，如C盘内存不足可选择其他磁盘进行安装。&#10;&#10;2. **获取并输入投屏码**  &#10;   - 在接收端打开“无线传屏”程序，获取投屏码。  &#10;   - 在发送端打开希象传屏软件，输入接收端提供的投屏码进行连接。&#10;&#10;3. **选择投屏方式**  &#10;   - 投屏成功后，可在发送端选择投屏模式为“桌面”或“窗口”。&#10;&#10;4. **确保网络一致**  &#10;   - 注意：投屏前请确认发送端和接收端连接的是同一个WiFi网络。&#10;&#10;**💡 提示**: 默认情况下，“安全模式”是关闭的，如果开启则需要输入4位数字码。如遇到问题，可联系IT帮助台或在OA系统（http://oa.zy.com）填写报障单。"/>
-        <filter val="好的!关于**如何重置263邮箱密码**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **通过企业微信重置密码**  &#10;   打开企业微信，点击【工作台】-【IT服务台】-【更多功能】-【邮箱密码重置】，按照页面提示进行密码修改。&#10;&#10;2. **通过网页重置密码（已绑定手机）**  &#10;   访问网址：https://mm.263.com/wm2e/website/jsp/resetPassword.jsp，根据提示完成密码重置。&#10;&#10;**💡 提示**: 重置密码后，如果使用了邮件客户端（如Outlook、Foxmail、Macbook邮件等），需要更新客户端中的密码信息。此外，新密码需符合以下规则：包含大小写字母、数字和符号，长度不少于8位，不能使用连续字符或简单密码。"/>
-        <filter val="好的!关于**如何查看零信任控制器地址**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **打开零信任客户端**  &#10;   在桌面或开始菜单中找到并启动“零信任”客户端。&#10;&#10;2. **进入设置或连接界面**  &#10;   根据客户端界面，通常在首次启动或登录界面会提示输入控制器地址。如果没有提示，可以点击界面上的“设置”按钮。&#10;&#10;3. **查看控制器地址配置**  &#10;   在设置或连接选项中，可以看到当前配置的控制器地址（通常是 `124.71.208.207` 或 `sec.zy.com`）。&#10;&#10;4. **修改控制器地址（如需要）**  &#10;   如果需要切换控制器地址，可以选择手动输入新的地址（例如 `124.71.208.207`），然后保存设置。&#10;&#10;**💡 提示**:  &#10;- 如果无法看到控制器地址，请参考客户端的帮助文档或联系IT帮助台获取支持。  &#10;- 控制器地址默认为 `124.71.208.207`，如果遇到连接问题，可尝试重新输入该地址。"/>
-        <filter val="好的!关于**如何清理Windows C盘空间**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **使用系统自带的磁盘清理工具**  &#10;   按下 `Win` 键，搜索并打开“磁盘清理”，选择C盘进行清理。&#10;&#10;2. **清理临时文件**  &#10;   按下 `Win + R`，输入 `%temp%` 并回车，全选临时文件夹中的内容并删除。&#10;&#10;3. **转移微信个人数据文件**  &#10;   打开微信 → 设置 → 文件管理 → 更改存储路径至C盘以外的其他盘符（如D盘或E盘），以释放C盘空间。&#10;&#10;4. **转移企业微信个人数据文件**  &#10;   打开企业微信 → 设置 → 存储管理 → 更改存储位置至C盘以外的其他盘符。&#10;&#10;**💡 提示**: 如果C盘空间已满，请在执行上述操作前先清理出部分空间。此外，如果遇到安全软件误报问题，请根据提示允许相关操作。如有其他问题，可联系IT帮助台或在OA上填写IT报障单（OA系统地址：http://oa.zy.com）。&#10;&#10;如有其他问题随时问我！"/>
-        <filter val="好的!关于**零信任控制器无法连接怎么解决**,具体操作如下:&#10;&#10;**操作步骤**&#10;&#10;1. **切换控制器地址**  &#10;   打开零信任客户端，选择“控制器”选项，将地址切换为 `124.71.208.207`。&#10;&#10;2. **重置控制器并重新输入地址**  &#10;   如果切换控制器地址后问题仍未解决，尝试以下步骤：  &#10;   - 选择“重置控制器”功能；  &#10;   - 重置完成后，再次输入控制器地址 `124.71.208.207`。&#10;&#10;**💡 提示**: 如果仍然无法连接，请检查网络是否正常，并确保防火墙或安全软件没有拦截相关端口。如有需要，可联系IT帮助台进一步排查。"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
